--- a/tool/release-copy-maurizio-cattelan-le-26.xlsx
+++ b/tool/release-copy-maurizio-cattelan-le-26.xlsx
@@ -492,7 +492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C76"/>
+  <dimension ref="A1:C78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1054,409 +1054,441 @@
     <row r="39" ht="32" customHeight="1">
       <c r="A39" s="4" t="inlineStr">
         <is>
+          <t>card_line_1</t>
+        </is>
+      </c>
+      <c r="B39" s="8" t="inlineStr">
+        <is>
+          <t>The duct-taped banana of Comedian, transplanted from the gallery wall to a hyper-realistic landscape, in four silkscreen layers sealed with matte varnish.</t>
+        </is>
+      </c>
+      <c r="C39" s="9" t="inlineStr">
+        <is>
+          <t>one sentence on the first work, 15 to 30 words, under its card in six emails. With several works, say something different about each: the edition is described above the cards, so do not call each one a limited edition print.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="32" customHeight="1">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>card_line_2</t>
+        </is>
+      </c>
+      <c r="B40" s="8" t="inlineStr"/>
+      <c r="C40" s="9" t="inlineStr">
+        <is>
+          <t>the second titled work; blank otherwise</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="32" customHeight="1">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>card_line_3</t>
+        </is>
+      </c>
+      <c r="B41" s="8" t="inlineStr"/>
+      <c r="C41" s="9" t="inlineStr">
+        <is>
+          <t>the third; blank otherwise</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="32" customHeight="1">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
           <t>quote</t>
         </is>
       </c>
-      <c r="B39" s="8" t="inlineStr">
+      <c r="B42" s="8" t="inlineStr">
         <is>
           <t>A comedian is doomed to make people laugh.</t>
         </is>
       </c>
-      <c r="C39" s="9" t="inlineStr">
+      <c r="C42" s="9" t="inlineStr">
         <is>
           <t>verbatim, a complete sentence, or blank</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="7" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="7" t="inlineStr">
         <is>
           <t>Derived (formulas, do not edit)</t>
         </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="4" t="inlineStr">
-        <is>
-          <t>named</t>
-        </is>
-      </c>
-      <c r="B42" s="10">
-        <f>$B$4&amp;IF($B$6="",""," (@"&amp;$B$6&amp;")")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="4" t="inlineStr">
-        <is>
-          <t>named_x</t>
-        </is>
-      </c>
-      <c r="B43" s="10">
-        <f>$B$4&amp;IF($B$7="",""," (@"&amp;$B$7&amp;")")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="4" t="inlineStr">
-        <is>
-          <t>collab_x</t>
-        </is>
-      </c>
-      <c r="B44" s="10">
-        <f>IF($B$5=$B$4,$B$43,$B$5)</f>
-        <v/>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>a_unit</t>
+          <t>named</t>
         </is>
       </c>
       <c r="B45" s="10">
-        <f>IF(OR(LEFT($B$17,1)="a",LEFT($B$17,1)="e",LEFT($B$17,1)="i",LEFT($B$17,1)="o",LEFT($B$17,1)="u"),"an ","a ")&amp;$B$17</f>
+        <f>$B$4&amp;IF($B$6="",""," (@"&amp;$B$6&amp;")")</f>
         <v/>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>work</t>
+          <t>named_x</t>
         </is>
       </c>
       <c r="B46" s="10">
-        <f>IF($B$14="yes","the "&amp;$B$11&amp;" series",IF($B$12="","‘"&amp;$B$11&amp;"’",IF($B$13="","‘"&amp;$B$11&amp;"’ and ‘"&amp;$B$12&amp;"’","‘"&amp;$B$11&amp;"’, ‘"&amp;$B$12&amp;"’ and ‘"&amp;$B$13&amp;"’")))</f>
+        <f>$B$4&amp;IF($B$7="",""," (@"&amp;$B$7&amp;")")</f>
         <v/>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>Work</t>
+          <t>collab_x</t>
         </is>
       </c>
       <c r="B47" s="10">
-        <f>UPPER(LEFT($B$46,1))&amp;MID($B$46,2,999)</f>
+        <f>IF($B$5=$B$4,$B$46,$B$5)</f>
         <v/>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>work_email</t>
+          <t>a_unit</t>
         </is>
       </c>
       <c r="B48" s="10">
-        <f>IF($B$14="yes","the "&amp;$B$11&amp;" series",IF($B$12="",$B$11,IF($B$13="",$B$11&amp;" and "&amp;$B$12,$B$11&amp;", "&amp;$B$12&amp;" and "&amp;$B$13)))</f>
+        <f>IF(OR(LEFT($B$17,1)="a",LEFT($B$17,1)="e",LEFT($B$17,1)="i",LEFT($B$17,1)="o",LEFT($B$17,1)="u"),"an ","a ")&amp;$B$17</f>
         <v/>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>Work_email</t>
+          <t>work</t>
         </is>
       </c>
       <c r="B49" s="10">
-        <f>UPPER(LEFT($B$48,1))&amp;MID($B$48,2,999)</f>
+        <f>IF($B$14="yes","the "&amp;$B$11&amp;" series",IF($B$12="","‘"&amp;$B$11&amp;"’",IF($B$13="","‘"&amp;$B$11&amp;"’ and ‘"&amp;$B$12&amp;"’","‘"&amp;$B$11&amp;"’, ‘"&amp;$B$12&amp;"’ and ‘"&amp;$B$13&amp;"’")))</f>
         <v/>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>work_intro</t>
+          <t>Work</t>
         </is>
       </c>
       <c r="B50" s="10">
-        <f>IF($B$16=1,$B$11&amp;", ","")&amp;$B$15&amp;IF($B$37="","",IF(LEFT($B$37,1)=",",""," ")&amp;$B$37)</f>
+        <f>UPPER(LEFT($B$49,1))&amp;MID($B$49,2,999)</f>
         <v/>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>support</t>
+          <t>work_email</t>
         </is>
       </c>
       <c r="B51" s="10">
-        <f>IF(OR($B$22="",$B$54),"",", released in support of "&amp;$B$22)</f>
+        <f>IF($B$14="yes","the "&amp;$B$11&amp;" series",IF($B$12="",$B$11,IF($B$13="",$B$11&amp;" and "&amp;$B$12,$B$11&amp;", "&amp;$B$12&amp;" and "&amp;$B$13)))</f>
         <v/>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>beneficiary_tagged</t>
+          <t>Work_email</t>
         </is>
       </c>
       <c r="B52" s="10">
-        <f>IF($B$22="","",$B$22&amp;IF($B$23="",""," (@"&amp;$B$23&amp;")"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="53" ht="80" customHeight="1">
+        <f>UPPER(LEFT($B$51,1))&amp;MID($B$51,2,999)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>bio_tagged</t>
+          <t>work_intro</t>
         </is>
       </c>
       <c r="B53" s="10">
-        <f>IF($B$6="",$B$35,SUBSTITUTE($B$35,$B$4,$B$42,1))</f>
+        <f>IF($B$16=1,$B$11&amp;", ","")&amp;$B$15&amp;IF($B$37="","",IF(LEFT($B$37,1)=",",""," ")&amp;$B$37)</f>
         <v/>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>hook_names_beneficiary</t>
+          <t>support</t>
         </is>
       </c>
       <c r="B54" s="10">
-        <f>IF($B$22="",FALSE,ISNUMBER(SEARCH($B$22,$B$36)))</f>
+        <f>IF(OR($B$22="",$B$57),"",", released in support of "&amp;$B$22)</f>
         <v/>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>features</t>
+          <t>beneficiary_tagged</t>
         </is>
       </c>
       <c r="B55" s="10">
-        <f>$B$28&amp;IF($B$29="","",". "&amp;$B$29)&amp;IF($B$30="","",". "&amp;$B$30)&amp;IF($B$31="","",". "&amp;$B$31)&amp;IF($B$32="","",". "&amp;$B$32)&amp;"."</f>
-        <v/>
-      </c>
-    </row>
-    <row r="56" ht="60" customHeight="1">
+        <f>IF($B$22="","",$B$22&amp;IF($B$23="",""," (@"&amp;$B$23&amp;")"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56" ht="80" customHeight="1">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>features_list</t>
+          <t>bio_tagged</t>
         </is>
       </c>
       <c r="B56" s="10">
-        <f>"· "&amp;$B$28&amp;IF($B$29="","",CHAR(10)&amp;"· "&amp;$B$29)&amp;IF($B$30="","",CHAR(10)&amp;"· "&amp;$B$30)&amp;IF($B$31="","",CHAR(10)&amp;"· "&amp;$B$31)&amp;IF($B$32="","",CHAR(10)&amp;"· "&amp;$B$32)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="57" ht="70" customHeight="1">
+        <f>IF($B$6="",$B$35,SUBSTITUTE($B$35,$B$4,$B$45,1))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>features_list_support</t>
+          <t>hook_names_beneficiary</t>
         </is>
       </c>
       <c r="B57" s="10">
-        <f>$B$56&amp;IF(OR($B$22="",$B$54),"",CHAR(10)&amp;"· Released in support of "&amp;$B$22)</f>
+        <f>IF($B$22="",FALSE,ISNUMBER(SEARCH($B$22,$B$36)))</f>
         <v/>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>making_ours</t>
+          <t>features</t>
         </is>
       </c>
       <c r="B58" s="10">
-        <f>SUBSTITUTE($B$38,"printmakers at Make-Ready","our printmakers at Make-Ready")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="59">
+        <f>$B$28&amp;IF($B$29="","",". "&amp;$B$29)&amp;IF($B$30="","",". "&amp;$B$30)&amp;IF($B$31="","",". "&amp;$B$31)&amp;IF($B$32="","",". "&amp;$B$32)&amp;"."</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59" ht="60" customHeight="1">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>making_ours_tagged</t>
+          <t>features_list</t>
         </is>
       </c>
       <c r="B59" s="10">
-        <f>SUBSTITUTE($B$38,"printmakers at Make-Ready","our printmakers at Make-Ready (@make__ready)")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="60">
+        <f>"· "&amp;$B$28&amp;IF($B$29="","",CHAR(10)&amp;"· "&amp;$B$29)&amp;IF($B$30="","",CHAR(10)&amp;"· "&amp;$B$30)&amp;IF($B$31="","",CHAR(10)&amp;"· "&amp;$B$31)&amp;IF($B$32="","",CHAR(10)&amp;"· "&amp;$B$32)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60" ht="70" customHeight="1">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>launch_date</t>
+          <t>features_list_support</t>
         </is>
       </c>
       <c r="B60" s="10">
-        <f>TEXT($B$20,"d mmmm")</f>
+        <f>$B$59&amp;IF(OR($B$22="",$B$57),"",CHAR(10)&amp;"· Released in support of "&amp;$B$22)</f>
         <v/>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>launch_time</t>
+          <t>making_ours</t>
         </is>
       </c>
       <c r="B61" s="10">
-        <f>TEXT($B$20,"hh:mm")&amp;" UK time"</f>
+        <f>SUBSTITUTE($B$38,"printmakers at Make-Ready","our printmakers at Make-Ready")</f>
         <v/>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>launch_weekday</t>
+          <t>making_ours_tagged</t>
         </is>
       </c>
       <c r="B62" s="10">
-        <f>TEXT($B$20,"dddd")</f>
+        <f>SUBSTITUTE($B$38,"printmakers at Make-Ready","our printmakers at Make-Ready (@make__ready)")</f>
         <v/>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>launch_date_dd</t>
+          <t>launch_date</t>
         </is>
       </c>
       <c r="B63" s="10">
-        <f>TEXT($B$20,"dd mmmm")</f>
+        <f>TEXT($B$20,"d mmmm")</f>
         <v/>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>close_date</t>
+          <t>launch_time</t>
         </is>
       </c>
       <c r="B64" s="10">
-        <f>TEXT($B$21,"d mmmm")</f>
+        <f>TEXT($B$20,"hh:mm")&amp;" UK time"</f>
         <v/>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>close_time</t>
+          <t>launch_weekday</t>
         </is>
       </c>
       <c r="B65" s="10">
-        <f>TEXT($B$21,"hh:mm")&amp;" UK time"</f>
+        <f>TEXT($B$20,"dddd")</f>
         <v/>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>close_weekday</t>
+          <t>launch_date_dd</t>
         </is>
       </c>
       <c r="B66" s="10">
-        <f>TEXT($B$21,"dddd")</f>
+        <f>TEXT($B$20,"dd mmmm")</f>
         <v/>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>close_date_dd</t>
+          <t>close_date</t>
         </is>
       </c>
       <c r="B67" s="10">
-        <f>TEXT($B$21,"dd mmmm")</f>
+        <f>TEXT($B$21,"d mmmm")</f>
         <v/>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>collect_phrase</t>
+          <t>close_time</t>
         </is>
       </c>
       <c r="B68" s="10">
-        <f>SUBSTITUTE($B$15," new "," ",1)</f>
+        <f>TEXT($B$21,"hh:mm")&amp;" UK time"</f>
         <v/>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>edition_phrase_cap</t>
+          <t>close_weekday</t>
         </is>
       </c>
       <c r="B69" s="10">
-        <f>UPPER(LEFT($B$15,1))&amp;MID($B$15,2,999)</f>
+        <f>TEXT($B$21,"dddd")</f>
         <v/>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>window_cap</t>
+          <t>close_date_dd</t>
         </is>
       </c>
       <c r="B70" s="10">
-        <f>UPPER(LEFT($B$19,1))&amp;MID($B$19,2,999)</f>
+        <f>TEXT($B$21,"dd mmmm")</f>
         <v/>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>card_line</t>
+          <t>collect_phrase</t>
         </is>
       </c>
       <c r="B71" s="10">
-        <f>IF($B$12="",$B$69,"A limited edition "&amp;$B$17)&amp;" by "&amp;$B$4&amp;"."</f>
+        <f>SUBSTITUTE($B$15," new "," ",1)</f>
         <v/>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>card</t>
+          <t>edition_phrase_cap</t>
         </is>
       </c>
       <c r="B72" s="10">
-        <f>IF($B$14="yes","Untitled",$B$11)&amp;CHAR(10)&amp;$B$71&amp;IF($B$12="","",CHAR(10)&amp;CHAR(10)&amp;"Card: "&amp;$B$12&amp;CHAR(10)&amp;$B$71)&amp;IF($B$13="","",CHAR(10)&amp;CHAR(10)&amp;"Card: "&amp;$B$13&amp;CHAR(10)&amp;$B$71)</f>
+        <f>UPPER(LEFT($B$15,1))&amp;MID($B$15,2,999)</f>
         <v/>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>quote_line</t>
+          <t>window_cap</t>
         </is>
       </c>
       <c r="B73" s="10">
-        <f>IF($B$39="","","“"&amp;$B$39&amp;"” – "&amp;$B$4)</f>
+        <f>UPPER(LEFT($B$19,1))&amp;MID($B$19,2,999)</f>
         <v/>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>each_artwork</t>
+          <t>card</t>
         </is>
       </c>
       <c r="B74" s="10">
-        <f>IF($B$16&gt;1," for each artwork","")</f>
+        <f>IF($B$14="yes","Untitled",$B$11)&amp;IF($B$39="","",CHAR(10)&amp;$B$39)&amp;IF($B$12="","",CHAR(10)&amp;CHAR(10)&amp;"Card: "&amp;$B$12&amp;IF($B$40="","",CHAR(10)&amp;$B$40))&amp;IF($B$13="","",CHAR(10)&amp;CHAR(10)&amp;"Card: "&amp;$B$13&amp;IF($B$41="","",CHAR(10)&amp;$B$41))</f>
         <v/>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>work_word</t>
+          <t>quote_line</t>
         </is>
       </c>
       <c r="B75" s="10">
-        <f>IF($B$16&gt;1,"works","work")</f>
+        <f>IF($B$42="","","“"&amp;$B$42&amp;"” – "&amp;$B$4)</f>
         <v/>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
+          <t>each_artwork</t>
+        </is>
+      </c>
+      <c r="B76" s="10">
+        <f>IF($B$16&gt;1," for each artwork","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="4" t="inlineStr">
+        <is>
+          <t>work_word</t>
+        </is>
+      </c>
+      <c r="B77" s="10">
+        <f>IF($B$16&gt;1,"works","work")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="4" t="inlineStr">
+        <is>
           <t>add_what</t>
         </is>
       </c>
-      <c r="B76" s="10">
-        <f>IF($B$16&gt;1,$B$45,$B$48)</f>
+      <c r="B78" s="10">
+        <f>IF($B$16&gt;1,$B$48,$B$51)</f>
         <v/>
       </c>
     </row>
@@ -1545,7 +1577,7 @@
         </is>
       </c>
       <c r="C6" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6,"{named}",Inputs!$B$42),"{work}",Inputs!$B$46),"{edition_phrase}",Inputs!$B$15)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6,"{named}",Inputs!$B$45),"{work}",Inputs!$B$49),"{edition_phrase}",Inputs!$B$15)</f>
         <v/>
       </c>
     </row>
@@ -1561,7 +1593,7 @@
         </is>
       </c>
       <c r="C7" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B7,"{named}",Inputs!$B$42),"{work}",Inputs!$B$46),"{edition_phrase}",Inputs!$B$15)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B7,"{named}",Inputs!$B$45),"{work}",Inputs!$B$49),"{edition_phrase}",Inputs!$B$15)</f>
         <v/>
       </c>
     </row>
@@ -1577,7 +1609,7 @@
         </is>
       </c>
       <c r="C8" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B8,"{named}",Inputs!$B$42),"{work}",Inputs!$B$46),"{edition_phrase}",Inputs!$B$15)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B8,"{named}",Inputs!$B$45),"{work}",Inputs!$B$49),"{edition_phrase}",Inputs!$B$15)</f>
         <v/>
       </c>
     </row>
@@ -1593,7 +1625,7 @@
         </is>
       </c>
       <c r="C9" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(B9,"{artist}",Inputs!$B$4),"{quote}",Inputs!$B$39)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(B9,"{artist}",Inputs!$B$4),"{quote}",Inputs!$B$42)</f>
         <v/>
       </c>
     </row>
@@ -1609,7 +1641,7 @@
         </is>
       </c>
       <c r="C10" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B10,"{named}",Inputs!$B$42),"{Work}",Inputs!$B$47),"{edition_phrase}",Inputs!$B$15)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B10,"{named}",Inputs!$B$45),"{Work}",Inputs!$B$50),"{edition_phrase}",Inputs!$B$15)</f>
         <v/>
       </c>
     </row>
@@ -1625,7 +1657,7 @@
         </is>
       </c>
       <c r="C11" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B11,"{named}",Inputs!$B$42),"{Work}",Inputs!$B$47),"{window}",Inputs!$B$19)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B11,"{named}",Inputs!$B$45),"{Work}",Inputs!$B$50),"{window}",Inputs!$B$19)</f>
         <v/>
       </c>
     </row>
@@ -1641,7 +1673,7 @@
         </is>
       </c>
       <c r="C12" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(B12,"{named}",Inputs!$B$42),"{work}",Inputs!$B$46)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(B12,"{named}",Inputs!$B$45),"{work}",Inputs!$B$49)</f>
         <v/>
       </c>
     </row>
@@ -1657,7 +1689,7 @@
         </is>
       </c>
       <c r="C13" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(B13,"{named}",Inputs!$B$42),"{work}",Inputs!$B$46)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(B13,"{named}",Inputs!$B$45),"{work}",Inputs!$B$49)</f>
         <v/>
       </c>
     </row>
@@ -1673,7 +1705,7 @@
         </is>
       </c>
       <c r="C14" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(B14,"{named}",Inputs!$B$42),"{work}",Inputs!$B$46)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(B14,"{named}",Inputs!$B$45),"{work}",Inputs!$B$49)</f>
         <v/>
       </c>
     </row>
@@ -1689,7 +1721,7 @@
         </is>
       </c>
       <c r="C15" s="10">
-        <f>SUBSTITUTE(B15,"{features}",Inputs!$B$55)</f>
+        <f>SUBSTITUTE(B15,"{features}",Inputs!$B$58)</f>
         <v/>
       </c>
     </row>
@@ -1705,7 +1737,7 @@
         </is>
       </c>
       <c r="C16" s="10">
-        <f>SUBSTITUTE(B16,"{beneficiary_tagged}",Inputs!$B$52)</f>
+        <f>SUBSTITUTE(B16,"{beneficiary_tagged}",Inputs!$B$55)</f>
         <v/>
       </c>
     </row>
@@ -1721,7 +1753,7 @@
         </is>
       </c>
       <c r="C17" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B17,"{window}",Inputs!$B$19),"{launch_date}",Inputs!$B$60),"{launch_time}",Inputs!$B$61)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B17,"{window}",Inputs!$B$19),"{launch_date}",Inputs!$B$63),"{launch_time}",Inputs!$B$64)</f>
         <v/>
       </c>
     </row>
@@ -1737,7 +1769,7 @@
         </is>
       </c>
       <c r="C18" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(B18,"{close_date}",Inputs!$B$64),"{close_time}",Inputs!$B$65)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(B18,"{close_date}",Inputs!$B$67),"{close_time}",Inputs!$B$68)</f>
         <v/>
       </c>
     </row>
@@ -1753,7 +1785,7 @@
         </is>
       </c>
       <c r="C19" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B19,"{a_unit}",Inputs!$B$45),"{close_date}",Inputs!$B$64),"{close_time}",Inputs!$B$65)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B19,"{a_unit}",Inputs!$B$48),"{close_date}",Inputs!$B$67),"{close_time}",Inputs!$B$68)</f>
         <v/>
       </c>
     </row>
@@ -1769,7 +1801,7 @@
         </is>
       </c>
       <c r="C20" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(B20,"{close_date}",Inputs!$B$64),"{close_time}",Inputs!$B$65)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(B20,"{close_date}",Inputs!$B$67),"{close_time}",Inputs!$B$68)</f>
         <v/>
       </c>
     </row>
@@ -1824,7 +1856,7 @@
         </is>
       </c>
       <c r="C24" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(B24,"{collab_x}",Inputs!$B$44),"{ordinal}",Inputs!$B$10)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(B24,"{collab_x}",Inputs!$B$47),"{ordinal}",Inputs!$B$10)</f>
         <v/>
       </c>
     </row>
@@ -1872,7 +1904,7 @@
         </is>
       </c>
       <c r="C27" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B27,"{link}",Inputs!$B$8),"{window}",Inputs!$B$19),"{launch_date}",Inputs!$B$60),"{launch_time}",Inputs!$B$61)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B27,"{link}",Inputs!$B$8),"{window}",Inputs!$B$19),"{launch_date}",Inputs!$B$63),"{launch_time}",Inputs!$B$64)</f>
         <v/>
       </c>
     </row>
@@ -1888,7 +1920,7 @@
         </is>
       </c>
       <c r="C28" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B28,"{link}",Inputs!$B$8),"{close_date}",Inputs!$B$64),"{close_time}",Inputs!$B$65)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B28,"{link}",Inputs!$B$8),"{close_date}",Inputs!$B$67),"{close_time}",Inputs!$B$68)</f>
         <v/>
       </c>
     </row>
@@ -1904,7 +1936,7 @@
         </is>
       </c>
       <c r="C29" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B29,"{link}",Inputs!$B$8),"{a_unit}",Inputs!$B$45),"{close_date}",Inputs!$B$64),"{close_time}",Inputs!$B$65)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B29,"{link}",Inputs!$B$8),"{a_unit}",Inputs!$B$48),"{close_date}",Inputs!$B$67),"{close_time}",Inputs!$B$68)</f>
         <v/>
       </c>
     </row>
@@ -1959,7 +1991,7 @@
         </is>
       </c>
       <c r="C33" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(B33,"{close_date}",Inputs!$B$64),"{close_time}",Inputs!$B$65)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(B33,"{close_date}",Inputs!$B$67),"{close_time}",Inputs!$B$68)</f>
         <v/>
       </c>
     </row>
@@ -1991,7 +2023,7 @@
         </is>
       </c>
       <c r="C35" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(B35,"{artist}",Inputs!$B$4),"{a_unit}",Inputs!$B$45)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(B35,"{artist}",Inputs!$B$4),"{a_unit}",Inputs!$B$48)</f>
         <v/>
       </c>
     </row>
@@ -2046,7 +2078,7 @@
         </is>
       </c>
       <c r="C39" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(B39,"{artist}",Inputs!$B$4),"{edition_phrase_cap}",Inputs!$B$69)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(B39,"{artist}",Inputs!$B$4),"{edition_phrase_cap}",Inputs!$B$72)</f>
         <v/>
       </c>
     </row>
@@ -2062,7 +2094,7 @@
         </is>
       </c>
       <c r="C40" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B40,"{collab_with}",Inputs!$B$5),"{work_intro}",Inputs!$B$50),"{support}",Inputs!$B$51),"{ordinal}",Inputs!$B$10)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B40,"{collab_with}",Inputs!$B$5),"{work_intro}",Inputs!$B$53),"{support}",Inputs!$B$54),"{ordinal}",Inputs!$B$10)</f>
         <v/>
       </c>
     </row>
@@ -2078,7 +2110,7 @@
         </is>
       </c>
       <c r="C41" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B41,"{window}",Inputs!$B$19),"{launch_time}",Inputs!$B$61),"{launch_weekday}",Inputs!$B$62),"{launch_date_dd}",Inputs!$B$63)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B41,"{window}",Inputs!$B$19),"{launch_time}",Inputs!$B$64),"{launch_weekday}",Inputs!$B$65),"{launch_date_dd}",Inputs!$B$66)</f>
         <v/>
       </c>
     </row>
@@ -2188,7 +2220,7 @@
         </is>
       </c>
       <c r="C49" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B49,"{collab_with}",Inputs!$B$5),"{ordinal}",Inputs!$B$10),"{window}",Inputs!$B$19),"{launch_time}",Inputs!$B$61)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B49,"{collab_with}",Inputs!$B$5),"{ordinal}",Inputs!$B$10),"{window}",Inputs!$B$19),"{launch_time}",Inputs!$B$64)</f>
         <v/>
       </c>
     </row>
@@ -2252,7 +2284,7 @@
         </is>
       </c>
       <c r="C53" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B53,"{collab_with}",Inputs!$B$5),"{work_intro}",Inputs!$B$50),"{support}",Inputs!$B$51),"{ordinal}",Inputs!$B$10)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B53,"{collab_with}",Inputs!$B$5),"{work_intro}",Inputs!$B$53),"{support}",Inputs!$B$54),"{ordinal}",Inputs!$B$10)</f>
         <v/>
       </c>
     </row>
@@ -2268,7 +2300,7 @@
         </is>
       </c>
       <c r="C54" s="10">
-        <f>SUBSTITUTE(B54,"{launch_date}",Inputs!$B$60)</f>
+        <f>SUBSTITUTE(B54,"{launch_date}",Inputs!$B$63)</f>
         <v/>
       </c>
     </row>
@@ -2300,7 +2332,7 @@
         </is>
       </c>
       <c r="C56" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B56,"{collab_with}",Inputs!$B$5),"{work_intro}",Inputs!$B$50),"{support}",Inputs!$B$51),"{ordinal}",Inputs!$B$10)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B56,"{collab_with}",Inputs!$B$5),"{work_intro}",Inputs!$B$53),"{support}",Inputs!$B$54),"{ordinal}",Inputs!$B$10)</f>
         <v/>
       </c>
     </row>
@@ -2316,7 +2348,7 @@
         </is>
       </c>
       <c r="C57" s="10">
-        <f>SUBSTITUTE(B57,"{launch_date}",Inputs!$B$60)</f>
+        <f>SUBSTITUTE(B57,"{launch_date}",Inputs!$B$63)</f>
         <v/>
       </c>
     </row>
@@ -2332,7 +2364,7 @@
         </is>
       </c>
       <c r="C58" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(B58,"{window}",Inputs!$B$19),"{launch_time}",Inputs!$B$61)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(B58,"{window}",Inputs!$B$19),"{launch_time}",Inputs!$B$64)</f>
         <v/>
       </c>
     </row>
@@ -2405,7 +2437,7 @@
         </is>
       </c>
       <c r="C63" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B63,"{collab_with}",Inputs!$B$5),"{work_intro}",Inputs!$B$50),"{support}",Inputs!$B$51),"{ordinal}",Inputs!$B$10),"{window}",Inputs!$B$19)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B63,"{collab_with}",Inputs!$B$5),"{work_intro}",Inputs!$B$53),"{support}",Inputs!$B$54),"{ordinal}",Inputs!$B$10),"{window}",Inputs!$B$19)</f>
         <v/>
       </c>
     </row>
@@ -2421,7 +2453,7 @@
         </is>
       </c>
       <c r="C64" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B64,"{close_time}",Inputs!$B$65),"{close_weekday}",Inputs!$B$66),"{close_date_dd}",Inputs!$B$67),"{add_what}",Inputs!$B$76)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B64,"{close_time}",Inputs!$B$68),"{close_weekday}",Inputs!$B$69),"{close_date_dd}",Inputs!$B$70),"{add_what}",Inputs!$B$78)</f>
         <v/>
       </c>
     </row>
@@ -2453,7 +2485,7 @@
         </is>
       </c>
       <c r="C66" s="10">
-        <f>SUBSTITUTE(B66,"{a_unit}",Inputs!$B$45)</f>
+        <f>SUBSTITUTE(B66,"{a_unit}",Inputs!$B$48)</f>
         <v/>
       </c>
     </row>
@@ -2501,7 +2533,7 @@
         </is>
       </c>
       <c r="C69" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(B69,"{artist}",Inputs!$B$4),"{collect_phrase}",Inputs!$B$68)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(B69,"{artist}",Inputs!$B$4),"{collect_phrase}",Inputs!$B$71)</f>
         <v/>
       </c>
     </row>
@@ -2517,7 +2549,7 @@
         </is>
       </c>
       <c r="C70" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B70,"{close_time}",Inputs!$B$65),"{close_weekday}",Inputs!$B$66),"{close_date_dd}",Inputs!$B$67)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B70,"{close_time}",Inputs!$B$68),"{close_weekday}",Inputs!$B$69),"{close_date_dd}",Inputs!$B$70)</f>
         <v/>
       </c>
     </row>
@@ -2533,7 +2565,7 @@
         </is>
       </c>
       <c r="C71" s="10">
-        <f>SUBSTITUTE(B71,"{a_unit}",Inputs!$B$45)</f>
+        <f>SUBSTITUTE(B71,"{a_unit}",Inputs!$B$48)</f>
         <v/>
       </c>
     </row>
@@ -2556,7 +2588,7 @@
         </is>
       </c>
       <c r="C73" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B73,"{collab_with}",Inputs!$B$5),"{collect_phrase}",Inputs!$B$68),"{ordinal}",Inputs!$B$10),"{close_time}",Inputs!$B$65),"{close_weekday}",Inputs!$B$66),"{close_date_dd}",Inputs!$B$67)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B73,"{collab_with}",Inputs!$B$5),"{collect_phrase}",Inputs!$B$71),"{ordinal}",Inputs!$B$10),"{close_time}",Inputs!$B$68),"{close_weekday}",Inputs!$B$69),"{close_date_dd}",Inputs!$B$70)</f>
         <v/>
       </c>
     </row>
@@ -2572,7 +2604,7 @@
         </is>
       </c>
       <c r="C74" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(B74,"{each_artwork}",Inputs!$B$74),"{work_word}",Inputs!$B$75)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(B74,"{each_artwork}",Inputs!$B$76),"{work_word}",Inputs!$B$77)</f>
         <v/>
       </c>
     </row>
@@ -2588,7 +2620,7 @@
         </is>
       </c>
       <c r="C75" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B75,"{artist}",Inputs!$B$4),"{work_email}",Inputs!$B$48),"{collect_phrase}",Inputs!$B$68)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B75,"{artist}",Inputs!$B$4),"{work_email}",Inputs!$B$51),"{collect_phrase}",Inputs!$B$71)</f>
         <v/>
       </c>
     </row>
@@ -2604,7 +2636,7 @@
         </is>
       </c>
       <c r="C76" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B76,"{close_time}",Inputs!$B$65),"{close_weekday}",Inputs!$B$66),"{close_date_dd}",Inputs!$B$67)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B76,"{close_time}",Inputs!$B$68),"{close_weekday}",Inputs!$B$69),"{close_date_dd}",Inputs!$B$70)</f>
         <v/>
       </c>
     </row>
@@ -2794,7 +2826,7 @@
         </is>
       </c>
       <c r="C89" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B89,"{collab_with}",Inputs!$B$5),"{work_intro}",Inputs!$B$50),"{support}",Inputs!$B$51)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B89,"{collab_with}",Inputs!$B$5),"{work_intro}",Inputs!$B$53),"{support}",Inputs!$B$54)</f>
         <v/>
       </c>
     </row>
@@ -2810,7 +2842,7 @@
         </is>
       </c>
       <c r="C90" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(B90,"{close_date}",Inputs!$B$64),"{close_time}",Inputs!$B$65)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(B90,"{close_date}",Inputs!$B$67),"{close_time}",Inputs!$B$68)</f>
         <v/>
       </c>
     </row>
@@ -2826,7 +2858,7 @@
         </is>
       </c>
       <c r="C91" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B91,"{window}",Inputs!$B$19),"{launch_time}",Inputs!$B$61),"{launch_weekday}",Inputs!$B$62),"{launch_date_dd}",Inputs!$B$63)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B91,"{window}",Inputs!$B$19),"{launch_time}",Inputs!$B$64),"{launch_weekday}",Inputs!$B$65),"{launch_date_dd}",Inputs!$B$66)</f>
         <v/>
       </c>
     </row>
@@ -2952,7 +2984,7 @@
         <v/>
       </c>
       <c r="F4" s="11">
-        <f>Inputs!$B$53</f>
+        <f>Inputs!$B$56</f>
         <v/>
       </c>
       <c r="G4" s="11">
@@ -3004,7 +3036,7 @@
         <v/>
       </c>
       <c r="G5" s="11">
-        <f>Lines!$C$15&amp;IF(Inputs!$B$54,"",IF(Inputs!$B$52="",""," "&amp;Lines!$C$16))</f>
+        <f>Lines!$C$15&amp;IF(Inputs!$B$57,"",IF(Inputs!$B$55="",""," "&amp;Lines!$C$16))</f>
         <v/>
       </c>
       <c r="H5" s="11">
@@ -3048,11 +3080,11 @@
         <v/>
       </c>
       <c r="F6" s="11">
-        <f>Inputs!$B$59</f>
+        <f>Inputs!$B$62</f>
         <v/>
       </c>
       <c r="G6" s="11">
-        <f>Lines!$C$15&amp;IF(Inputs!$B$52="",""," "&amp;Lines!$C$16)</f>
+        <f>Lines!$C$15&amp;IF(Inputs!$B$55="",""," "&amp;Lines!$C$16)</f>
         <v/>
       </c>
       <c r="H6" s="11">
@@ -3092,19 +3124,19 @@
         </is>
       </c>
       <c r="E7" s="11">
-        <f>IF(Inputs!$B$39="","(no quote given, post skipped)",Lines!$C$9)</f>
+        <f>IF(Inputs!$B$42="","(no quote given, post skipped)",Lines!$C$9)</f>
         <v/>
       </c>
       <c r="F7" s="11">
-        <f>IF(Inputs!$B$39="","",Lines!$C$10)</f>
+        <f>IF(Inputs!$B$42="","",Lines!$C$10)</f>
         <v/>
       </c>
       <c r="G7" s="11">
-        <f>IF(Inputs!$B$39="","",Lines!$C$15&amp;IF(Inputs!$B$52="",""," "&amp;Lines!$C$16))</f>
+        <f>IF(Inputs!$B$42="","",Lines!$C$15&amp;IF(Inputs!$B$55="",""," "&amp;Lines!$C$16))</f>
         <v/>
       </c>
       <c r="H7" s="11">
-        <f>IF(Inputs!$B$39="","",IF(Inputs!$B$18="draw",Lines!$C$18,Lines!$C$17))</f>
+        <f>IF(Inputs!$B$42="","",IF(Inputs!$B$18="draw",Lines!$C$18,Lines!$C$17))</f>
         <v/>
       </c>
       <c r="I7" s="11">
@@ -3112,7 +3144,7 @@
         <v/>
       </c>
       <c r="J7" s="11">
-        <f>IF(Inputs!$B$39="","(no quote given, post skipped)",E7&amp;IF(F7="","",CHAR(10)&amp;CHAR(10)&amp;F7)&amp;IF(G7="","",CHAR(10)&amp;CHAR(10)&amp;G7)&amp;IF(H7="","",CHAR(10)&amp;CHAR(10)&amp;H7))</f>
+        <f>IF(Inputs!$B$42="","(no quote given, post skipped)",E7&amp;IF(F7="","",CHAR(10)&amp;CHAR(10)&amp;F7)&amp;IF(G7="","",CHAR(10)&amp;CHAR(10)&amp;G7)&amp;IF(H7="","",CHAR(10)&amp;CHAR(10)&amp;H7))</f>
         <v/>
       </c>
       <c r="K7" s="11">
@@ -3148,7 +3180,7 @@
         <v/>
       </c>
       <c r="G8" s="11">
-        <f>IF(Inputs!$B$18="draw","",Lines!$C$15&amp;IF(Inputs!$B$52="",""," "&amp;Lines!$C$16))</f>
+        <f>IF(Inputs!$B$18="draw","",Lines!$C$15&amp;IF(Inputs!$B$55="",""," "&amp;Lines!$C$16))</f>
         <v/>
       </c>
       <c r="H8" s="11">
@@ -3196,7 +3228,7 @@
         <v/>
       </c>
       <c r="G9" s="11">
-        <f>IF(Inputs!$B$18="draw","",Lines!$C$15&amp;IF(Inputs!$B$52="",""," "&amp;Lines!$C$16))</f>
+        <f>IF(Inputs!$B$18="draw","",Lines!$C$15&amp;IF(Inputs!$B$55="",""," "&amp;Lines!$C$16))</f>
         <v/>
       </c>
       <c r="H9" s="11">
@@ -3244,7 +3276,7 @@
         <v/>
       </c>
       <c r="G10" s="11">
-        <f>Lines!$C$15&amp;IF(Inputs!$B$52="",""," "&amp;Lines!$C$16)</f>
+        <f>Lines!$C$15&amp;IF(Inputs!$B$55="",""," "&amp;Lines!$C$16)</f>
         <v/>
       </c>
       <c r="H10" s="11">
@@ -3404,7 +3436,7 @@
         </is>
       </c>
       <c r="D5" s="11">
-        <f>SUBSTITUTE(IF(Inputs!$B$14="yes",Lines!$C$7,Lines!$C$6),Inputs!$B$42,Inputs!$B$43)</f>
+        <f>SUBSTITUTE(IF(Inputs!$B$14="yes",Lines!$C$7,Lines!$C$6),Inputs!$B$45,Inputs!$B$46)</f>
         <v/>
       </c>
       <c r="E5" s="11">
@@ -3412,7 +3444,7 @@
         <v/>
       </c>
       <c r="F5" s="11">
-        <f>IF(OR(Inputs!$B$22="",Inputs!$B$54),"",Lines!$C$26)</f>
+        <f>IF(OR(Inputs!$B$22="",Inputs!$B$57),"",Lines!$C$26)</f>
         <v/>
       </c>
       <c r="G5" s="11">
@@ -3443,7 +3475,7 @@
         </is>
       </c>
       <c r="D6" s="11">
-        <f>IF(Inputs!$B$18="draw","(not used for a draw)",SUBSTITUTE(Lines!$C$11,Inputs!$B$42,Inputs!$B$43))</f>
+        <f>IF(Inputs!$B$18="draw","(not used for a draw)",SUBSTITUTE(Lines!$C$11,Inputs!$B$45,Inputs!$B$46))</f>
         <v/>
       </c>
       <c r="E6" s="11">
@@ -3482,7 +3514,7 @@
         </is>
       </c>
       <c r="D7" s="11">
-        <f>IF(Inputs!$B$18="draw","(not used for a draw)",SUBSTITUTE(Lines!$C$12,Inputs!$B$42,Inputs!$B$43))</f>
+        <f>IF(Inputs!$B$18="draw","(not used for a draw)",SUBSTITUTE(Lines!$C$12,Inputs!$B$45,Inputs!$B$46))</f>
         <v/>
       </c>
       <c r="E7" s="11">
@@ -3521,7 +3553,7 @@
         </is>
       </c>
       <c r="D8" s="11">
-        <f>IF(Inputs!$B$18="draw",SUBSTITUTE(Lines!$C$14,Inputs!$B$42,Inputs!$B$43),SUBSTITUTE(Lines!$C$13,Inputs!$B$42,Inputs!$B$43))</f>
+        <f>IF(Inputs!$B$18="draw",SUBSTITUTE(Lines!$C$14,Inputs!$B$45,Inputs!$B$46),SUBSTITUTE(Lines!$C$13,Inputs!$B$45,Inputs!$B$46))</f>
         <v/>
       </c>
       <c r="E8" s="11">
@@ -3690,19 +3722,19 @@
         <v/>
       </c>
       <c r="F4" s="11">
-        <f>IF($D4&lt;&gt;"yes","",IF(Inputs!$B$18="draw","Enter the draw for a chance to collect. Closes "&amp;Inputs!$B$64&amp;".","Launching "&amp;Inputs!$B$60&amp;". Register for updates."))</f>
+        <f>IF($D4&lt;&gt;"yes","",IF(Inputs!$B$18="draw","Enter the draw for a chance to collect. Closes "&amp;Inputs!$B$67&amp;".","Launching "&amp;Inputs!$B$63&amp;". Register for updates."))</f>
         <v/>
       </c>
       <c r="G4" s="11">
-        <f>IF($D4&lt;&gt;"yes","",IF(Inputs!$B$18="draw","Enter the draw","Launching "&amp;Inputs!$B$60))</f>
+        <f>IF($D4&lt;&gt;"yes","",IF(Inputs!$B$18="draw","Enter the draw","Launching "&amp;Inputs!$B$63))</f>
         <v/>
       </c>
       <c r="H4" s="11">
-        <f>IF($D4&lt;&gt;"yes","",IF(Inputs!$B$18="draw",Inputs!$B$49,Inputs!$B$49&amp;" by "&amp;Inputs!$B$4))</f>
+        <f>IF($D4&lt;&gt;"yes","",IF(Inputs!$B$18="draw",Inputs!$B$52,Inputs!$B$52&amp;" by "&amp;Inputs!$B$4))</f>
         <v/>
       </c>
       <c r="I4" s="11">
-        <f>IF($D4&lt;&gt;"yes","",(Lines!$C$40&amp;IF(Inputs!$B$36="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$36)&amp;IF(Inputs!$B$58="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$58)&amp;IF(Inputs!$B$56="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$56)&amp;IF(IF(Inputs!$B$18="draw",Lines!$C$33,(Lines!$C$41&amp;IF(Lines!$C$42="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$42)))="","",CHAR(10)&amp;CHAR(10)&amp;IF(Inputs!$B$18="draw",Lines!$C$33,(Lines!$C$41&amp;IF(Lines!$C$42="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$42))))))</f>
+        <f>IF($D4&lt;&gt;"yes","",(Lines!$C$40&amp;IF(Inputs!$B$36="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$36)&amp;IF(Inputs!$B$61="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$61)&amp;IF(Inputs!$B$59="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$59)&amp;IF(IF(Inputs!$B$18="draw",Lines!$C$33,(Lines!$C$41&amp;IF(Lines!$C$42="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$42)))="","",CHAR(10)&amp;CHAR(10)&amp;IF(Inputs!$B$18="draw",Lines!$C$33,(Lines!$C$41&amp;IF(Lines!$C$42="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$42))))))</f>
         <v/>
       </c>
       <c r="J4" s="11">
@@ -3710,15 +3742,15 @@
         <v/>
       </c>
       <c r="K4" s="11">
-        <f>IF($D4&lt;&gt;"yes","",Inputs!$B$72)</f>
+        <f>IF($D4&lt;&gt;"yes","",Inputs!$B$74)</f>
         <v/>
       </c>
       <c r="L4" s="11">
-        <f>IF($D4&lt;&gt;"yes","",Inputs!$B$73)</f>
+        <f>IF($D4&lt;&gt;"yes","",Inputs!$B$75)</f>
         <v/>
       </c>
       <c r="M4" s="11">
-        <f>IF($D4&lt;&gt;"yes","",IF(Inputs!$B$18="draw","Collect "&amp;Inputs!$B$68,"Launching "&amp;Inputs!$B$60))</f>
+        <f>IF($D4&lt;&gt;"yes","",IF(Inputs!$B$18="draw","Collect "&amp;Inputs!$B$71,"Launching "&amp;Inputs!$B$63))</f>
         <v/>
       </c>
       <c r="N4" s="11">
@@ -3828,7 +3860,7 @@
         <v/>
       </c>
       <c r="I6" s="11">
-        <f>IF($D6&lt;&gt;"yes","",(Lines!$C$31&amp;IF(Lines!$C$49="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$49)&amp;IF(Inputs!$B$36="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$36)&amp;IF(Inputs!$B$57="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$57)&amp;IF(Lines!$C$50="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$50)&amp;IF(IF(Inputs!$B$26="","",Lines!$C$36)="","",CHAR(10)&amp;CHAR(10)&amp;IF(Inputs!$B$26="","",Lines!$C$36))&amp;IF(Lines!$C$52="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$52)))</f>
+        <f>IF($D6&lt;&gt;"yes","",(Lines!$C$31&amp;IF(Lines!$C$49="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$49)&amp;IF(Inputs!$B$36="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$36)&amp;IF(Inputs!$B$60="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$60)&amp;IF(Lines!$C$50="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$50)&amp;IF(IF(Inputs!$B$26="","",Lines!$C$36)="","",CHAR(10)&amp;CHAR(10)&amp;IF(Inputs!$B$26="","",Lines!$C$36))&amp;IF(Lines!$C$52="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$52)))</f>
         <v/>
       </c>
       <c r="J6" s="11">
@@ -3891,7 +3923,7 @@
         <v/>
       </c>
       <c r="I7" s="11">
-        <f>IF($D7&lt;&gt;"yes","",(Lines!$C$31&amp;IF(Lines!$C$49="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$49)&amp;IF(Inputs!$B$36="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$36)&amp;IF(Inputs!$B$57="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$57)&amp;IF(Lines!$C$51="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$51)&amp;IF(Lines!$C$52="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$52)&amp;IF(Lines!$C$34="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$34)&amp;IF(Lines!$C$32="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$32)))</f>
+        <f>IF($D7&lt;&gt;"yes","",(Lines!$C$31&amp;IF(Lines!$C$49="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$49)&amp;IF(Inputs!$B$36="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$36)&amp;IF(Inputs!$B$60="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$60)&amp;IF(Lines!$C$51="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$51)&amp;IF(Lines!$C$52="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$52)&amp;IF(Lines!$C$34="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$34)&amp;IF(Lines!$C$32="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$32)))</f>
         <v/>
       </c>
       <c r="J7" s="11">
@@ -3899,7 +3931,7 @@
         <v/>
       </c>
       <c r="K7" s="11">
-        <f>IF($D7&lt;&gt;"yes","",Inputs!$B$72)</f>
+        <f>IF($D7&lt;&gt;"yes","",Inputs!$B$74)</f>
         <v/>
       </c>
       <c r="L7" s="11">
@@ -3962,7 +3994,7 @@
         <v/>
       </c>
       <c r="K8" s="11">
-        <f>IF($D8&lt;&gt;"yes","",Inputs!$B$72)</f>
+        <f>IF($D8&lt;&gt;"yes","",Inputs!$B$74)</f>
         <v/>
       </c>
       <c r="L8" s="11">
@@ -4025,7 +4057,7 @@
         <v/>
       </c>
       <c r="K9" s="11">
-        <f>IF($D9&lt;&gt;"yes","",Inputs!$B$72)</f>
+        <f>IF($D9&lt;&gt;"yes","",Inputs!$B$74)</f>
         <v/>
       </c>
       <c r="L9" s="11">
@@ -4068,7 +4100,7 @@
         <v/>
       </c>
       <c r="F10" s="11">
-        <f>IF($D10&lt;&gt;"yes","",Inputs!$B$70&amp;", starting now.")</f>
+        <f>IF($D10&lt;&gt;"yes","",Inputs!$B$73&amp;", starting now.")</f>
         <v/>
       </c>
       <c r="G10" s="11">
@@ -4076,11 +4108,11 @@
         <v/>
       </c>
       <c r="H10" s="11">
-        <f>IF($D10&lt;&gt;"yes","",Inputs!$B$70&amp;", starting now")</f>
+        <f>IF($D10&lt;&gt;"yes","",Inputs!$B$73&amp;", starting now")</f>
         <v/>
       </c>
       <c r="I10" s="11">
-        <f>IF($D10&lt;&gt;"yes","",(Lines!$C$63&amp;IF(Inputs!$B$36="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$36)&amp;IF(Inputs!$B$58="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$58)&amp;IF(Inputs!$B$57="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$57)&amp;IF(Lines!$C$64="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$64)&amp;IF(IF(Inputs!$B$26="","",Lines!$C$36)="","",CHAR(10)&amp;CHAR(10)&amp;IF(Inputs!$B$26="","",Lines!$C$36))))</f>
+        <f>IF($D10&lt;&gt;"yes","",(Lines!$C$63&amp;IF(Inputs!$B$36="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$36)&amp;IF(Inputs!$B$61="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$61)&amp;IF(Inputs!$B$60="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$60)&amp;IF(Lines!$C$64="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$64)&amp;IF(IF(Inputs!$B$26="","",Lines!$C$36)="","",CHAR(10)&amp;CHAR(10)&amp;IF(Inputs!$B$26="","",Lines!$C$36))))</f>
         <v/>
       </c>
       <c r="J10" s="11">
@@ -4088,15 +4120,15 @@
         <v/>
       </c>
       <c r="K10" s="11">
-        <f>IF($D10&lt;&gt;"yes","",Inputs!$B$72)</f>
+        <f>IF($D10&lt;&gt;"yes","",Inputs!$B$74)</f>
         <v/>
       </c>
       <c r="L10" s="11">
-        <f>IF($D10&lt;&gt;"yes","",Inputs!$B$73)</f>
+        <f>IF($D10&lt;&gt;"yes","",Inputs!$B$75)</f>
         <v/>
       </c>
       <c r="M10" s="11">
-        <f>IF($D10&lt;&gt;"yes","","Collect "&amp;Inputs!$B$68)</f>
+        <f>IF($D10&lt;&gt;"yes","","Collect "&amp;Inputs!$B$71)</f>
         <v/>
       </c>
       <c r="N10" s="11">
@@ -4210,7 +4242,7 @@
         <v/>
       </c>
       <c r="J12" s="11">
-        <f>IF($D12&lt;&gt;"yes","","Buy "&amp;Inputs!$B$45)</f>
+        <f>IF($D12&lt;&gt;"yes","","Buy "&amp;Inputs!$B$48)</f>
         <v/>
       </c>
       <c r="K12" s="11">
@@ -4261,7 +4293,7 @@
         <v/>
       </c>
       <c r="G13" s="11">
-        <f>IF($D13&lt;&gt;"yes","",Inputs!$B$49&amp;" by "&amp;Inputs!$B$4)</f>
+        <f>IF($D13&lt;&gt;"yes","",Inputs!$B$52&amp;" by "&amp;Inputs!$B$4)</f>
         <v/>
       </c>
       <c r="H13" s="11">
@@ -4273,11 +4305,11 @@
         <v/>
       </c>
       <c r="J13" s="11">
-        <f>IF($D13&lt;&gt;"yes","","Buy "&amp;Inputs!$B$45)</f>
+        <f>IF($D13&lt;&gt;"yes","","Buy "&amp;Inputs!$B$48)</f>
         <v/>
       </c>
       <c r="K13" s="11">
-        <f>IF($D13&lt;&gt;"yes","",Inputs!$B$72)</f>
+        <f>IF($D13&lt;&gt;"yes","",Inputs!$B$74)</f>
         <v/>
       </c>
       <c r="L13" s="11">
@@ -4320,7 +4352,7 @@
         <v/>
       </c>
       <c r="F14" s="11">
-        <f>IF($D14&lt;&gt;"yes","",IF(Inputs!$B$18="draw","The draw closes at "&amp;Inputs!$B$65&amp;" on "&amp;Inputs!$B$64&amp;".","Time is almost up."))</f>
+        <f>IF($D14&lt;&gt;"yes","",IF(Inputs!$B$18="draw","The draw closes at "&amp;Inputs!$B$68&amp;" on "&amp;Inputs!$B$67&amp;".","Time is almost up."))</f>
         <v/>
       </c>
       <c r="G14" s="11">
@@ -4340,7 +4372,7 @@
         <v/>
       </c>
       <c r="K14" s="11">
-        <f>IF($D14&lt;&gt;"yes","",Inputs!$B$72)</f>
+        <f>IF($D14&lt;&gt;"yes","",Inputs!$B$74)</f>
         <v/>
       </c>
       <c r="L14" s="11">
@@ -4521,7 +4553,7 @@
         <v/>
       </c>
       <c r="I17" s="11">
-        <f>IF($D17&lt;&gt;"yes","",(Lines!$C$89&amp;IF(Inputs!$B$36="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$36)&amp;IF(Inputs!$B$58="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$58)&amp;IF(IF(Inputs!$B$18="draw",Lines!$C$90,Lines!$C$91)="","",CHAR(10)&amp;CHAR(10)&amp;IF(Inputs!$B$18="draw",Lines!$C$90,Lines!$C$91))))</f>
+        <f>IF($D17&lt;&gt;"yes","",(Lines!$C$89&amp;IF(Inputs!$B$36="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$36)&amp;IF(Inputs!$B$61="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$61)&amp;IF(IF(Inputs!$B$18="draw",Lines!$C$90,Lines!$C$91)="","",CHAR(10)&amp;CHAR(10)&amp;IF(Inputs!$B$18="draw",Lines!$C$90,Lines!$C$91))))</f>
         <v/>
       </c>
       <c r="J17" s="11">

--- a/tool/release-copy-maurizio-cattelan-le-26.xlsx
+++ b/tool/release-copy-maurizio-cattelan-le-26.xlsx
@@ -1030,7 +1030,7 @@
       </c>
       <c r="C37" s="9" t="inlineStr">
         <is>
-          <t>a few words after the edition phrase in the email opener, e.g. spanning five decades of the artist's career. Ten words at most, a phrase not a sentence, no we or our, no artist name, no beneficiary. Blank for none.</t>
+          <t>a few words after the edition phrase in the email opener, e.g. spanning five decades of the artist's career. Ten words at most, a phrase not a sentence, no we or our, no artist name, no beneficiary. Leave it blank when the opener already names the work or says what it supports: with several works the title drops out of this line, and that is what it is for.</t>
         </is>
       </c>
     </row>

--- a/tool/release-copy-maurizio-cattelan-le-26.xlsx
+++ b/tool/release-copy-maurizio-cattelan-le-26.xlsx
@@ -1030,7 +1030,7 @@
       </c>
       <c r="C37" s="9" t="inlineStr">
         <is>
-          <t>a few words after the edition phrase in the email opener, e.g. spanning five decades of the artist's career. Ten words at most, a phrase not a sentence, no we or our, no artist name, no beneficiary. Leave it blank when the opener already names the work or says what it supports: with several works the title drops out of this line, and that is what it is for.</t>
+          <t>a few words after the edition phrase in the email opener, e.g. spanning five decades of the artist's career. Ten words at most, a phrase not a sentence, no we or our, no artist name. Ignored when there is a beneficiary: 'released in support of X' fills the same opening. With several works the title drops out of this line, and that is what it is for.</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
         </is>
       </c>
       <c r="B53" s="10">
-        <f>IF($B$16=1,$B$11&amp;", ","")&amp;$B$15&amp;IF($B$37="","",IF(LEFT($B$37,1)=",",""," ")&amp;$B$37)</f>
+        <f>IF($B$16=1,$B$11&amp;", ","")&amp;$B$15&amp;IF(OR($B$37="",$B$54&lt;&gt;""),"",IF(LEFT($B$37,1)=",",""," ")&amp;$B$37)</f>
         <v/>
       </c>
     </row>

--- a/tool/release-copy-maurizio-cattelan-le-26.xlsx
+++ b/tool/release-copy-maurizio-cattelan-le-26.xlsx
@@ -655,7 +655,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>exactly as it appears; the set's one title if it has one; for untitled works from a named series, the series name</t>
+          <t>exactly as it appears, and what the card is headed with. Untitled works from a series still keep their own titles here</t>
         </is>
       </c>
     </row>
@@ -688,17 +688,13 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>is_series</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+          <t>series_name</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr"/>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>yes only for untitled works from a named series</t>
+          <t>set it to name the works by their series in the prose, for untitled works; the cards keep their own titles. Blank otherwise</t>
         </is>
       </c>
     </row>
@@ -1169,7 +1165,7 @@
         </is>
       </c>
       <c r="B49" s="10">
-        <f>IF($B$14="yes","the "&amp;$B$11&amp;" series",IF($B$12="","‘"&amp;$B$11&amp;"’",IF($B$13="","‘"&amp;$B$11&amp;"’ and ‘"&amp;$B$12&amp;"’","‘"&amp;$B$11&amp;"’, ‘"&amp;$B$12&amp;"’ and ‘"&amp;$B$13&amp;"’")))</f>
+        <f>IF($B$14&lt;&gt;"","the "&amp;$B$14&amp;" series",IF($B$12="","‘"&amp;$B$11&amp;"’",IF($B$13="","‘"&amp;$B$11&amp;"’ and ‘"&amp;$B$12&amp;"’","‘"&amp;$B$11&amp;"’, ‘"&amp;$B$12&amp;"’ and ‘"&amp;$B$13&amp;"’")))</f>
         <v/>
       </c>
     </row>
@@ -1191,7 +1187,7 @@
         </is>
       </c>
       <c r="B51" s="10">
-        <f>IF($B$14="yes","the "&amp;$B$11&amp;" series",IF($B$12="",$B$11,IF($B$13="",$B$11&amp;" and "&amp;$B$12,$B$11&amp;", "&amp;$B$12&amp;" and "&amp;$B$13)))</f>
+        <f>IF($B$14&lt;&gt;"","the "&amp;$B$14&amp;" series",IF($B$12="",$B$11,IF($B$13="",$B$11&amp;" and "&amp;$B$12,$B$11&amp;", "&amp;$B$12&amp;" and "&amp;$B$13)))</f>
         <v/>
       </c>
     </row>
@@ -1444,7 +1440,7 @@
         </is>
       </c>
       <c r="B74" s="10">
-        <f>IF($B$14="yes","Untitled",$B$11)&amp;IF($B$39="","",CHAR(10)&amp;$B$39)&amp;IF($B$12="","",CHAR(10)&amp;CHAR(10)&amp;"Card: "&amp;$B$12&amp;IF($B$40="","",CHAR(10)&amp;$B$40))&amp;IF($B$13="","",CHAR(10)&amp;CHAR(10)&amp;"Card: "&amp;$B$13&amp;IF($B$41="","",CHAR(10)&amp;$B$41))</f>
+        <f>$B$11&amp;IF($B$39="","",CHAR(10)&amp;$B$39)&amp;IF($B$12="","",CHAR(10)&amp;CHAR(10)&amp;"Card: "&amp;$B$12&amp;IF($B$40="","",CHAR(10)&amp;$B$40))&amp;IF($B$13="","",CHAR(10)&amp;CHAR(10)&amp;"Card: "&amp;$B$13&amp;IF($B$41="","",CHAR(10)&amp;$B$41))</f>
         <v/>
       </c>
     </row>
@@ -3028,7 +3024,7 @@
         </is>
       </c>
       <c r="E5" s="11">
-        <f>IF(Inputs!$B$14="yes",Lines!$C$7,Lines!$C$6)</f>
+        <f>IF(Inputs!$B$14&lt;&gt;"",Lines!$C$7,Lines!$C$6)</f>
         <v/>
       </c>
       <c r="F5" s="11">
@@ -3436,7 +3432,7 @@
         </is>
       </c>
       <c r="D5" s="11">
-        <f>SUBSTITUTE(IF(Inputs!$B$14="yes",Lines!$C$7,Lines!$C$6),Inputs!$B$45,Inputs!$B$46)</f>
+        <f>SUBSTITUTE(IF(Inputs!$B$14&lt;&gt;"",Lines!$C$7,Lines!$C$6),Inputs!$B$45,Inputs!$B$46)</f>
         <v/>
       </c>
       <c r="E5" s="11">

--- a/tool/release-copy-maurizio-cattelan-le-26.xlsx
+++ b/tool/release-copy-maurizio-cattelan-le-26.xlsx
@@ -1009,7 +1009,7 @@
       </c>
       <c r="C36" s="9" t="inlineStr">
         <is>
-          <t>2 to 3 sentences about the work. Write it as editorially as you like; the one test is that it must read as well in the middle of an email as at the top of a post. Self-contained, no rhetorical question. It reaches 16 slots, so it is the one fragment that must stand alone.</t>
+          <t>2 to 3 sentences about the work. Write it as editorially as you like; the one test is that it must read as well in the middle of an email as at the top of a post. Self-contained, no rhetorical question, the artist by surname only (the frame has used the full name), one dash at most and never a pair. It reaches 16 slots, so it is the one fragment that must stand alone.</t>
         </is>
       </c>
     </row>

--- a/tool/release-copy-maurizio-cattelan-le-26.xlsx
+++ b/tool/release-copy-maurizio-cattelan-le-26.xlsx
@@ -492,7 +492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C78"/>
+  <dimension ref="A1:C79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1220,270 +1220,281 @@
         </is>
       </c>
       <c r="B54" s="10">
-        <f>IF(OR($B$22="",$B$57),"",", released in support of "&amp;$B$22)</f>
+        <f>IF(OR($B$22="",$B$58),"",", released in support of "&amp;$B$22)</f>
         <v/>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
+          <t>tweet_beneficiary</t>
+        </is>
+      </c>
+      <c r="B55" s="10">
+        <f>IF(OR($B$22="",$B$58),"",", in support of "&amp;$B$22)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
           <t>beneficiary_tagged</t>
         </is>
       </c>
-      <c r="B55" s="10">
+      <c r="B56" s="10">
         <f>IF($B$22="","",$B$22&amp;IF($B$23="",""," (@"&amp;$B$23&amp;")"))</f>
         <v/>
       </c>
     </row>
-    <row r="56" ht="80" customHeight="1">
-      <c r="A56" s="4" t="inlineStr">
+    <row r="57" ht="80" customHeight="1">
+      <c r="A57" s="4" t="inlineStr">
         <is>
           <t>bio_tagged</t>
         </is>
       </c>
-      <c r="B56" s="10">
+      <c r="B57" s="10">
         <f>IF($B$6="",$B$35,SUBSTITUTE($B$35,$B$4,$B$45,1))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="4" t="inlineStr">
-        <is>
-          <t>hook_names_beneficiary</t>
-        </is>
-      </c>
-      <c r="B57" s="10">
-        <f>IF($B$22="",FALSE,ISNUMBER(SEARCH($B$22,$B$36)))</f>
         <v/>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
+          <t>hook_names_beneficiary</t>
+        </is>
+      </c>
+      <c r="B58" s="10">
+        <f>IF($B$22="",FALSE,ISNUMBER(SEARCH($B$22,$B$36)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
           <t>features</t>
         </is>
       </c>
-      <c r="B58" s="10">
+      <c r="B59" s="10">
         <f>$B$28&amp;IF($B$29="","",". "&amp;$B$29)&amp;IF($B$30="","",". "&amp;$B$30)&amp;IF($B$31="","",". "&amp;$B$31)&amp;IF($B$32="","",". "&amp;$B$32)&amp;"."</f>
         <v/>
       </c>
     </row>
-    <row r="59" ht="60" customHeight="1">
-      <c r="A59" s="4" t="inlineStr">
+    <row r="60" ht="60" customHeight="1">
+      <c r="A60" s="4" t="inlineStr">
         <is>
           <t>features_list</t>
         </is>
       </c>
-      <c r="B59" s="10">
+      <c r="B60" s="10">
         <f>"· "&amp;$B$28&amp;IF($B$29="","",CHAR(10)&amp;"· "&amp;$B$29)&amp;IF($B$30="","",CHAR(10)&amp;"· "&amp;$B$30)&amp;IF($B$31="","",CHAR(10)&amp;"· "&amp;$B$31)&amp;IF($B$32="","",CHAR(10)&amp;"· "&amp;$B$32)</f>
         <v/>
       </c>
     </row>
-    <row r="60" ht="70" customHeight="1">
-      <c r="A60" s="4" t="inlineStr">
+    <row r="61" ht="70" customHeight="1">
+      <c r="A61" s="4" t="inlineStr">
         <is>
           <t>features_list_support</t>
         </is>
       </c>
-      <c r="B60" s="10">
-        <f>$B$59&amp;IF(OR($B$22="",$B$57),"",CHAR(10)&amp;"· Released in support of "&amp;$B$22)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="4" t="inlineStr">
-        <is>
-          <t>making_ours</t>
-        </is>
-      </c>
       <c r="B61" s="10">
-        <f>SUBSTITUTE($B$38,"printmakers at Make-Ready","our printmakers at Make-Ready")</f>
+        <f>$B$60&amp;IF(OR($B$22="",$B$58),"",CHAR(10)&amp;"· Released in support of "&amp;$B$22)</f>
         <v/>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>making_ours_tagged</t>
+          <t>making_ours</t>
         </is>
       </c>
       <c r="B62" s="10">
-        <f>SUBSTITUTE($B$38,"printmakers at Make-Ready","our printmakers at Make-Ready (@make__ready)")</f>
+        <f>SUBSTITUTE($B$38,"printmakers at Make-Ready","our printmakers at Make-Ready")</f>
         <v/>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>launch_date</t>
+          <t>making_ours_tagged</t>
         </is>
       </c>
       <c r="B63" s="10">
-        <f>TEXT($B$20,"d mmmm")</f>
+        <f>SUBSTITUTE($B$38,"printmakers at Make-Ready","our printmakers at Make-Ready (@make__ready)")</f>
         <v/>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>launch_time</t>
+          <t>launch_date</t>
         </is>
       </c>
       <c r="B64" s="10">
-        <f>TEXT($B$20,"hh:mm")&amp;" UK time"</f>
+        <f>TEXT($B$20,"d mmmm")</f>
         <v/>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>launch_weekday</t>
+          <t>launch_time</t>
         </is>
       </c>
       <c r="B65" s="10">
-        <f>TEXT($B$20,"dddd")</f>
+        <f>TEXT($B$20,"hh:mm")&amp;" UK time"</f>
         <v/>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>launch_date_dd</t>
+          <t>launch_weekday</t>
         </is>
       </c>
       <c r="B66" s="10">
-        <f>TEXT($B$20,"dd mmmm")</f>
+        <f>TEXT($B$20,"dddd")</f>
         <v/>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>close_date</t>
+          <t>launch_date_dd</t>
         </is>
       </c>
       <c r="B67" s="10">
-        <f>TEXT($B$21,"d mmmm")</f>
+        <f>TEXT($B$20,"dd mmmm")</f>
         <v/>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>close_time</t>
+          <t>close_date</t>
         </is>
       </c>
       <c r="B68" s="10">
-        <f>TEXT($B$21,"hh:mm")&amp;" UK time"</f>
+        <f>TEXT($B$21,"d mmmm")</f>
         <v/>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>close_weekday</t>
+          <t>close_time</t>
         </is>
       </c>
       <c r="B69" s="10">
-        <f>TEXT($B$21,"dddd")</f>
+        <f>TEXT($B$21,"hh:mm")&amp;" UK time"</f>
         <v/>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>close_date_dd</t>
+          <t>close_weekday</t>
         </is>
       </c>
       <c r="B70" s="10">
-        <f>TEXT($B$21,"dd mmmm")</f>
+        <f>TEXT($B$21,"dddd")</f>
         <v/>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>collect_phrase</t>
+          <t>close_date_dd</t>
         </is>
       </c>
       <c r="B71" s="10">
-        <f>SUBSTITUTE($B$15," new "," ",1)</f>
+        <f>TEXT($B$21,"dd mmmm")</f>
         <v/>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>edition_phrase_cap</t>
+          <t>collect_phrase</t>
         </is>
       </c>
       <c r="B72" s="10">
-        <f>UPPER(LEFT($B$15,1))&amp;MID($B$15,2,999)</f>
+        <f>SUBSTITUTE($B$15," new "," ",1)</f>
         <v/>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>window_cap</t>
+          <t>edition_phrase_cap</t>
         </is>
       </c>
       <c r="B73" s="10">
-        <f>UPPER(LEFT($B$19,1))&amp;MID($B$19,2,999)</f>
+        <f>UPPER(LEFT($B$15,1))&amp;MID($B$15,2,999)</f>
         <v/>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>card</t>
+          <t>window_cap</t>
         </is>
       </c>
       <c r="B74" s="10">
-        <f>$B$11&amp;IF($B$39="","",CHAR(10)&amp;$B$39)&amp;IF($B$12="","",CHAR(10)&amp;CHAR(10)&amp;"Card: "&amp;$B$12&amp;IF($B$40="","",CHAR(10)&amp;$B$40))&amp;IF($B$13="","",CHAR(10)&amp;CHAR(10)&amp;"Card: "&amp;$B$13&amp;IF($B$41="","",CHAR(10)&amp;$B$41))</f>
+        <f>UPPER(LEFT($B$19,1))&amp;MID($B$19,2,999)</f>
         <v/>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>quote_line</t>
+          <t>card</t>
         </is>
       </c>
       <c r="B75" s="10">
-        <f>IF($B$42="","","“"&amp;$B$42&amp;"” – "&amp;$B$4)</f>
+        <f>$B$11&amp;IF($B$39="","",CHAR(10)&amp;$B$39)&amp;IF($B$12="","",CHAR(10)&amp;CHAR(10)&amp;"Card: "&amp;$B$12&amp;IF($B$40="","",CHAR(10)&amp;$B$40))&amp;IF($B$13="","",CHAR(10)&amp;CHAR(10)&amp;"Card: "&amp;$B$13&amp;IF($B$41="","",CHAR(10)&amp;$B$41))</f>
         <v/>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>each_artwork</t>
+          <t>quote_line</t>
         </is>
       </c>
       <c r="B76" s="10">
-        <f>IF($B$16&gt;1," for each artwork","")</f>
+        <f>IF($B$42="","","“"&amp;$B$42&amp;"” – "&amp;$B$4)</f>
         <v/>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>work_word</t>
+          <t>each_artwork</t>
         </is>
       </c>
       <c r="B77" s="10">
-        <f>IF($B$16&gt;1,"works","work")</f>
+        <f>IF($B$16&gt;1," for each artwork","")</f>
         <v/>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
         <is>
+          <t>work_word</t>
+        </is>
+      </c>
+      <c r="B78" s="10">
+        <f>IF($B$16&gt;1,"works","work")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="4" t="inlineStr">
+        <is>
           <t>add_what</t>
         </is>
       </c>
-      <c r="B78" s="10">
+      <c r="B79" s="10">
         <f>IF($B$16&gt;1,$B$48,$B$51)</f>
         <v/>
       </c>
@@ -1499,7 +1510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C91"/>
+  <dimension ref="A1:C92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -1717,7 +1728,7 @@
         </is>
       </c>
       <c r="C15" s="10">
-        <f>SUBSTITUTE(B15,"{features}",Inputs!$B$58)</f>
+        <f>SUBSTITUTE(B15,"{features}",Inputs!$B$59)</f>
         <v/>
       </c>
     </row>
@@ -1733,7 +1744,7 @@
         </is>
       </c>
       <c r="C16" s="10">
-        <f>SUBSTITUTE(B16,"{beneficiary_tagged}",Inputs!$B$55)</f>
+        <f>SUBSTITUTE(B16,"{beneficiary_tagged}",Inputs!$B$56)</f>
         <v/>
       </c>
     </row>
@@ -1749,7 +1760,7 @@
         </is>
       </c>
       <c r="C17" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B17,"{window}",Inputs!$B$19),"{launch_date}",Inputs!$B$63),"{launch_time}",Inputs!$B$64)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B17,"{window}",Inputs!$B$19),"{launch_date}",Inputs!$B$64),"{launch_time}",Inputs!$B$65)</f>
         <v/>
       </c>
     </row>
@@ -1765,7 +1776,7 @@
         </is>
       </c>
       <c r="C18" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(B18,"{close_date}",Inputs!$B$67),"{close_time}",Inputs!$B$68)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(B18,"{close_date}",Inputs!$B$68),"{close_time}",Inputs!$B$69)</f>
         <v/>
       </c>
     </row>
@@ -1781,7 +1792,7 @@
         </is>
       </c>
       <c r="C19" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B19,"{a_unit}",Inputs!$B$48),"{close_date}",Inputs!$B$67),"{close_time}",Inputs!$B$68)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B19,"{a_unit}",Inputs!$B$48),"{close_date}",Inputs!$B$68),"{close_time}",Inputs!$B$69)</f>
         <v/>
       </c>
     </row>
@@ -1797,7 +1808,7 @@
         </is>
       </c>
       <c r="C20" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(B20,"{close_date}",Inputs!$B$67),"{close_time}",Inputs!$B$68)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(B20,"{close_date}",Inputs!$B$68),"{close_time}",Inputs!$B$69)</f>
         <v/>
       </c>
     </row>
@@ -1875,99 +1886,99 @@
     <row r="26" ht="16" customHeight="1">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>tweet · beneficiary line</t>
+          <t>tweet · announce · status</t>
         </is>
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>Released in support of {beneficiary}.</t>
+          <t>Announcing {work}, {edition_phrase} by {named_x}{tweet_beneficiary}.</t>
         </is>
       </c>
       <c r="C26" s="10">
-        <f>SUBSTITUTE(B26,"{beneficiary}",Inputs!$B$22)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B26,"{named_x}",Inputs!$B$46),"{work}",Inputs!$B$49),"{tweet_beneficiary}",Inputs!$B$55),"{edition_phrase}",Inputs!$B$15)</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="32" customHeight="1">
       <c r="A27" s="4" t="inlineStr">
         <is>
+          <t>tweet · announce · status, series</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>Announcing {edition_phrase} by {named_x}, from {work}{tweet_beneficiary}.</t>
+        </is>
+      </c>
+      <c r="C27" s="10">
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B27,"{named_x}",Inputs!$B$46),"{work}",Inputs!$B$49),"{tweet_beneficiary}",Inputs!$B$55),"{edition_phrase}",Inputs!$B$15)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="32" customHeight="1">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
           <t>tweet · action before launch, timed</t>
         </is>
       </c>
-      <c r="B27" s="8" t="inlineStr">
-        <is>
-          <t>Available for {window} from {launch_time} on {launch_date}. Sign up for updates: {link}</t>
-        </is>
-      </c>
-      <c r="C27" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B27,"{link}",Inputs!$B$8),"{window}",Inputs!$B$19),"{launch_date}",Inputs!$B$63),"{launch_time}",Inputs!$B$64)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28" ht="16" customHeight="1">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>tweet · action, draw</t>
-        </is>
-      </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>Closes {close_date} at {close_time}. Enter the draw: {link}</t>
+          <t>Launches {launch_date} at {launch_time} for {window}. Sign up for updates: {link}</t>
         </is>
       </c>
       <c r="C28" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B28,"{link}",Inputs!$B$8),"{close_date}",Inputs!$B$67),"{close_time}",Inputs!$B$68)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B28,"{link}",Inputs!$B$8),"{window}",Inputs!$B$19),"{launch_date}",Inputs!$B$64),"{launch_time}",Inputs!$B$65)</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="16" customHeight="1">
       <c r="A29" s="4" t="inlineStr">
         <is>
+          <t>tweet · action, draw</t>
+        </is>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>Closes {close_date} at {close_time}. Enter the draw: {link}</t>
+        </is>
+      </c>
+      <c r="C29" s="10">
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B29,"{link}",Inputs!$B$8),"{close_date}",Inputs!$B$68),"{close_time}",Inputs!$B$69)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" ht="16" customHeight="1">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
           <t>tweet · action while open, timed</t>
         </is>
       </c>
-      <c r="B29" s="8" t="inlineStr">
+      <c r="B30" s="8" t="inlineStr">
         <is>
           <t>Closes {close_date} at {close_time}. Buy {a_unit}: {link}</t>
         </is>
       </c>
-      <c r="C29" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B29,"{link}",Inputs!$B$8),"{a_unit}",Inputs!$B$48),"{close_date}",Inputs!$B$67),"{close_time}",Inputs!$B$68)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="3" t="inlineStr">
+      <c r="C30" s="10">
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B30,"{link}",Inputs!$B$8),"{a_unit}",Inputs!$B$48),"{close_date}",Inputs!$B$68),"{close_time}",Inputs!$B$69)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
         <is>
           <t>EMAILS · shared</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="16" customHeight="1">
-      <c r="A31" s="4" t="inlineStr">
+    <row r="32" ht="16" customHeight="1">
+      <c r="A32" s="4" t="inlineStr">
         <is>
           <t>email · greeting</t>
         </is>
       </c>
-      <c r="B31" s="8" t="inlineStr">
+      <c r="B32" s="8" t="inlineStr">
         <is>
           <t>Hi {{ personalization_token('contact.firstname', 'there') }},</t>
-        </is>
-      </c>
-      <c r="C31" s="10">
-        <f>B31</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32" ht="32" customHeight="1">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t>email · questions line</t>
-        </is>
-      </c>
-      <c r="B32" s="8" t="inlineStr">
-        <is>
-          <t>If you have any questions, please don't hesitate to get in touch by replying to this email.</t>
         </is>
       </c>
       <c r="C32" s="10">
@@ -1978,76 +1989,76 @@
     <row r="33" ht="32" customHeight="1">
       <c r="A33" s="4" t="inlineStr">
         <is>
+          <t>email · questions line</t>
+        </is>
+      </c>
+      <c r="B33" s="8" t="inlineStr">
+        <is>
+          <t>If you have any questions, please don't hesitate to get in touch by replying to this email.</t>
+        </is>
+      </c>
+      <c r="C33" s="10">
+        <f>B33</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34" ht="32" customHeight="1">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
           <t>email · draw line</t>
         </is>
       </c>
-      <c r="B33" s="8" t="inlineStr">
+      <c r="B34" s="8" t="inlineStr">
         <is>
           <t>Enter the draw for a chance to collect. Closes at {close_time} on {close_date}.</t>
         </is>
       </c>
-      <c r="C33" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(B33,"{close_date}",Inputs!$B$67),"{close_time}",Inputs!$B$68)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34" ht="64" customHeight="1">
-      <c r="A34" s="4" t="inlineStr">
+      <c r="C34" s="10">
+        <f>SUBSTITUTE(SUBSTITUTE(B34,"{close_date}",Inputs!$B$68),"{close_time}",Inputs!$B$69)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35" ht="64" customHeight="1">
+      <c r="A35" s="4" t="inlineStr">
         <is>
           <t>email · edition numbers line</t>
         </is>
       </c>
-      <c r="B34" s="8" t="inlineStr">
+      <c r="B35" s="8" t="inlineStr">
         <is>
           <t>Earlier orders will typically receive a lower edition number, with framed editions receiving lower edition numbers than unframed prints. You can read more on how we allocate edition numbers across a release here.</t>
         </is>
       </c>
-      <c r="C34" s="10">
-        <f>B34</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35" ht="16" customHeight="1">
-      <c r="A35" s="4" t="inlineStr">
+      <c r="C35" s="10">
+        <f>B35</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36" ht="16" customHeight="1">
+      <c r="A36" s="4" t="inlineStr">
         <is>
           <t>email · kicker · collect</t>
         </is>
       </c>
-      <c r="B35" s="8" t="inlineStr">
+      <c r="B36" s="8" t="inlineStr">
         <is>
           <t>Collect {a_unit} by {artist}</t>
         </is>
       </c>
-      <c r="C35" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(B35,"{artist}",Inputs!$B$4),"{a_unit}",Inputs!$B$48)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36" ht="32" customHeight="1">
-      <c r="A36" s="4" t="inlineStr">
-        <is>
-          <t>email · framing offer · welcome</t>
-        </is>
-      </c>
-      <c r="B36" s="8" t="inlineStr">
-        <is>
-          <t>As a welcome gesture, enjoy {framing_percent}% off our in-house framing on your first purchase using the code {framing_code} at checkout.</t>
-        </is>
-      </c>
       <c r="C36" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(B36,"{framing_code}",Inputs!$B$26),"{framing_percent}",Inputs!$B$27)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(B36,"{artist}",Inputs!$B$4),"{a_unit}",Inputs!$B$48)</f>
         <v/>
       </c>
     </row>
     <row r="37" ht="32" customHeight="1">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>email · framing offer · reminder</t>
+          <t>email · framing offer · welcome</t>
         </is>
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>As a reminder, you can enjoy {framing_percent}% off our in-house framing on your first purchase using the code {framing_code} at checkout.</t>
+          <t>As a welcome gesture, enjoy {framing_percent}% off our in-house framing on your first purchase using the code {framing_code} at checkout.</t>
         </is>
       </c>
       <c r="C37" s="10">
@@ -2055,109 +2066,109 @@
         <v/>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="3" t="inlineStr">
+    <row r="38" ht="32" customHeight="1">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>email · framing offer · reminder</t>
+        </is>
+      </c>
+      <c r="B38" s="8" t="inlineStr">
+        <is>
+          <t>As a reminder, you can enjoy {framing_percent}% off our in-house framing on your first purchase using the code {framing_code} at checkout.</t>
+        </is>
+      </c>
+      <c r="C38" s="10">
+        <f>SUBSTITUTE(SUBSTITUTE(B38,"{framing_code}",Inputs!$B$26),"{framing_percent}",Inputs!$B$27)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
         <is>
           <t>EMAILS · announcement</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="16" customHeight="1">
-      <c r="A39" s="4" t="inlineStr">
+    <row r="40" ht="16" customHeight="1">
+      <c r="A40" s="4" t="inlineStr">
         <is>
           <t>email · announce · subject</t>
         </is>
       </c>
-      <c r="B39" s="8" t="inlineStr">
+      <c r="B40" s="8" t="inlineStr">
         <is>
           <t>{artist} – {edition_phrase_cap}</t>
         </is>
       </c>
-      <c r="C39" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(B39,"{artist}",Inputs!$B$4),"{edition_phrase_cap}",Inputs!$B$72)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40" ht="32" customHeight="1">
-      <c r="A40" s="4" t="inlineStr">
-        <is>
-          <t>email · announce · opener</t>
-        </is>
-      </c>
-      <c r="B40" s="8" t="inlineStr">
-        <is>
-          <t>We're delighted to announce our {ordinal} collaboration with {collab_with} – {work_intro}{support}.</t>
-        </is>
-      </c>
       <c r="C40" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B40,"{collab_with}",Inputs!$B$5),"{work_intro}",Inputs!$B$53),"{support}",Inputs!$B$54),"{ordinal}",Inputs!$B$10)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(B40,"{artist}",Inputs!$B$4),"{edition_phrase_cap}",Inputs!$B$73)</f>
         <v/>
       </c>
     </row>
     <row r="41" ht="32" customHeight="1">
       <c r="A41" s="4" t="inlineStr">
         <is>
+          <t>email · announce · opener</t>
+        </is>
+      </c>
+      <c r="B41" s="8" t="inlineStr">
+        <is>
+          <t>We're delighted to announce our {ordinal} collaboration with {collab_with} – {work_intro}{support}.</t>
+        </is>
+      </c>
+      <c r="C41" s="10">
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B41,"{collab_with}",Inputs!$B$5),"{work_intro}",Inputs!$B$53),"{support}",Inputs!$B$54),"{ordinal}",Inputs!$B$10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42" ht="32" customHeight="1">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
           <t>email · announce · launch line, timed</t>
         </is>
       </c>
-      <c r="B41" s="8" t="inlineStr">
+      <c r="B42" s="8" t="inlineStr">
         <is>
           <t>The edition will be available to collect for {window} only, starting at {launch_time} on {launch_weekday}, {launch_date_dd}.</t>
         </is>
       </c>
-      <c r="C41" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B41,"{window}",Inputs!$B$19),"{launch_time}",Inputs!$B$64),"{launch_weekday}",Inputs!$B$65),"{launch_date_dd}",Inputs!$B$66)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="42" ht="16" customHeight="1">
-      <c r="A42" s="4" t="inlineStr">
+      <c r="C42" s="10">
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B42,"{window}",Inputs!$B$19),"{launch_time}",Inputs!$B$65),"{launch_weekday}",Inputs!$B$66),"{launch_date_dd}",Inputs!$B$67)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43" ht="16" customHeight="1">
+      <c r="A43" s="4" t="inlineStr">
         <is>
           <t>email · announce · register line</t>
         </is>
       </c>
-      <c r="B42" s="8" t="inlineStr">
+      <c r="B43" s="8" t="inlineStr">
         <is>
           <t>Click below to learn more and register for updates.</t>
         </is>
       </c>
-      <c r="C42" s="10">
-        <f>B42</f>
-        <v/>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="3" t="inlineStr">
+      <c r="C43" s="10">
+        <f>B43</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
         <is>
           <t>EMAILS · welcome (TL flow)</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="32" customHeight="1">
-      <c r="A44" s="4" t="inlineStr">
+    <row r="45" ht="32" customHeight="1">
+      <c r="A45" s="4" t="inlineStr">
         <is>
           <t>email · welcome · 1</t>
         </is>
       </c>
-      <c r="B44" s="8" t="inlineStr">
+      <c r="B45" s="8" t="inlineStr">
         <is>
           <t>Welcome {{ personalization_token('contact.firstname', 'to Avant Arte') }}!</t>
-        </is>
-      </c>
-      <c r="C44" s="10">
-        <f>B44</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45" ht="64" customHeight="1">
-      <c r="A45" s="4" t="inlineStr">
-        <is>
-          <t>email · welcome · 2</t>
-        </is>
-      </c>
-      <c r="B45" s="8" t="inlineStr">
-        <is>
-          <t>Avant Arte began with a simple mission – to make collecting art more accessible. Since then, we've collaborated with hundreds of inspiring artists, from rising stars to icons like Ai Weiwei, Jenny Holzer, Lee Ufan and Carrie Mae Weems.</t>
         </is>
       </c>
       <c r="C45" s="10">
@@ -2168,83 +2179,83 @@
     <row r="46" ht="64" customHeight="1">
       <c r="A46" s="4" t="inlineStr">
         <is>
+          <t>email · welcome · 2</t>
+        </is>
+      </c>
+      <c r="B46" s="8" t="inlineStr">
+        <is>
+          <t>Avant Arte began with a simple mission – to make collecting art more accessible. Since then, we've collaborated with hundreds of inspiring artists, from rising stars to icons like Ai Weiwei, Jenny Holzer, Lee Ufan and Carrie Mae Weems.</t>
+        </is>
+      </c>
+      <c r="C46" s="10">
+        <f>B46</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47" ht="64" customHeight="1">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
           <t>email · welcome · 3</t>
         </is>
       </c>
-      <c r="B46" s="8" t="inlineStr">
+      <c r="B47" s="8" t="inlineStr">
         <is>
           <t>Our upcoming collaboration with {collab_with} is the latest in this lineage. If you're new to collecting art or curious about limited editions, our library of guides is a good place to start. In particular, How to collect art and What is an edition?</t>
         </is>
       </c>
-      <c r="C46" s="10">
-        <f>SUBSTITUTE(B46,"{collab_with}",Inputs!$B$5)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="47" ht="32" customHeight="1">
-      <c r="A47" s="4" t="inlineStr">
+      <c r="C47" s="10">
+        <f>SUBSTITUTE(B47,"{collab_with}",Inputs!$B$5)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48" ht="32" customHeight="1">
+      <c r="A48" s="4" t="inlineStr">
         <is>
           <t>email · welcome · 4</t>
         </is>
       </c>
-      <c r="B47" s="8" t="inlineStr">
+      <c r="B48" s="8" t="inlineStr">
         <is>
           <t>Let us know if you have any questions. We're excited to see what you collect.</t>
         </is>
       </c>
-      <c r="C47" s="10">
-        <f>B47</f>
-        <v/>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="3" t="inlineStr">
+      <c r="C48" s="10">
+        <f>B48</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
         <is>
           <t>EMAILS · early access</t>
         </is>
-      </c>
-    </row>
-    <row r="49" ht="32" customHeight="1">
-      <c r="A49" s="4" t="inlineStr">
-        <is>
-          <t>email · early access, timed · opener</t>
-        </is>
-      </c>
-      <c r="B49" s="8" t="inlineStr">
-        <is>
-          <t>Our {ordinal} collaboration with {collab_with} launches tomorrow at {launch_time} and will be available to collect for {window} only.</t>
-        </is>
-      </c>
-      <c r="C49" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B49,"{collab_with}",Inputs!$B$5),"{ordinal}",Inputs!$B$10),"{window}",Inputs!$B$19),"{launch_time}",Inputs!$B$64)</f>
-        <v/>
       </c>
     </row>
     <row r="50" ht="32" customHeight="1">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>email · early access, timed · registered line</t>
+          <t>email · early access, timed · opener</t>
         </is>
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>As a thank you for registering for updates, we're offering you the chance to collect the release 24 hours before everyone else.</t>
+          <t>Our {ordinal} collaboration with {collab_with} launches tomorrow at {launch_time} and will be available to collect for {window} only.</t>
         </is>
       </c>
       <c r="C50" s="10">
-        <f>B50</f>
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B50,"{collab_with}",Inputs!$B$5),"{ordinal}",Inputs!$B$10),"{window}",Inputs!$B$19),"{launch_time}",Inputs!$B$65)</f>
         <v/>
       </c>
     </row>
     <row r="51" ht="32" customHeight="1">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>email · early access, timed · past collectors line</t>
+          <t>email · early access, timed · registered line</t>
         </is>
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>As a previous collector of the artist, we're offering you the chance to order the collaboration 24 hours before everyone else.</t>
+          <t>As a thank you for registering for updates, we're offering you the chance to collect the release 24 hours before everyone else.</t>
         </is>
       </c>
       <c r="C51" s="10">
@@ -2252,15 +2263,15 @@
         <v/>
       </c>
     </row>
-    <row r="52" ht="16" customHeight="1">
+    <row r="52" ht="32" customHeight="1">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>email · early access, timed · unlock line</t>
+          <t>email · early access, timed · past collectors line</t>
         </is>
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>Unlock early access using the link below.</t>
+          <t>As a previous collector of the artist, we're offering you the chance to order the collaboration 24 hours before everyone else.</t>
         </is>
       </c>
       <c r="C52" s="10">
@@ -2268,248 +2279,248 @@
         <v/>
       </c>
     </row>
-    <row r="53" ht="32" customHeight="1">
+    <row r="53" ht="16" customHeight="1">
       <c r="A53" s="4" t="inlineStr">
         <is>
+          <t>email · early access, timed · unlock line</t>
+        </is>
+      </c>
+      <c r="B53" s="8" t="inlineStr">
+        <is>
+          <t>Unlock early access using the link below.</t>
+        </is>
+      </c>
+      <c r="C53" s="10">
+        <f>B53</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54" ht="32" customHeight="1">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
           <t>email · early access, draw · 1</t>
         </is>
       </c>
-      <c r="B53" s="8" t="inlineStr">
+      <c r="B54" s="8" t="inlineStr">
         <is>
           <t>We're currently preparing the launch of our {ordinal} collaboration with {collab_with} – {work_intro}{support}.</t>
         </is>
       </c>
-      <c r="C53" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B53,"{collab_with}",Inputs!$B$5),"{work_intro}",Inputs!$B$53),"{support}",Inputs!$B$54),"{ordinal}",Inputs!$B$10)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="54" ht="96" customHeight="1">
-      <c r="A54" s="4" t="inlineStr">
+      <c r="C54" s="10">
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B54,"{collab_with}",Inputs!$B$5),"{work_intro}",Inputs!$B$53),"{support}",Inputs!$B$54),"{ordinal}",Inputs!$B$10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55" ht="96" customHeight="1">
+      <c r="A55" s="4" t="inlineStr">
         <is>
           <t>email · early access, draw · 2</t>
         </is>
       </c>
-      <c r="B54" s="8" t="inlineStr">
+      <c r="B55" s="8" t="inlineStr">
         <is>
           <t>The edition will launch publicly on {launch_date} and will be allocated by a randomised draw; however, for the next 48 hours we're offering a small group of collectors a first look, plus access to a limited number of pre-orders. Based on your order history and the artists you've expressed an interest in, I thought the edition would be a good fit for your collection.</t>
         </is>
       </c>
-      <c r="C54" s="10">
-        <f>SUBSTITUTE(B54,"{launch_date}",Inputs!$B$63)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="55" ht="32" customHeight="1">
-      <c r="A55" s="4" t="inlineStr">
-        <is>
-          <t>email · early access, draw · 3</t>
-        </is>
-      </c>
-      <c r="B55" s="8" t="inlineStr">
-        <is>
-          <t>Explore the artwork and place your order via the private link below. Use code {early_access_code} to unlock early access.</t>
-        </is>
-      </c>
       <c r="C55" s="10">
-        <f>SUBSTITUTE(B55,"{early_access_code}",Inputs!$B$25)</f>
+        <f>SUBSTITUTE(B55,"{launch_date}",Inputs!$B$64)</f>
         <v/>
       </c>
     </row>
     <row r="56" ht="32" customHeight="1">
       <c r="A56" s="4" t="inlineStr">
         <is>
+          <t>email · early access, draw · 3</t>
+        </is>
+      </c>
+      <c r="B56" s="8" t="inlineStr">
+        <is>
+          <t>Explore the artwork and place your order via the private link below. Use code {early_access_code} to unlock early access.</t>
+        </is>
+      </c>
+      <c r="C56" s="10">
+        <f>SUBSTITUTE(B56,"{early_access_code}",Inputs!$B$25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57" ht="32" customHeight="1">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
           <t>email · insiders · opener</t>
         </is>
       </c>
-      <c r="B56" s="8" t="inlineStr">
+      <c r="B57" s="8" t="inlineStr">
         <is>
           <t>I'm delighted to share our {ordinal} collaboration with {collab_with} – {work_intro}{support}.</t>
         </is>
       </c>
-      <c r="C56" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B56,"{collab_with}",Inputs!$B$5),"{work_intro}",Inputs!$B$53),"{support}",Inputs!$B$54),"{ordinal}",Inputs!$B$10)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="57" ht="64" customHeight="1">
-      <c r="A57" s="4" t="inlineStr">
+      <c r="C57" s="10">
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B57,"{collab_with}",Inputs!$B$5),"{work_intro}",Inputs!$B$53),"{support}",Inputs!$B$54),"{ordinal}",Inputs!$B$10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58" ht="64" customHeight="1">
+      <c r="A58" s="4" t="inlineStr">
         <is>
           <t>email · insiders · mechanics, draw</t>
         </is>
       </c>
-      <c r="B57" s="8" t="inlineStr">
+      <c r="B58" s="8" t="inlineStr">
         <is>
           <t>The edition will launch publicly on {launch_date} and will be allocated by a randomised draw. However, for the next 48 hours, I'm excited to offer you a first look, plus early access to a limited number of pre-orders.</t>
         </is>
       </c>
-      <c r="C57" s="10">
-        <f>SUBSTITUTE(B57,"{launch_date}",Inputs!$B$63)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="58" ht="48" customHeight="1">
-      <c r="A58" s="4" t="inlineStr">
+      <c r="C58" s="10">
+        <f>SUBSTITUTE(B58,"{launch_date}",Inputs!$B$64)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59" ht="48" customHeight="1">
+      <c r="A59" s="4" t="inlineStr">
         <is>
           <t>email · insiders · mechanics, timed</t>
         </is>
       </c>
-      <c r="B58" s="8" t="inlineStr">
+      <c r="B59" s="8" t="inlineStr">
         <is>
           <t>The edition launches tomorrow at {launch_time} and will be available to collect for {window} only. For the next 24 hours, I'm excited to offer you early access ahead of the public launch.</t>
         </is>
       </c>
-      <c r="C58" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(B58,"{window}",Inputs!$B$19),"{launch_time}",Inputs!$B$64)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="59" ht="32" customHeight="1">
-      <c r="A59" s="4" t="inlineStr">
+      <c r="C59" s="10">
+        <f>SUBSTITUTE(SUBSTITUTE(B59,"{window}",Inputs!$B$19),"{launch_time}",Inputs!$B$65)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60" ht="32" customHeight="1">
+      <c r="A60" s="4" t="inlineStr">
         <is>
           <t>email · insiders · code line, draw</t>
         </is>
       </c>
-      <c r="B59" s="8" t="inlineStr">
+      <c r="B60" s="8" t="inlineStr">
         <is>
           <t>Discover the artwork and place your order via the private link below. Use code {early_access_code} to unlock early access.</t>
         </is>
       </c>
-      <c r="C59" s="10">
-        <f>SUBSTITUTE(B59,"{early_access_code}",Inputs!$B$25)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="60" ht="16" customHeight="1">
-      <c r="A60" s="4" t="inlineStr">
+      <c r="C60" s="10">
+        <f>SUBSTITUTE(B60,"{early_access_code}",Inputs!$B$25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61" ht="16" customHeight="1">
+      <c r="A61" s="4" t="inlineStr">
         <is>
           <t>email · insiders · link line, timed</t>
         </is>
       </c>
-      <c r="B60" s="8" t="inlineStr">
+      <c r="B61" s="8" t="inlineStr">
         <is>
           <t>Discover the artwork and place your order via the private link below.</t>
         </is>
       </c>
-      <c r="C60" s="10">
-        <f>B60</f>
-        <v/>
-      </c>
-    </row>
-    <row r="61" ht="64" customHeight="1">
-      <c r="A61" s="4" t="inlineStr">
+      <c r="C61" s="10">
+        <f>B61</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62" ht="64" customHeight="1">
+      <c r="A62" s="4" t="inlineStr">
         <is>
           <t>email · insiders · sign-off</t>
         </is>
       </c>
-      <c r="B61" s="8" t="inlineStr">
+      <c r="B62" s="8" t="inlineStr">
         <is>
           <t>Best regards,
 {advisor}
 Art Advisor at Avant Arte</t>
         </is>
       </c>
-      <c r="C61" s="10">
-        <f>SUBSTITUTE(B61,"{advisor}",Inputs!$B$24)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="3" t="inlineStr">
+      <c r="C62" s="10">
+        <f>SUBSTITUTE(B62,"{advisor}",Inputs!$B$24)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
         <is>
           <t>EMAILS · the window (TL)</t>
         </is>
       </c>
     </row>
-    <row r="63" ht="32" customHeight="1">
-      <c r="A63" s="4" t="inlineStr">
+    <row r="64" ht="32" customHeight="1">
+      <c r="A64" s="4" t="inlineStr">
         <is>
           <t>email · live · opener</t>
         </is>
       </c>
-      <c r="B63" s="8" t="inlineStr">
+      <c r="B64" s="8" t="inlineStr">
         <is>
           <t>Our {ordinal} collaboration with {collab_with} is now available to collect for {window} only – {work_intro}{support}.</t>
         </is>
       </c>
-      <c r="C63" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B63,"{collab_with}",Inputs!$B$5),"{work_intro}",Inputs!$B$53),"{support}",Inputs!$B$54),"{ordinal}",Inputs!$B$10),"{window}",Inputs!$B$19)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="64" ht="48" customHeight="1">
-      <c r="A64" s="4" t="inlineStr">
+      <c r="C64" s="10">
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B64,"{collab_with}",Inputs!$B$5),"{work_intro}",Inputs!$B$53),"{support}",Inputs!$B$54),"{ordinal}",Inputs!$B$10),"{window}",Inputs!$B$19)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65" ht="48" customHeight="1">
+      <c r="A65" s="4" t="inlineStr">
         <is>
           <t>email · live · closing line</t>
         </is>
       </c>
-      <c r="B64" s="8" t="inlineStr">
+      <c r="B65" s="8" t="inlineStr">
         <is>
           <t>The opportunity to collect an edition ends at {close_time} on {close_weekday}, {close_date_dd}. Click the link below to add {add_what} to your collection.</t>
         </is>
       </c>
-      <c r="C64" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B64,"{close_time}",Inputs!$B$68),"{close_weekday}",Inputs!$B$69),"{close_date_dd}",Inputs!$B$70),"{add_what}",Inputs!$B$78)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="65" ht="16" customHeight="1">
-      <c r="A65" s="4" t="inlineStr">
-        <is>
-          <t>email · halfway · headline</t>
-        </is>
-      </c>
-      <c r="B65" s="8" t="inlineStr">
-        <is>
-          <t>24 hours down, 24 to go</t>
-        </is>
-      </c>
       <c r="C65" s="10">
-        <f>B65</f>
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B65,"{close_time}",Inputs!$B$69),"{close_weekday}",Inputs!$B$70),"{close_date_dd}",Inputs!$B$71),"{add_what}",Inputs!$B$79)</f>
         <v/>
       </c>
     </row>
     <row r="66" ht="16" customHeight="1">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>email · halfway · footer</t>
+          <t>email · halfway · headline</t>
         </is>
       </c>
       <c r="B66" s="8" t="inlineStr">
         <is>
-          <t>There's still time to add {a_unit} to your collection.</t>
+          <t>24 hours down, 24 to go</t>
         </is>
       </c>
       <c r="C66" s="10">
-        <f>SUBSTITUTE(B66,"{a_unit}",Inputs!$B$48)</f>
+        <f>B66</f>
         <v/>
       </c>
     </row>
     <row r="67" ht="16" customHeight="1">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>email · 5 days · headline</t>
+          <t>email · halfway · footer</t>
         </is>
       </c>
       <c r="B67" s="8" t="inlineStr">
         <is>
-          <t>2 days down, 5 days to go</t>
+          <t>There's still time to add {a_unit} to your collection.</t>
         </is>
       </c>
       <c r="C67" s="10">
-        <f>B67</f>
+        <f>SUBSTITUTE(B67,"{a_unit}",Inputs!$B$48)</f>
         <v/>
       </c>
     </row>
     <row r="68" ht="16" customHeight="1">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>email · 3 days · headline</t>
+          <t>email · 5 days · headline</t>
         </is>
       </c>
       <c r="B68" s="8" t="inlineStr">
         <is>
-          <t>Three days left to collect</t>
+          <t>2 days down, 5 days to go</t>
         </is>
       </c>
       <c r="C68" s="10">
@@ -2517,205 +2528,205 @@
         <v/>
       </c>
     </row>
-    <row r="69" ht="32" customHeight="1">
+    <row r="69" ht="16" customHeight="1">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>email · 3 days · 1</t>
+          <t>email · 3 days · headline</t>
         </is>
       </c>
       <c r="B69" s="8" t="inlineStr">
         <is>
-          <t>There are just three days left to collect {collect_phrase} by {artist}.</t>
+          <t>Three days left to collect</t>
         </is>
       </c>
       <c r="C69" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(B69,"{artist}",Inputs!$B$4),"{collect_phrase}",Inputs!$B$71)</f>
+        <f>B69</f>
         <v/>
       </c>
     </row>
     <row r="70" ht="32" customHeight="1">
       <c r="A70" s="4" t="inlineStr">
         <is>
+          <t>email · 3 days · 1</t>
+        </is>
+      </c>
+      <c r="B70" s="8" t="inlineStr">
+        <is>
+          <t>There are just three days left to collect {collect_phrase} by {artist}.</t>
+        </is>
+      </c>
+      <c r="C70" s="10">
+        <f>SUBSTITUTE(SUBSTITUTE(B70,"{artist}",Inputs!$B$4),"{collect_phrase}",Inputs!$B$72)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="71" ht="32" customHeight="1">
+      <c r="A71" s="4" t="inlineStr">
+        <is>
           <t>email · 3 days · 2</t>
         </is>
       </c>
-      <c r="B70" s="8" t="inlineStr">
+      <c r="B71" s="8" t="inlineStr">
         <is>
           <t>Click the link to collect before {close_time} on {close_weekday}, {close_date_dd}.</t>
         </is>
       </c>
-      <c r="C70" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B70,"{close_time}",Inputs!$B$68),"{close_weekday}",Inputs!$B$69),"{close_date_dd}",Inputs!$B$70)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="71" ht="16" customHeight="1">
-      <c r="A71" s="4" t="inlineStr">
+      <c r="C71" s="10">
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B71,"{close_time}",Inputs!$B$69),"{close_weekday}",Inputs!$B$70),"{close_date_dd}",Inputs!$B$71)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="72" ht="16" customHeight="1">
+      <c r="A72" s="4" t="inlineStr">
         <is>
           <t>email · days to go · footer</t>
         </is>
       </c>
-      <c r="B71" s="8" t="inlineStr">
+      <c r="B72" s="8" t="inlineStr">
         <is>
           <t>Add {a_unit} to your collection</t>
         </is>
       </c>
-      <c r="C71" s="10">
-        <f>SUBSTITUTE(B71,"{a_unit}",Inputs!$B$48)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="3" t="inlineStr">
+      <c r="C72" s="10">
+        <f>SUBSTITUTE(B72,"{a_unit}",Inputs!$B$48)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="inlineStr">
         <is>
           <t>EMAILS · last chance</t>
         </is>
       </c>
     </row>
-    <row r="73" ht="48" customHeight="1">
-      <c r="A73" s="4" t="inlineStr">
+    <row r="74" ht="48" customHeight="1">
+      <c r="A74" s="4" t="inlineStr">
         <is>
           <t>email · last chance, timed · 1</t>
         </is>
       </c>
-      <c r="B73" s="8" t="inlineStr">
+      <c r="B74" s="8" t="inlineStr">
         <is>
           <t>It's now or never for our {ordinal} collaboration with {collab_with} – {collect_phrase} will be available to order until {close_time} on {close_weekday}, {close_date_dd}.</t>
         </is>
       </c>
-      <c r="C73" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B73,"{collab_with}",Inputs!$B$5),"{collect_phrase}",Inputs!$B$71),"{ordinal}",Inputs!$B$10),"{close_time}",Inputs!$B$68),"{close_weekday}",Inputs!$B$69),"{close_date_dd}",Inputs!$B$70)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="74" ht="32" customHeight="1">
-      <c r="A74" s="4" t="inlineStr">
-        <is>
-          <t>email · last chance, timed · 2</t>
-        </is>
-      </c>
-      <c r="B74" s="8" t="inlineStr">
-        <is>
-          <t>After this time, the edition size{each_artwork} will be confirmed, and the {work_word} will no longer be available to purchase.</t>
-        </is>
-      </c>
       <c r="C74" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(B74,"{each_artwork}",Inputs!$B$76),"{work_word}",Inputs!$B$77)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B74,"{collab_with}",Inputs!$B$5),"{collect_phrase}",Inputs!$B$72),"{ordinal}",Inputs!$B$10),"{close_time}",Inputs!$B$69),"{close_weekday}",Inputs!$B$70),"{close_date_dd}",Inputs!$B$71)</f>
         <v/>
       </c>
     </row>
     <row r="75" ht="32" customHeight="1">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>email · last chance, draw · 1</t>
+          <t>email · last chance, timed · 2</t>
         </is>
       </c>
       <c r="B75" s="8" t="inlineStr">
         <is>
-          <t>This is your final opportunity to enter the draw for {work_email}, {collect_phrase} by {artist}.</t>
+          <t>After this time, the edition size{each_artwork} will be confirmed, and the {work_word} will no longer be available to purchase.</t>
         </is>
       </c>
       <c r="C75" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B75,"{artist}",Inputs!$B$4),"{work_email}",Inputs!$B$51),"{collect_phrase}",Inputs!$B$71)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(B75,"{each_artwork}",Inputs!$B$77),"{work_word}",Inputs!$B$78)</f>
         <v/>
       </c>
     </row>
     <row r="76" ht="32" customHeight="1">
       <c r="A76" s="4" t="inlineStr">
         <is>
+          <t>email · last chance, draw · 1</t>
+        </is>
+      </c>
+      <c r="B76" s="8" t="inlineStr">
+        <is>
+          <t>This is your final opportunity to enter the draw for {work_email}, {collect_phrase} by {artist}.</t>
+        </is>
+      </c>
+      <c r="C76" s="10">
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B76,"{artist}",Inputs!$B$4),"{work_email}",Inputs!$B$51),"{collect_phrase}",Inputs!$B$72)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="77" ht="32" customHeight="1">
+      <c r="A77" s="4" t="inlineStr">
+        <is>
           <t>email · last chance, draw · 2</t>
         </is>
       </c>
-      <c r="B76" s="8" t="inlineStr">
+      <c r="B77" s="8" t="inlineStr">
         <is>
           <t>For a chance to collect, click the link below to enter the draw. The draw closes at {close_time} on {close_weekday}, {close_date_dd}.</t>
         </is>
       </c>
-      <c r="C76" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B76,"{close_time}",Inputs!$B$68),"{close_weekday}",Inputs!$B$69),"{close_date_dd}",Inputs!$B$70)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="3" t="inlineStr">
+      <c r="C77" s="10">
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B77,"{close_time}",Inputs!$B$69),"{close_weekday}",Inputs!$B$70),"{close_date_dd}",Inputs!$B$71)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="3" t="inlineStr">
         <is>
           <t>EMAILS · surveys (LE)</t>
         </is>
       </c>
     </row>
-    <row r="78" ht="16" customHeight="1">
-      <c r="A78" s="4" t="inlineStr">
+    <row r="79" ht="16" customHeight="1">
+      <c r="A79" s="4" t="inlineStr">
         <is>
           <t>email · first-time survey · subject</t>
         </is>
       </c>
-      <c r="B78" s="8" t="inlineStr">
+      <c r="B79" s="8" t="inlineStr">
         <is>
           <t>Congratulations on your first Avant Arte edition</t>
         </is>
       </c>
-      <c r="C78" s="10">
-        <f>B78</f>
-        <v/>
-      </c>
-    </row>
-    <row r="79" ht="32" customHeight="1">
-      <c r="A79" s="4" t="inlineStr">
+      <c r="C79" s="10">
+        <f>B79</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80" ht="32" customHeight="1">
+      <c r="A80" s="4" t="inlineStr">
         <is>
           <t>email · first-time survey · 1</t>
         </is>
       </c>
-      <c r="B79" s="8" t="inlineStr">
+      <c r="B80" s="8" t="inlineStr">
         <is>
           <t>Thank you for adding our collaboration with {collab_with} to your collection. Great choice!</t>
         </is>
       </c>
-      <c r="C79" s="10">
-        <f>SUBSTITUTE(B79,"{collab_with}",Inputs!$B$5)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="80" ht="48" customHeight="1">
-      <c r="A80" s="4" t="inlineStr">
+      <c r="C80" s="10">
+        <f>SUBSTITUTE(B80,"{collab_with}",Inputs!$B$5)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="81" ht="48" customHeight="1">
+      <c r="A81" s="4" t="inlineStr">
         <is>
           <t>email · first-time survey · 2</t>
         </is>
       </c>
-      <c r="B80" s="8" t="inlineStr">
+      <c r="B81" s="8" t="inlineStr">
         <is>
           <t>I'm {advisor}, an art advisor at Avant Arte. I'm here to connect collectors with artists by making suggestions, answering questions and offering early access to our collaborations.</t>
         </is>
       </c>
-      <c r="C80" s="10">
-        <f>SUBSTITUTE(B80,"{advisor}",Inputs!$B$24)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="81" ht="32" customHeight="1">
-      <c r="A81" s="4" t="inlineStr">
+      <c r="C81" s="10">
+        <f>SUBSTITUTE(B81,"{advisor}",Inputs!$B$24)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="82" ht="32" customHeight="1">
+      <c r="A82" s="4" t="inlineStr">
         <is>
           <t>email · first-time survey · 3</t>
         </is>
       </c>
-      <c r="B81" s="8" t="inlineStr">
+      <c r="B82" s="8" t="inlineStr">
         <is>
           <t>If you have two minutes to complete a short survey about your collecting journey to date, your responses will help guide my recommendations.</t>
-        </is>
-      </c>
-      <c r="C81" s="10">
-        <f>B81</f>
-        <v/>
-      </c>
-    </row>
-    <row r="82" ht="16" customHeight="1">
-      <c r="A82" s="4" t="inlineStr">
-        <is>
-          <t>email · first-time survey · 4</t>
-        </is>
-      </c>
-      <c r="B82" s="8" t="inlineStr">
-        <is>
-          <t>Any questions? Reply to this email.</t>
         </is>
       </c>
       <c r="C82" s="10">
@@ -2723,47 +2734,47 @@
         <v/>
       </c>
     </row>
-    <row r="83" ht="48" customHeight="1">
+    <row r="83" ht="16" customHeight="1">
       <c r="A83" s="4" t="inlineStr">
         <is>
+          <t>email · first-time survey · 4</t>
+        </is>
+      </c>
+      <c r="B83" s="8" t="inlineStr">
+        <is>
+          <t>Any questions? Reply to this email.</t>
+        </is>
+      </c>
+      <c r="C83" s="10">
+        <f>B83</f>
+        <v/>
+      </c>
+    </row>
+    <row r="84" ht="48" customHeight="1">
+      <c r="A84" s="4" t="inlineStr">
+        <is>
           <t>email · non-purchaser survey · 1</t>
         </is>
       </c>
-      <c r="B83" s="8" t="inlineStr">
+      <c r="B84" s="8" t="inlineStr">
         <is>
           <t>As someone who registered for updates but ultimately decided not to enter the draw for our collaboration with {collab_with}, we'd love your feedback.</t>
         </is>
       </c>
-      <c r="C83" s="10">
-        <f>SUBSTITUTE(B83,"{collab_with}",Inputs!$B$5)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="84" ht="32" customHeight="1">
-      <c r="A84" s="4" t="inlineStr">
+      <c r="C84" s="10">
+        <f>SUBSTITUTE(B84,"{collab_with}",Inputs!$B$5)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="85" ht="32" customHeight="1">
+      <c r="A85" s="4" t="inlineStr">
         <is>
           <t>email · non-purchaser survey · 2</t>
         </is>
       </c>
-      <c r="B84" s="8" t="inlineStr">
+      <c r="B85" s="8" t="inlineStr">
         <is>
           <t>This two-minute survey will guide our future collaborations and help us recommend the right artists and editions for your collection.</t>
-        </is>
-      </c>
-      <c r="C84" s="10">
-        <f>B84</f>
-        <v/>
-      </c>
-    </row>
-    <row r="85" ht="48" customHeight="1">
-      <c r="A85" s="4" t="inlineStr">
-        <is>
-          <t>email · non-purchaser survey · 3</t>
-        </is>
-      </c>
-      <c r="B85" s="8" t="inlineStr">
-        <is>
-          <t>As a thank you for taking part in the survey and helping us improve the collector experience, you'll be entered into a draw to win a €500 Avant Arte gift card.</t>
         </is>
       </c>
       <c r="C85" s="10">
@@ -2771,15 +2782,15 @@
         <v/>
       </c>
     </row>
-    <row r="86" ht="16" customHeight="1">
+    <row r="86" ht="48" customHeight="1">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>email · non-purchaser survey · terms</t>
+          <t>email · non-purchaser survey · 3</t>
         </is>
       </c>
       <c r="B86" s="8" t="inlineStr">
         <is>
-          <t>You can read the terms here.</t>
+          <t>As a thank you for taking part in the survey and helping us improve the collector experience, you'll be entered into a draw to win a €500 Avant Arte gift card.</t>
         </is>
       </c>
       <c r="C86" s="10">
@@ -2790,12 +2801,12 @@
     <row r="87" ht="16" customHeight="1">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>email · non-purchaser survey · footer</t>
+          <t>email · non-purchaser survey · terms</t>
         </is>
       </c>
       <c r="B87" s="8" t="inlineStr">
         <is>
-          <t>What can we do better?</t>
+          <t>You can read the terms here.</t>
         </is>
       </c>
       <c r="C87" s="10">
@@ -2803,58 +2814,74 @@
         <v/>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="3" t="inlineStr">
+    <row r="88" ht="16" customHeight="1">
+      <c r="A88" s="4" t="inlineStr">
+        <is>
+          <t>email · non-purchaser survey · footer</t>
+        </is>
+      </c>
+      <c r="B88" s="8" t="inlineStr">
+        <is>
+          <t>What can we do better?</t>
+        </is>
+      </c>
+      <c r="C88" s="10">
+        <f>B88</f>
+        <v/>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="3" t="inlineStr">
         <is>
           <t>EMAILS · monthly preview</t>
         </is>
       </c>
     </row>
-    <row r="89" ht="16" customHeight="1">
-      <c r="A89" s="4" t="inlineStr">
+    <row r="90" ht="16" customHeight="1">
+      <c r="A90" s="4" t="inlineStr">
         <is>
           <t>email · monthly preview · opener</t>
         </is>
       </c>
-      <c r="B89" s="8" t="inlineStr">
+      <c r="B90" s="8" t="inlineStr">
         <is>
           <t>From {collab_with} comes {work_intro}{support}.</t>
         </is>
       </c>
-      <c r="C89" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B89,"{collab_with}",Inputs!$B$5),"{work_intro}",Inputs!$B$53),"{support}",Inputs!$B$54)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="90" ht="32" customHeight="1">
-      <c r="A90" s="4" t="inlineStr">
-        <is>
-          <t>email · monthly preview · when, draw</t>
-        </is>
-      </c>
-      <c r="B90" s="8" t="inlineStr">
-        <is>
-          <t>The edition will be allocated by a randomised draw, which closes at {close_time} on {close_date}.</t>
-        </is>
-      </c>
       <c r="C90" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(B90,"{close_date}",Inputs!$B$67),"{close_time}",Inputs!$B$68)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B90,"{collab_with}",Inputs!$B$5),"{work_intro}",Inputs!$B$53),"{support}",Inputs!$B$54)</f>
         <v/>
       </c>
     </row>
     <row r="91" ht="32" customHeight="1">
       <c r="A91" s="4" t="inlineStr">
         <is>
+          <t>email · monthly preview · when, draw</t>
+        </is>
+      </c>
+      <c r="B91" s="8" t="inlineStr">
+        <is>
+          <t>The edition will be allocated by a randomised draw, which closes at {close_time} on {close_date}.</t>
+        </is>
+      </c>
+      <c r="C91" s="10">
+        <f>SUBSTITUTE(SUBSTITUTE(B91,"{close_date}",Inputs!$B$68),"{close_time}",Inputs!$B$69)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="92" ht="32" customHeight="1">
+      <c r="A92" s="4" t="inlineStr">
+        <is>
           <t>email · monthly preview · when, timed</t>
         </is>
       </c>
-      <c r="B91" s="8" t="inlineStr">
+      <c r="B92" s="8" t="inlineStr">
         <is>
           <t>The edition will be available to collect for {window} only, from {launch_time} on {launch_weekday}, {launch_date_dd}.</t>
         </is>
       </c>
-      <c r="C91" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B91,"{window}",Inputs!$B$19),"{launch_time}",Inputs!$B$64),"{launch_weekday}",Inputs!$B$65),"{launch_date_dd}",Inputs!$B$66)</f>
+      <c r="C92" s="10">
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B92,"{window}",Inputs!$B$19),"{launch_time}",Inputs!$B$65),"{launch_weekday}",Inputs!$B$66),"{launch_date_dd}",Inputs!$B$67)</f>
         <v/>
       </c>
     </row>
@@ -2980,7 +3007,7 @@
         <v/>
       </c>
       <c r="F4" s="11">
-        <f>Inputs!$B$56</f>
+        <f>Inputs!$B$57</f>
         <v/>
       </c>
       <c r="G4" s="11">
@@ -3032,7 +3059,7 @@
         <v/>
       </c>
       <c r="G5" s="11">
-        <f>Lines!$C$15&amp;IF(Inputs!$B$57,"",IF(Inputs!$B$55="",""," "&amp;Lines!$C$16))</f>
+        <f>Lines!$C$15&amp;IF(Inputs!$B$58,"",IF(Inputs!$B$56="",""," "&amp;Lines!$C$16))</f>
         <v/>
       </c>
       <c r="H5" s="11">
@@ -3076,11 +3103,11 @@
         <v/>
       </c>
       <c r="F6" s="11">
-        <f>Inputs!$B$62</f>
+        <f>Inputs!$B$63</f>
         <v/>
       </c>
       <c r="G6" s="11">
-        <f>Lines!$C$15&amp;IF(Inputs!$B$55="",""," "&amp;Lines!$C$16)</f>
+        <f>Lines!$C$15&amp;IF(Inputs!$B$56="",""," "&amp;Lines!$C$16)</f>
         <v/>
       </c>
       <c r="H6" s="11">
@@ -3128,7 +3155,7 @@
         <v/>
       </c>
       <c r="G7" s="11">
-        <f>IF(Inputs!$B$42="","",Lines!$C$15&amp;IF(Inputs!$B$55="",""," "&amp;Lines!$C$16))</f>
+        <f>IF(Inputs!$B$42="","",Lines!$C$15&amp;IF(Inputs!$B$56="",""," "&amp;Lines!$C$16))</f>
         <v/>
       </c>
       <c r="H7" s="11">
@@ -3176,7 +3203,7 @@
         <v/>
       </c>
       <c r="G8" s="11">
-        <f>IF(Inputs!$B$18="draw","",Lines!$C$15&amp;IF(Inputs!$B$55="",""," "&amp;Lines!$C$16))</f>
+        <f>IF(Inputs!$B$18="draw","",Lines!$C$15&amp;IF(Inputs!$B$56="",""," "&amp;Lines!$C$16))</f>
         <v/>
       </c>
       <c r="H8" s="11">
@@ -3224,7 +3251,7 @@
         <v/>
       </c>
       <c r="G9" s="11">
-        <f>IF(Inputs!$B$18="draw","",Lines!$C$15&amp;IF(Inputs!$B$55="",""," "&amp;Lines!$C$16))</f>
+        <f>IF(Inputs!$B$18="draw","",Lines!$C$15&amp;IF(Inputs!$B$56="",""," "&amp;Lines!$C$16))</f>
         <v/>
       </c>
       <c r="H9" s="11">
@@ -3272,7 +3299,7 @@
         <v/>
       </c>
       <c r="G10" s="11">
-        <f>Lines!$C$15&amp;IF(Inputs!$B$55="",""," "&amp;Lines!$C$16)</f>
+        <f>Lines!$C$15&amp;IF(Inputs!$B$56="",""," "&amp;Lines!$C$16)</f>
         <v/>
       </c>
       <c r="H10" s="11">
@@ -3327,7 +3354,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>The post's status line with the X handle, the hook on the announcement only, the beneficiary named once, and an action line that ends with the link. No features line, no hashtag, no bio.</t>
+          <t>The post's status line with the X handle, the hook on the announcement only, the beneficiary named once, and an action line that ends with the link. No features line, no hashtag, no bio. The announcement runs over X's limit until the tool cuts its hook.</t>
         </is>
       </c>
     </row>
@@ -3428,11 +3455,11 @@
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>status · hook · beneficiary · action</t>
+          <t>status, with the beneficiary · hook · action</t>
         </is>
       </c>
       <c r="D5" s="11">
-        <f>SUBSTITUTE(IF(Inputs!$B$14&lt;&gt;"",Lines!$C$7,Lines!$C$6),Inputs!$B$45,Inputs!$B$46)</f>
+        <f>IF(Inputs!$B$14&lt;&gt;"",Lines!$C$27,Lines!$C$26)</f>
         <v/>
       </c>
       <c r="E5" s="11">
@@ -3440,15 +3467,15 @@
         <v/>
       </c>
       <c r="F5" s="11">
-        <f>IF(OR(Inputs!$B$22="",Inputs!$B$57),"",Lines!$C$26)</f>
+        <f>""</f>
         <v/>
       </c>
       <c r="G5" s="11">
-        <f>IF(Inputs!$B$18="draw",Lines!$C$28,Lines!$C$27)</f>
+        <f>IF(Inputs!$B$18="draw",Lines!$C$29,Lines!$C$28)</f>
         <v/>
       </c>
       <c r="H5" s="11">
-        <f>D5&amp;IF(E5="","",CHAR(10)&amp;CHAR(10)&amp;E5)&amp;IF(F5="","",CHAR(10)&amp;CHAR(10)&amp;F5)&amp;IF(G5="","",CHAR(10)&amp;CHAR(10)&amp;G5)</f>
+        <f>D5&amp;IF(E5="","",CHAR(10)&amp;CHAR(10)&amp;E5)&amp;IF(G5="","",CHAR(10)&amp;CHAR(10)&amp;G5)</f>
         <v/>
       </c>
       <c r="I5" s="11">
@@ -3483,7 +3510,7 @@
         <v/>
       </c>
       <c r="G6" s="11">
-        <f>IF(Inputs!$B$18="draw","",IF(Inputs!$B$18="draw",Lines!$C$28,Lines!$C$29))</f>
+        <f>IF(Inputs!$B$18="draw","",IF(Inputs!$B$18="draw",Lines!$C$29,Lines!$C$30))</f>
         <v/>
       </c>
       <c r="H6" s="11">
@@ -3522,7 +3549,7 @@
         <v/>
       </c>
       <c r="G7" s="11">
-        <f>IF(Inputs!$B$18="draw","",IF(Inputs!$B$18="draw",Lines!$C$28,Lines!$C$29))</f>
+        <f>IF(Inputs!$B$18="draw","",IF(Inputs!$B$18="draw",Lines!$C$29,Lines!$C$30))</f>
         <v/>
       </c>
       <c r="H7" s="11">
@@ -3561,7 +3588,7 @@
         <v/>
       </c>
       <c r="G8" s="11">
-        <f>IF(Inputs!$B$18="draw",Lines!$C$28,Lines!$C$29)</f>
+        <f>IF(Inputs!$B$18="draw",Lines!$C$29,Lines!$C$30)</f>
         <v/>
       </c>
       <c r="H8" s="11">
@@ -3714,15 +3741,15 @@
         <v/>
       </c>
       <c r="E4" s="11">
-        <f>IF($D4&lt;&gt;"yes","",Lines!$C$39)</f>
+        <f>IF($D4&lt;&gt;"yes","",Lines!$C$40)</f>
         <v/>
       </c>
       <c r="F4" s="11">
-        <f>IF($D4&lt;&gt;"yes","",IF(Inputs!$B$18="draw","Enter the draw for a chance to collect. Closes "&amp;Inputs!$B$67&amp;".","Launching "&amp;Inputs!$B$63&amp;". Register for updates."))</f>
+        <f>IF($D4&lt;&gt;"yes","",IF(Inputs!$B$18="draw","Enter the draw for a chance to collect. Closes "&amp;Inputs!$B$68&amp;".","Launching "&amp;Inputs!$B$64&amp;". Register for updates."))</f>
         <v/>
       </c>
       <c r="G4" s="11">
-        <f>IF($D4&lt;&gt;"yes","",IF(Inputs!$B$18="draw","Enter the draw","Launching "&amp;Inputs!$B$63))</f>
+        <f>IF($D4&lt;&gt;"yes","",IF(Inputs!$B$18="draw","Enter the draw","Launching "&amp;Inputs!$B$64))</f>
         <v/>
       </c>
       <c r="H4" s="11">
@@ -3730,7 +3757,7 @@
         <v/>
       </c>
       <c r="I4" s="11">
-        <f>IF($D4&lt;&gt;"yes","",(Lines!$C$40&amp;IF(Inputs!$B$36="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$36)&amp;IF(Inputs!$B$61="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$61)&amp;IF(Inputs!$B$59="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$59)&amp;IF(IF(Inputs!$B$18="draw",Lines!$C$33,(Lines!$C$41&amp;IF(Lines!$C$42="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$42)))="","",CHAR(10)&amp;CHAR(10)&amp;IF(Inputs!$B$18="draw",Lines!$C$33,(Lines!$C$41&amp;IF(Lines!$C$42="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$42))))))</f>
+        <f>IF($D4&lt;&gt;"yes","",(Lines!$C$41&amp;IF(Inputs!$B$36="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$36)&amp;IF(Inputs!$B$62="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$62)&amp;IF(Inputs!$B$60="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$60)&amp;IF(IF(Inputs!$B$18="draw",Lines!$C$34,(Lines!$C$42&amp;IF(Lines!$C$43="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$43)))="","",CHAR(10)&amp;CHAR(10)&amp;IF(Inputs!$B$18="draw",Lines!$C$34,(Lines!$C$42&amp;IF(Lines!$C$43="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$43))))))</f>
         <v/>
       </c>
       <c r="J4" s="11">
@@ -3738,15 +3765,15 @@
         <v/>
       </c>
       <c r="K4" s="11">
-        <f>IF($D4&lt;&gt;"yes","",Inputs!$B$74)</f>
+        <f>IF($D4&lt;&gt;"yes","",Inputs!$B$75)</f>
         <v/>
       </c>
       <c r="L4" s="11">
-        <f>IF($D4&lt;&gt;"yes","",Inputs!$B$75)</f>
+        <f>IF($D4&lt;&gt;"yes","",Inputs!$B$76)</f>
         <v/>
       </c>
       <c r="M4" s="11">
-        <f>IF($D4&lt;&gt;"yes","",IF(Inputs!$B$18="draw","Collect "&amp;Inputs!$B$71,"Launching "&amp;Inputs!$B$63))</f>
+        <f>IF($D4&lt;&gt;"yes","",IF(Inputs!$B$18="draw","Collect "&amp;Inputs!$B$72,"Launching "&amp;Inputs!$B$64))</f>
         <v/>
       </c>
       <c r="N4" s="11">
@@ -3793,7 +3820,7 @@
         <v/>
       </c>
       <c r="I5" s="11">
-        <f>IF($D5&lt;&gt;"yes","",(Lines!$C$44&amp;IF(Lines!$C$45="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$45)&amp;IF(Lines!$C$46="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$46)&amp;IF(Lines!$C$47="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$47)))</f>
+        <f>IF($D5&lt;&gt;"yes","",(Lines!$C$45&amp;IF(Lines!$C$46="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$46)&amp;IF(Lines!$C$47="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$47)&amp;IF(Lines!$C$48="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$48)))</f>
         <v/>
       </c>
       <c r="J5" s="11">
@@ -3856,7 +3883,7 @@
         <v/>
       </c>
       <c r="I6" s="11">
-        <f>IF($D6&lt;&gt;"yes","",(Lines!$C$31&amp;IF(Lines!$C$49="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$49)&amp;IF(Inputs!$B$36="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$36)&amp;IF(Inputs!$B$60="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$60)&amp;IF(Lines!$C$50="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$50)&amp;IF(IF(Inputs!$B$26="","",Lines!$C$36)="","",CHAR(10)&amp;CHAR(10)&amp;IF(Inputs!$B$26="","",Lines!$C$36))&amp;IF(Lines!$C$52="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$52)))</f>
+        <f>IF($D6&lt;&gt;"yes","",(Lines!$C$32&amp;IF(Lines!$C$50="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$50)&amp;IF(Inputs!$B$36="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$36)&amp;IF(Inputs!$B$61="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$61)&amp;IF(Lines!$C$51="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$51)&amp;IF(IF(Inputs!$B$26="","",Lines!$C$37)="","",CHAR(10)&amp;CHAR(10)&amp;IF(Inputs!$B$26="","",Lines!$C$37))&amp;IF(Lines!$C$53="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$53)))</f>
         <v/>
       </c>
       <c r="J6" s="11">
@@ -3919,7 +3946,7 @@
         <v/>
       </c>
       <c r="I7" s="11">
-        <f>IF($D7&lt;&gt;"yes","",(Lines!$C$31&amp;IF(Lines!$C$49="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$49)&amp;IF(Inputs!$B$36="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$36)&amp;IF(Inputs!$B$60="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$60)&amp;IF(Lines!$C$51="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$51)&amp;IF(Lines!$C$52="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$52)&amp;IF(Lines!$C$34="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$34)&amp;IF(Lines!$C$32="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$32)))</f>
+        <f>IF($D7&lt;&gt;"yes","",(Lines!$C$32&amp;IF(Lines!$C$50="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$50)&amp;IF(Inputs!$B$36="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$36)&amp;IF(Inputs!$B$61="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$61)&amp;IF(Lines!$C$52="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$52)&amp;IF(Lines!$C$53="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$53)&amp;IF(Lines!$C$35="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$35)&amp;IF(Lines!$C$33="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$33)))</f>
         <v/>
       </c>
       <c r="J7" s="11">
@@ -3927,7 +3954,7 @@
         <v/>
       </c>
       <c r="K7" s="11">
-        <f>IF($D7&lt;&gt;"yes","",Inputs!$B$74)</f>
+        <f>IF($D7&lt;&gt;"yes","",Inputs!$B$75)</f>
         <v/>
       </c>
       <c r="L7" s="11">
@@ -3982,7 +4009,7 @@
         <v/>
       </c>
       <c r="I8" s="11">
-        <f>IF($D8&lt;&gt;"yes","",(Lines!$C$31&amp;IF(Lines!$C$56="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$56)&amp;IF(Inputs!$B$36="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$36)&amp;IF(IF(Inputs!$B$18="draw",Lines!$C$57,Lines!$C$58)="","",CHAR(10)&amp;CHAR(10)&amp;IF(Inputs!$B$18="draw",Lines!$C$57,Lines!$C$58))&amp;IF(IF(Inputs!$B$18="draw",Lines!$C$59,Lines!$C$60)="","",CHAR(10)&amp;CHAR(10)&amp;IF(Inputs!$B$18="draw",Lines!$C$59,Lines!$C$60))&amp;IF(Lines!$C$32="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$32)&amp;IF(Lines!$C$61="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$61)))</f>
+        <f>IF($D8&lt;&gt;"yes","",(Lines!$C$32&amp;IF(Lines!$C$57="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$57)&amp;IF(Inputs!$B$36="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$36)&amp;IF(IF(Inputs!$B$18="draw",Lines!$C$58,Lines!$C$59)="","",CHAR(10)&amp;CHAR(10)&amp;IF(Inputs!$B$18="draw",Lines!$C$58,Lines!$C$59))&amp;IF(IF(Inputs!$B$18="draw",Lines!$C$60,Lines!$C$61)="","",CHAR(10)&amp;CHAR(10)&amp;IF(Inputs!$B$18="draw",Lines!$C$60,Lines!$C$61))&amp;IF(Lines!$C$33="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$33)&amp;IF(Lines!$C$62="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$62)))</f>
         <v/>
       </c>
       <c r="J8" s="11">
@@ -3990,7 +4017,7 @@
         <v/>
       </c>
       <c r="K8" s="11">
-        <f>IF($D8&lt;&gt;"yes","",Inputs!$B$74)</f>
+        <f>IF($D8&lt;&gt;"yes","",Inputs!$B$75)</f>
         <v/>
       </c>
       <c r="L8" s="11">
@@ -4045,7 +4072,7 @@
         <v/>
       </c>
       <c r="I9" s="11">
-        <f>IF($D9&lt;&gt;"yes","",(Lines!$C$31&amp;IF(Lines!$C$53="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$53)&amp;IF(Inputs!$B$36="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$36)&amp;IF(Lines!$C$54="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$54)&amp;IF(Lines!$C$55="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$55)&amp;IF(Lines!$C$34="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$34)&amp;IF(Lines!$C$32="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$32)))</f>
+        <f>IF($D9&lt;&gt;"yes","",(Lines!$C$32&amp;IF(Lines!$C$54="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$54)&amp;IF(Inputs!$B$36="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$36)&amp;IF(Lines!$C$55="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$55)&amp;IF(Lines!$C$56="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$56)&amp;IF(Lines!$C$35="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$35)&amp;IF(Lines!$C$33="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$33)))</f>
         <v/>
       </c>
       <c r="J9" s="11">
@@ -4053,7 +4080,7 @@
         <v/>
       </c>
       <c r="K9" s="11">
-        <f>IF($D9&lt;&gt;"yes","",Inputs!$B$74)</f>
+        <f>IF($D9&lt;&gt;"yes","",Inputs!$B$75)</f>
         <v/>
       </c>
       <c r="L9" s="11">
@@ -4096,19 +4123,19 @@
         <v/>
       </c>
       <c r="F10" s="11">
-        <f>IF($D10&lt;&gt;"yes","",Inputs!$B$73&amp;", starting now.")</f>
+        <f>IF($D10&lt;&gt;"yes","",Inputs!$B$74&amp;", starting now.")</f>
         <v/>
       </c>
       <c r="G10" s="11">
-        <f>IF($D10&lt;&gt;"yes","",Lines!$C$35)</f>
+        <f>IF($D10&lt;&gt;"yes","",Lines!$C$36)</f>
         <v/>
       </c>
       <c r="H10" s="11">
-        <f>IF($D10&lt;&gt;"yes","",Inputs!$B$73&amp;", starting now")</f>
+        <f>IF($D10&lt;&gt;"yes","",Inputs!$B$74&amp;", starting now")</f>
         <v/>
       </c>
       <c r="I10" s="11">
-        <f>IF($D10&lt;&gt;"yes","",(Lines!$C$63&amp;IF(Inputs!$B$36="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$36)&amp;IF(Inputs!$B$61="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$61)&amp;IF(Inputs!$B$60="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$60)&amp;IF(Lines!$C$64="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$64)&amp;IF(IF(Inputs!$B$26="","",Lines!$C$36)="","",CHAR(10)&amp;CHAR(10)&amp;IF(Inputs!$B$26="","",Lines!$C$36))))</f>
+        <f>IF($D10&lt;&gt;"yes","",(Lines!$C$64&amp;IF(Inputs!$B$36="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$36)&amp;IF(Inputs!$B$62="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$62)&amp;IF(Inputs!$B$61="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$61)&amp;IF(Lines!$C$65="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$65)&amp;IF(IF(Inputs!$B$26="","",Lines!$C$37)="","",CHAR(10)&amp;CHAR(10)&amp;IF(Inputs!$B$26="","",Lines!$C$37))))</f>
         <v/>
       </c>
       <c r="J10" s="11">
@@ -4116,15 +4143,15 @@
         <v/>
       </c>
       <c r="K10" s="11">
-        <f>IF($D10&lt;&gt;"yes","",Inputs!$B$74)</f>
+        <f>IF($D10&lt;&gt;"yes","",Inputs!$B$75)</f>
         <v/>
       </c>
       <c r="L10" s="11">
-        <f>IF($D10&lt;&gt;"yes","",Inputs!$B$75)</f>
+        <f>IF($D10&lt;&gt;"yes","",Inputs!$B$76)</f>
         <v/>
       </c>
       <c r="M10" s="11">
-        <f>IF($D10&lt;&gt;"yes","","Collect "&amp;Inputs!$B$71)</f>
+        <f>IF($D10&lt;&gt;"yes","","Collect "&amp;Inputs!$B$72)</f>
         <v/>
       </c>
       <c r="N10" s="11">
@@ -4163,11 +4190,11 @@
         <v/>
       </c>
       <c r="G11" s="11">
-        <f>IF($D11&lt;&gt;"yes","",Lines!$C$35)</f>
+        <f>IF($D11&lt;&gt;"yes","",Lines!$C$36)</f>
         <v/>
       </c>
       <c r="H11" s="11">
-        <f>IF($D11&lt;&gt;"yes","",Lines!$C$65)</f>
+        <f>IF($D11&lt;&gt;"yes","",Lines!$C$66)</f>
         <v/>
       </c>
       <c r="I11" s="11">
@@ -4187,7 +4214,7 @@
         <v/>
       </c>
       <c r="M11" s="11">
-        <f>IF($D11&lt;&gt;"yes","",Lines!$C$66)</f>
+        <f>IF($D11&lt;&gt;"yes","",Lines!$C$67)</f>
         <v/>
       </c>
       <c r="N11" s="11">
@@ -4226,11 +4253,11 @@
         <v/>
       </c>
       <c r="G12" s="11">
-        <f>IF($D12&lt;&gt;"yes","",Lines!$C$35)</f>
+        <f>IF($D12&lt;&gt;"yes","",Lines!$C$36)</f>
         <v/>
       </c>
       <c r="H12" s="11">
-        <f>IF($D12&lt;&gt;"yes","",Lines!$C$67)</f>
+        <f>IF($D12&lt;&gt;"yes","",Lines!$C$68)</f>
         <v/>
       </c>
       <c r="I12" s="11">
@@ -4250,7 +4277,7 @@
         <v/>
       </c>
       <c r="M12" s="11">
-        <f>IF($D12&lt;&gt;"yes","",Lines!$C$71)</f>
+        <f>IF($D12&lt;&gt;"yes","",Lines!$C$72)</f>
         <v/>
       </c>
       <c r="N12" s="11">
@@ -4293,11 +4320,11 @@
         <v/>
       </c>
       <c r="H13" s="11">
-        <f>IF($D13&lt;&gt;"yes","",Lines!$C$68)</f>
+        <f>IF($D13&lt;&gt;"yes","",Lines!$C$69)</f>
         <v/>
       </c>
       <c r="I13" s="11">
-        <f>IF($D13&lt;&gt;"yes","",(Lines!$C$69&amp;IF(Inputs!$B$36="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$36)&amp;IF(Lines!$C$70="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$70)&amp;IF(IF(Inputs!$B$26="","",Lines!$C$37)="","",CHAR(10)&amp;CHAR(10)&amp;IF(Inputs!$B$26="","",Lines!$C$37))))</f>
+        <f>IF($D13&lt;&gt;"yes","",(Lines!$C$70&amp;IF(Inputs!$B$36="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$36)&amp;IF(Lines!$C$71="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$71)&amp;IF(IF(Inputs!$B$26="","",Lines!$C$38)="","",CHAR(10)&amp;CHAR(10)&amp;IF(Inputs!$B$26="","",Lines!$C$38))))</f>
         <v/>
       </c>
       <c r="J13" s="11">
@@ -4305,7 +4332,7 @@
         <v/>
       </c>
       <c r="K13" s="11">
-        <f>IF($D13&lt;&gt;"yes","",Inputs!$B$74)</f>
+        <f>IF($D13&lt;&gt;"yes","",Inputs!$B$75)</f>
         <v/>
       </c>
       <c r="L13" s="11">
@@ -4313,7 +4340,7 @@
         <v/>
       </c>
       <c r="M13" s="11">
-        <f>IF($D13&lt;&gt;"yes","",Lines!$C$71)</f>
+        <f>IF($D13&lt;&gt;"yes","",Lines!$C$72)</f>
         <v/>
       </c>
       <c r="N13" s="11">
@@ -4348,7 +4375,7 @@
         <v/>
       </c>
       <c r="F14" s="11">
-        <f>IF($D14&lt;&gt;"yes","",IF(Inputs!$B$18="draw","The draw closes at "&amp;Inputs!$B$68&amp;" on "&amp;Inputs!$B$67&amp;".","Time is almost up."))</f>
+        <f>IF($D14&lt;&gt;"yes","",IF(Inputs!$B$18="draw","The draw closes at "&amp;Inputs!$B$69&amp;" on "&amp;Inputs!$B$68&amp;".","Time is almost up."))</f>
         <v/>
       </c>
       <c r="G14" s="11">
@@ -4360,7 +4387,7 @@
         <v/>
       </c>
       <c r="I14" s="11">
-        <f>IF($D14&lt;&gt;"yes","",IF(Inputs!$B$18="draw",(Lines!$C$75&amp;IF(Inputs!$B$36="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$36)&amp;IF(Lines!$C$76="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$76)),(Lines!$C$73&amp;IF(Lines!$C$74="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$74)&amp;IF(IF(Inputs!$B$26="","",Lines!$C$37)="","",CHAR(10)&amp;CHAR(10)&amp;IF(Inputs!$B$26="","",Lines!$C$37)))))</f>
+        <f>IF($D14&lt;&gt;"yes","",IF(Inputs!$B$18="draw",(Lines!$C$76&amp;IF(Inputs!$B$36="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$36)&amp;IF(Lines!$C$77="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$77)),(Lines!$C$74&amp;IF(Lines!$C$75="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$75)&amp;IF(IF(Inputs!$B$26="","",Lines!$C$38)="","",CHAR(10)&amp;CHAR(10)&amp;IF(Inputs!$B$26="","",Lines!$C$38)))))</f>
         <v/>
       </c>
       <c r="J14" s="11">
@@ -4368,7 +4395,7 @@
         <v/>
       </c>
       <c r="K14" s="11">
-        <f>IF($D14&lt;&gt;"yes","",Inputs!$B$74)</f>
+        <f>IF($D14&lt;&gt;"yes","",Inputs!$B$75)</f>
         <v/>
       </c>
       <c r="L14" s="11">
@@ -4407,7 +4434,7 @@
         <v/>
       </c>
       <c r="E15" s="11">
-        <f>IF($D15&lt;&gt;"yes","",Lines!$C$78)</f>
+        <f>IF($D15&lt;&gt;"yes","",Lines!$C$79)</f>
         <v/>
       </c>
       <c r="F15" s="11">
@@ -4423,7 +4450,7 @@
         <v/>
       </c>
       <c r="I15" s="11">
-        <f>IF($D15&lt;&gt;"yes","",(Lines!$C$31&amp;IF(Lines!$C$79="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$79)&amp;IF(Lines!$C$80="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$80)&amp;IF(Lines!$C$81="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$81)&amp;IF(Lines!$C$82="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$82)))</f>
+        <f>IF($D15&lt;&gt;"yes","",(Lines!$C$32&amp;IF(Lines!$C$80="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$80)&amp;IF(Lines!$C$81="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$81)&amp;IF(Lines!$C$82="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$82)&amp;IF(Lines!$C$83="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$83)))</f>
         <v/>
       </c>
       <c r="J15" s="11">
@@ -4486,7 +4513,7 @@
         <v/>
       </c>
       <c r="I16" s="11">
-        <f>IF($D16&lt;&gt;"yes","",(Lines!$C$83&amp;IF(Lines!$C$84="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$84)&amp;IF(Lines!$C$85="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$85)&amp;IF(Lines!$C$86="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$86)))</f>
+        <f>IF($D16&lt;&gt;"yes","",(Lines!$C$84&amp;IF(Lines!$C$85="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$85)&amp;IF(Lines!$C$86="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$86)&amp;IF(Lines!$C$87="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$87)))</f>
         <v/>
       </c>
       <c r="J16" s="11">
@@ -4502,7 +4529,7 @@
         <v/>
       </c>
       <c r="M16" s="11">
-        <f>IF($D16&lt;&gt;"yes","",Lines!$C$87)</f>
+        <f>IF($D16&lt;&gt;"yes","",Lines!$C$88)</f>
         <v/>
       </c>
       <c r="N16" s="11">
@@ -4549,7 +4576,7 @@
         <v/>
       </c>
       <c r="I17" s="11">
-        <f>IF($D17&lt;&gt;"yes","",(Lines!$C$89&amp;IF(Inputs!$B$36="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$36)&amp;IF(Inputs!$B$61="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$61)&amp;IF(IF(Inputs!$B$18="draw",Lines!$C$90,Lines!$C$91)="","",CHAR(10)&amp;CHAR(10)&amp;IF(Inputs!$B$18="draw",Lines!$C$90,Lines!$C$91))))</f>
+        <f>IF($D17&lt;&gt;"yes","",(Lines!$C$90&amp;IF(Inputs!$B$36="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$36)&amp;IF(Inputs!$B$62="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$62)&amp;IF(IF(Inputs!$B$18="draw",Lines!$C$91,Lines!$C$92)="","",CHAR(10)&amp;CHAR(10)&amp;IF(Inputs!$B$18="draw",Lines!$C$91,Lines!$C$92))))</f>
         <v/>
       </c>
       <c r="J17" s="11">

--- a/tool/release-copy-maurizio-cattelan-le-26.xlsx
+++ b/tool/release-copy-maurizio-cattelan-le-26.xlsx
@@ -492,7 +492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C79"/>
+  <dimension ref="A1:C81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1033,469 +1033,493 @@
     <row r="38" ht="32" customHeight="1">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>making</t>
-        </is>
-      </c>
-      <c r="B38" s="8" t="inlineStr">
-        <is>
-          <t>Each silkscreen print was produced by printmakers at Make-Ready in four layers, sealed with a matte varnish.</t>
-        </is>
-      </c>
+          <t>opener</t>
+        </is>
+      </c>
+      <c r="B38" s="8" t="inlineStr"/>
       <c r="C38" s="9" t="inlineStr">
         <is>
-          <t>one sentence on how the edition was made; write 'printmakers at Make-Ready' and the sheet adds 'our'.</t>
+          <t>or the announcement's first sentence written whole, e.g. Surveillance and defiance bubble to the surface in a new limited edition silkscreen print by Ai Weiwei. Blank keeps the framed line. One sentence, the artist in full, the words limited edition. The four other emails keep the framed line either way; if this leaves out the beneficiary, the features list names it.</t>
         </is>
       </c>
     </row>
     <row r="39" ht="32" customHeight="1">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>card_line_1</t>
+          <t>making</t>
         </is>
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>The duct-taped banana of Comedian, transplanted from the gallery wall to a hyper-realistic landscape, in four silkscreen layers sealed with matte varnish.</t>
+          <t>Each silkscreen print was produced by printmakers at Make-Ready in four layers, sealed with a matte varnish.</t>
         </is>
       </c>
       <c r="C39" s="9" t="inlineStr">
         <is>
-          <t>one sentence on the first work, 15 to 30 words, under its card in six emails. With several works, say something different about each: the edition is described above the cards, so do not call each one a limited edition print.</t>
+          <t>one sentence on how the edition was made; write 'printmakers at Make-Ready' and the sheet adds 'our'.</t>
         </is>
       </c>
     </row>
     <row r="40" ht="32" customHeight="1">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>card_line_2</t>
-        </is>
-      </c>
-      <c r="B40" s="8" t="inlineStr"/>
+          <t>card_line_1</t>
+        </is>
+      </c>
+      <c r="B40" s="8" t="inlineStr">
+        <is>
+          <t>The duct-taped banana of Comedian, transplanted from the gallery wall to a hyper-realistic landscape, in four silkscreen layers sealed with matte varnish.</t>
+        </is>
+      </c>
       <c r="C40" s="9" t="inlineStr">
         <is>
-          <t>the second titled work; blank otherwise</t>
+          <t>one sentence on the first work, 15 to 30 words, under its card in six emails. With several works, say something different about each: the edition is described above the cards, so do not call each one a limited edition print.</t>
         </is>
       </c>
     </row>
     <row r="41" ht="32" customHeight="1">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>card_line_3</t>
+          <t>card_line_2</t>
         </is>
       </c>
       <c r="B41" s="8" t="inlineStr"/>
       <c r="C41" s="9" t="inlineStr">
         <is>
-          <t>the third; blank otherwise</t>
+          <t>the second titled work; blank otherwise</t>
         </is>
       </c>
     </row>
     <row r="42" ht="32" customHeight="1">
       <c r="A42" s="4" t="inlineStr">
         <is>
+          <t>card_line_3</t>
+        </is>
+      </c>
+      <c r="B42" s="8" t="inlineStr"/>
+      <c r="C42" s="9" t="inlineStr">
+        <is>
+          <t>the third; blank otherwise</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="32" customHeight="1">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
           <t>quote</t>
         </is>
       </c>
-      <c r="B42" s="8" t="inlineStr">
+      <c r="B43" s="8" t="inlineStr">
         <is>
           <t>A comedian is doomed to make people laugh.</t>
         </is>
       </c>
-      <c r="C42" s="9" t="inlineStr">
+      <c r="C43" s="9" t="inlineStr">
         <is>
           <t>verbatim, a complete sentence, or blank</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="7" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="7" t="inlineStr">
         <is>
           <t>Derived (formulas, do not edit)</t>
         </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="4" t="inlineStr">
-        <is>
-          <t>named</t>
-        </is>
-      </c>
-      <c r="B45" s="10">
-        <f>$B$4&amp;IF($B$6="",""," (@"&amp;$B$6&amp;")")</f>
-        <v/>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>named_x</t>
+          <t>named</t>
         </is>
       </c>
       <c r="B46" s="10">
-        <f>$B$4&amp;IF($B$7="",""," (@"&amp;$B$7&amp;")")</f>
+        <f>$B$4&amp;IF($B$6="",""," (@"&amp;$B$6&amp;")")</f>
         <v/>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>collab_x</t>
+          <t>named_x</t>
         </is>
       </c>
       <c r="B47" s="10">
-        <f>IF($B$5=$B$4,$B$46,$B$5)</f>
+        <f>$B$4&amp;IF($B$7="",""," (@"&amp;$B$7&amp;")")</f>
         <v/>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>a_unit</t>
+          <t>collab_x</t>
         </is>
       </c>
       <c r="B48" s="10">
-        <f>IF(OR(LEFT($B$17,1)="a",LEFT($B$17,1)="e",LEFT($B$17,1)="i",LEFT($B$17,1)="o",LEFT($B$17,1)="u"),"an ","a ")&amp;$B$17</f>
+        <f>IF($B$5=$B$4,$B$47,$B$5)</f>
         <v/>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>work</t>
+          <t>a_unit</t>
         </is>
       </c>
       <c r="B49" s="10">
-        <f>IF($B$14&lt;&gt;"","the "&amp;$B$14&amp;" series",IF($B$12="","‘"&amp;$B$11&amp;"’",IF($B$13="","‘"&amp;$B$11&amp;"’ and ‘"&amp;$B$12&amp;"’","‘"&amp;$B$11&amp;"’, ‘"&amp;$B$12&amp;"’ and ‘"&amp;$B$13&amp;"’")))</f>
+        <f>IF(OR(LEFT($B$17,1)="a",LEFT($B$17,1)="e",LEFT($B$17,1)="i",LEFT($B$17,1)="o",LEFT($B$17,1)="u"),"an ","a ")&amp;$B$17</f>
         <v/>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>Work</t>
+          <t>work</t>
         </is>
       </c>
       <c r="B50" s="10">
-        <f>UPPER(LEFT($B$49,1))&amp;MID($B$49,2,999)</f>
+        <f>IF($B$14&lt;&gt;"","the "&amp;$B$14&amp;" series",IF($B$12="","‘"&amp;$B$11&amp;"’",IF($B$13="","‘"&amp;$B$11&amp;"’ and ‘"&amp;$B$12&amp;"’","‘"&amp;$B$11&amp;"’, ‘"&amp;$B$12&amp;"’ and ‘"&amp;$B$13&amp;"’")))</f>
         <v/>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>work_email</t>
+          <t>Work</t>
         </is>
       </c>
       <c r="B51" s="10">
-        <f>IF($B$14&lt;&gt;"","the "&amp;$B$14&amp;" series",IF($B$12="",$B$11,IF($B$13="",$B$11&amp;" and "&amp;$B$12,$B$11&amp;", "&amp;$B$12&amp;" and "&amp;$B$13)))</f>
+        <f>UPPER(LEFT($B$50,1))&amp;MID($B$50,2,999)</f>
         <v/>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>Work_email</t>
+          <t>work_email</t>
         </is>
       </c>
       <c r="B52" s="10">
-        <f>UPPER(LEFT($B$51,1))&amp;MID($B$51,2,999)</f>
+        <f>IF($B$14&lt;&gt;"","the "&amp;$B$14&amp;" series",IF($B$12="",$B$11,IF($B$13="",$B$11&amp;" and "&amp;$B$12,$B$11&amp;", "&amp;$B$12&amp;" and "&amp;$B$13)))</f>
         <v/>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>work_intro</t>
+          <t>Work_email</t>
         </is>
       </c>
       <c r="B53" s="10">
-        <f>IF($B$16=1,$B$11&amp;", ","")&amp;$B$15&amp;IF(OR($B$37="",$B$54&lt;&gt;""),"",IF(LEFT($B$37,1)=",",""," ")&amp;$B$37)</f>
+        <f>UPPER(LEFT($B$52,1))&amp;MID($B$52,2,999)</f>
         <v/>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>support</t>
+          <t>work_intro</t>
         </is>
       </c>
       <c r="B54" s="10">
-        <f>IF(OR($B$22="",$B$58),"",", released in support of "&amp;$B$22)</f>
+        <f>IF($B$16=1,$B$11&amp;", ","")&amp;$B$15&amp;IF(OR($B$37="",$B$55&lt;&gt;""),"",IF(LEFT($B$37,1)=",",""," ")&amp;$B$37)</f>
         <v/>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>tweet_beneficiary</t>
+          <t>support</t>
         </is>
       </c>
       <c r="B55" s="10">
-        <f>IF(OR($B$22="",$B$58),"",", in support of "&amp;$B$22)</f>
+        <f>IF(OR($B$22="",$B$59),"",", released in support of "&amp;$B$22)</f>
         <v/>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
+          <t>tweet_beneficiary</t>
+        </is>
+      </c>
+      <c r="B56" s="10">
+        <f>IF(OR($B$22="",$B$59),"",", in support of "&amp;$B$22)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
           <t>beneficiary_tagged</t>
         </is>
       </c>
-      <c r="B56" s="10">
+      <c r="B57" s="10">
         <f>IF($B$22="","",$B$22&amp;IF($B$23="",""," (@"&amp;$B$23&amp;")"))</f>
         <v/>
       </c>
     </row>
-    <row r="57" ht="80" customHeight="1">
-      <c r="A57" s="4" t="inlineStr">
+    <row r="58" ht="80" customHeight="1">
+      <c r="A58" s="4" t="inlineStr">
         <is>
           <t>bio_tagged</t>
         </is>
       </c>
-      <c r="B57" s="10">
-        <f>IF($B$6="",$B$35,SUBSTITUTE($B$35,$B$4,$B$45,1))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="4" t="inlineStr">
-        <is>
-          <t>hook_names_beneficiary</t>
-        </is>
-      </c>
       <c r="B58" s="10">
-        <f>IF($B$22="",FALSE,ISNUMBER(SEARCH($B$22,$B$36)))</f>
+        <f>IF($B$6="",$B$35,SUBSTITUTE($B$35,$B$4,$B$46,1))</f>
         <v/>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
+          <t>hook_names_beneficiary</t>
+        </is>
+      </c>
+      <c r="B59" s="10">
+        <f>IF($B$22="",FALSE,ISNUMBER(SEARCH($B$22,$B$36)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="inlineStr">
+        <is>
+          <t>opener_names_beneficiary</t>
+        </is>
+      </c>
+      <c r="B60" s="10">
+        <f>IF($B$22="",FALSE,ISNUMBER(SEARCH($B$22,$B$38)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="inlineStr">
+        <is>
           <t>features</t>
         </is>
       </c>
-      <c r="B59" s="10">
+      <c r="B61" s="10">
         <f>$B$28&amp;IF($B$29="","",". "&amp;$B$29)&amp;IF($B$30="","",". "&amp;$B$30)&amp;IF($B$31="","",". "&amp;$B$31)&amp;IF($B$32="","",". "&amp;$B$32)&amp;"."</f>
         <v/>
       </c>
     </row>
-    <row r="60" ht="60" customHeight="1">
-      <c r="A60" s="4" t="inlineStr">
+    <row r="62" ht="60" customHeight="1">
+      <c r="A62" s="4" t="inlineStr">
         <is>
           <t>features_list</t>
         </is>
       </c>
-      <c r="B60" s="10">
+      <c r="B62" s="10">
         <f>"· "&amp;$B$28&amp;IF($B$29="","",CHAR(10)&amp;"· "&amp;$B$29)&amp;IF($B$30="","",CHAR(10)&amp;"· "&amp;$B$30)&amp;IF($B$31="","",CHAR(10)&amp;"· "&amp;$B$31)&amp;IF($B$32="","",CHAR(10)&amp;"· "&amp;$B$32)</f>
         <v/>
       </c>
     </row>
-    <row r="61" ht="70" customHeight="1">
-      <c r="A61" s="4" t="inlineStr">
+    <row r="63" ht="70" customHeight="1">
+      <c r="A63" s="4" t="inlineStr">
         <is>
           <t>features_list_support</t>
         </is>
       </c>
-      <c r="B61" s="10">
-        <f>$B$60&amp;IF(OR($B$22="",$B$58),"",CHAR(10)&amp;"· Released in support of "&amp;$B$22)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="4" t="inlineStr">
-        <is>
-          <t>making_ours</t>
-        </is>
-      </c>
-      <c r="B62" s="10">
-        <f>SUBSTITUTE($B$38,"printmakers at Make-Ready","our printmakers at Make-Ready")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="4" t="inlineStr">
-        <is>
-          <t>making_ours_tagged</t>
-        </is>
-      </c>
       <c r="B63" s="10">
-        <f>SUBSTITUTE($B$38,"printmakers at Make-Ready","our printmakers at Make-Ready (@make__ready)")</f>
+        <f>$B$62&amp;IF(OR($B$22="",$B$59),"",CHAR(10)&amp;"· Released in support of "&amp;$B$22)</f>
         <v/>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>launch_date</t>
+          <t>making_ours</t>
         </is>
       </c>
       <c r="B64" s="10">
-        <f>TEXT($B$20,"d mmmm")</f>
+        <f>SUBSTITUTE($B$39,"printmakers at Make-Ready","our printmakers at Make-Ready")</f>
         <v/>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>launch_time</t>
+          <t>making_ours_tagged</t>
         </is>
       </c>
       <c r="B65" s="10">
-        <f>TEXT($B$20,"hh:mm")&amp;" UK time"</f>
+        <f>SUBSTITUTE($B$39,"printmakers at Make-Ready","our printmakers at Make-Ready (@make__ready)")</f>
         <v/>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>launch_weekday</t>
+          <t>launch_date</t>
         </is>
       </c>
       <c r="B66" s="10">
-        <f>TEXT($B$20,"dddd")</f>
+        <f>TEXT($B$20,"d mmmm")</f>
         <v/>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>launch_date_dd</t>
+          <t>launch_time</t>
         </is>
       </c>
       <c r="B67" s="10">
-        <f>TEXT($B$20,"dd mmmm")</f>
+        <f>TEXT($B$20,"hh:mm")&amp;" UK time"</f>
         <v/>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>close_date</t>
+          <t>launch_weekday</t>
         </is>
       </c>
       <c r="B68" s="10">
-        <f>TEXT($B$21,"d mmmm")</f>
+        <f>TEXT($B$20,"dddd")</f>
         <v/>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>close_time</t>
+          <t>launch_date_dd</t>
         </is>
       </c>
       <c r="B69" s="10">
-        <f>TEXT($B$21,"hh:mm")&amp;" UK time"</f>
+        <f>TEXT($B$20,"dd mmmm")</f>
         <v/>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>close_weekday</t>
+          <t>close_date</t>
         </is>
       </c>
       <c r="B70" s="10">
-        <f>TEXT($B$21,"dddd")</f>
+        <f>TEXT($B$21,"d mmmm")</f>
         <v/>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>close_date_dd</t>
+          <t>close_time</t>
         </is>
       </c>
       <c r="B71" s="10">
-        <f>TEXT($B$21,"dd mmmm")</f>
+        <f>TEXT($B$21,"hh:mm")&amp;" UK time"</f>
         <v/>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>collect_phrase</t>
+          <t>close_weekday</t>
         </is>
       </c>
       <c r="B72" s="10">
-        <f>SUBSTITUTE($B$15," new "," ",1)</f>
+        <f>TEXT($B$21,"dddd")</f>
         <v/>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>edition_phrase_cap</t>
+          <t>close_date_dd</t>
         </is>
       </c>
       <c r="B73" s="10">
-        <f>UPPER(LEFT($B$15,1))&amp;MID($B$15,2,999)</f>
+        <f>TEXT($B$21,"dd mmmm")</f>
         <v/>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>window_cap</t>
+          <t>collect_phrase</t>
         </is>
       </c>
       <c r="B74" s="10">
-        <f>UPPER(LEFT($B$19,1))&amp;MID($B$19,2,999)</f>
+        <f>SUBSTITUTE($B$15," new "," ",1)</f>
         <v/>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>card</t>
+          <t>edition_phrase_cap</t>
         </is>
       </c>
       <c r="B75" s="10">
-        <f>$B$11&amp;IF($B$39="","",CHAR(10)&amp;$B$39)&amp;IF($B$12="","",CHAR(10)&amp;CHAR(10)&amp;"Card: "&amp;$B$12&amp;IF($B$40="","",CHAR(10)&amp;$B$40))&amp;IF($B$13="","",CHAR(10)&amp;CHAR(10)&amp;"Card: "&amp;$B$13&amp;IF($B$41="","",CHAR(10)&amp;$B$41))</f>
+        <f>UPPER(LEFT($B$15,1))&amp;MID($B$15,2,999)</f>
         <v/>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>quote_line</t>
+          <t>window_cap</t>
         </is>
       </c>
       <c r="B76" s="10">
-        <f>IF($B$42="","","“"&amp;$B$42&amp;"” – "&amp;$B$4)</f>
+        <f>UPPER(LEFT($B$19,1))&amp;MID($B$19,2,999)</f>
         <v/>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>each_artwork</t>
+          <t>card</t>
         </is>
       </c>
       <c r="B77" s="10">
-        <f>IF($B$16&gt;1," for each artwork","")</f>
+        <f>$B$11&amp;IF($B$40="","",CHAR(10)&amp;$B$40)&amp;IF($B$12="","",CHAR(10)&amp;CHAR(10)&amp;"Card: "&amp;$B$12&amp;IF($B$41="","",CHAR(10)&amp;$B$41))&amp;IF($B$13="","",CHAR(10)&amp;CHAR(10)&amp;"Card: "&amp;$B$13&amp;IF($B$42="","",CHAR(10)&amp;$B$42))</f>
         <v/>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>work_word</t>
+          <t>quote_line</t>
         </is>
       </c>
       <c r="B78" s="10">
-        <f>IF($B$16&gt;1,"works","work")</f>
+        <f>IF($B$43="","","“"&amp;$B$43&amp;"” – "&amp;$B$4)</f>
         <v/>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
+          <t>each_artwork</t>
+        </is>
+      </c>
+      <c r="B79" s="10">
+        <f>IF($B$16&gt;1," for each artwork","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="4" t="inlineStr">
+        <is>
+          <t>work_word</t>
+        </is>
+      </c>
+      <c r="B80" s="10">
+        <f>IF($B$16&gt;1,"works","work")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="4" t="inlineStr">
+        <is>
           <t>add_what</t>
         </is>
       </c>
-      <c r="B79" s="10">
-        <f>IF($B$16&gt;1,$B$48,$B$51)</f>
+      <c r="B81" s="10">
+        <f>IF($B$16&gt;1,$B$49,$B$52)</f>
         <v/>
       </c>
     </row>
@@ -1584,7 +1608,7 @@
         </is>
       </c>
       <c r="C6" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6,"{named}",Inputs!$B$45),"{work}",Inputs!$B$49),"{edition_phrase}",Inputs!$B$15)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6,"{named}",Inputs!$B$46),"{work}",Inputs!$B$50),"{edition_phrase}",Inputs!$B$15)</f>
         <v/>
       </c>
     </row>
@@ -1600,7 +1624,7 @@
         </is>
       </c>
       <c r="C7" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B7,"{named}",Inputs!$B$45),"{work}",Inputs!$B$49),"{edition_phrase}",Inputs!$B$15)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B7,"{named}",Inputs!$B$46),"{work}",Inputs!$B$50),"{edition_phrase}",Inputs!$B$15)</f>
         <v/>
       </c>
     </row>
@@ -1616,7 +1640,7 @@
         </is>
       </c>
       <c r="C8" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B8,"{named}",Inputs!$B$45),"{work}",Inputs!$B$49),"{edition_phrase}",Inputs!$B$15)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B8,"{named}",Inputs!$B$46),"{work}",Inputs!$B$50),"{edition_phrase}",Inputs!$B$15)</f>
         <v/>
       </c>
     </row>
@@ -1632,7 +1656,7 @@
         </is>
       </c>
       <c r="C9" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(B9,"{artist}",Inputs!$B$4),"{quote}",Inputs!$B$42)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(B9,"{artist}",Inputs!$B$4),"{quote}",Inputs!$B$43)</f>
         <v/>
       </c>
     </row>
@@ -1648,7 +1672,7 @@
         </is>
       </c>
       <c r="C10" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B10,"{named}",Inputs!$B$45),"{Work}",Inputs!$B$50),"{edition_phrase}",Inputs!$B$15)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B10,"{named}",Inputs!$B$46),"{Work}",Inputs!$B$51),"{edition_phrase}",Inputs!$B$15)</f>
         <v/>
       </c>
     </row>
@@ -1664,7 +1688,7 @@
         </is>
       </c>
       <c r="C11" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B11,"{named}",Inputs!$B$45),"{Work}",Inputs!$B$50),"{window}",Inputs!$B$19)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B11,"{named}",Inputs!$B$46),"{Work}",Inputs!$B$51),"{window}",Inputs!$B$19)</f>
         <v/>
       </c>
     </row>
@@ -1680,7 +1704,7 @@
         </is>
       </c>
       <c r="C12" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(B12,"{named}",Inputs!$B$45),"{work}",Inputs!$B$49)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(B12,"{named}",Inputs!$B$46),"{work}",Inputs!$B$50)</f>
         <v/>
       </c>
     </row>
@@ -1696,7 +1720,7 @@
         </is>
       </c>
       <c r="C13" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(B13,"{named}",Inputs!$B$45),"{work}",Inputs!$B$49)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(B13,"{named}",Inputs!$B$46),"{work}",Inputs!$B$50)</f>
         <v/>
       </c>
     </row>
@@ -1712,7 +1736,7 @@
         </is>
       </c>
       <c r="C14" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(B14,"{named}",Inputs!$B$45),"{work}",Inputs!$B$49)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(B14,"{named}",Inputs!$B$46),"{work}",Inputs!$B$50)</f>
         <v/>
       </c>
     </row>
@@ -1728,7 +1752,7 @@
         </is>
       </c>
       <c r="C15" s="10">
-        <f>SUBSTITUTE(B15,"{features}",Inputs!$B$59)</f>
+        <f>SUBSTITUTE(B15,"{features}",Inputs!$B$61)</f>
         <v/>
       </c>
     </row>
@@ -1744,7 +1768,7 @@
         </is>
       </c>
       <c r="C16" s="10">
-        <f>SUBSTITUTE(B16,"{beneficiary_tagged}",Inputs!$B$56)</f>
+        <f>SUBSTITUTE(B16,"{beneficiary_tagged}",Inputs!$B$57)</f>
         <v/>
       </c>
     </row>
@@ -1760,7 +1784,7 @@
         </is>
       </c>
       <c r="C17" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B17,"{window}",Inputs!$B$19),"{launch_date}",Inputs!$B$64),"{launch_time}",Inputs!$B$65)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B17,"{window}",Inputs!$B$19),"{launch_date}",Inputs!$B$66),"{launch_time}",Inputs!$B$67)</f>
         <v/>
       </c>
     </row>
@@ -1776,7 +1800,7 @@
         </is>
       </c>
       <c r="C18" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(B18,"{close_date}",Inputs!$B$68),"{close_time}",Inputs!$B$69)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(B18,"{close_date}",Inputs!$B$70),"{close_time}",Inputs!$B$71)</f>
         <v/>
       </c>
     </row>
@@ -1792,7 +1816,7 @@
         </is>
       </c>
       <c r="C19" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B19,"{a_unit}",Inputs!$B$48),"{close_date}",Inputs!$B$68),"{close_time}",Inputs!$B$69)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B19,"{a_unit}",Inputs!$B$49),"{close_date}",Inputs!$B$70),"{close_time}",Inputs!$B$71)</f>
         <v/>
       </c>
     </row>
@@ -1808,7 +1832,7 @@
         </is>
       </c>
       <c r="C20" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(B20,"{close_date}",Inputs!$B$68),"{close_time}",Inputs!$B$69)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(B20,"{close_date}",Inputs!$B$70),"{close_time}",Inputs!$B$71)</f>
         <v/>
       </c>
     </row>
@@ -1863,7 +1887,7 @@
         </is>
       </c>
       <c r="C24" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(B24,"{collab_x}",Inputs!$B$47),"{ordinal}",Inputs!$B$10)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(B24,"{collab_x}",Inputs!$B$48),"{ordinal}",Inputs!$B$10)</f>
         <v/>
       </c>
     </row>
@@ -1895,7 +1919,7 @@
         </is>
       </c>
       <c r="C26" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B26,"{named_x}",Inputs!$B$46),"{work}",Inputs!$B$49),"{tweet_beneficiary}",Inputs!$B$55),"{edition_phrase}",Inputs!$B$15)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B26,"{named_x}",Inputs!$B$47),"{work}",Inputs!$B$50),"{tweet_beneficiary}",Inputs!$B$56),"{edition_phrase}",Inputs!$B$15)</f>
         <v/>
       </c>
     </row>
@@ -1911,7 +1935,7 @@
         </is>
       </c>
       <c r="C27" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B27,"{named_x}",Inputs!$B$46),"{work}",Inputs!$B$49),"{tweet_beneficiary}",Inputs!$B$55),"{edition_phrase}",Inputs!$B$15)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B27,"{named_x}",Inputs!$B$47),"{work}",Inputs!$B$50),"{tweet_beneficiary}",Inputs!$B$56),"{edition_phrase}",Inputs!$B$15)</f>
         <v/>
       </c>
     </row>
@@ -1927,7 +1951,7 @@
         </is>
       </c>
       <c r="C28" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B28,"{link}",Inputs!$B$8),"{window}",Inputs!$B$19),"{launch_date}",Inputs!$B$64),"{launch_time}",Inputs!$B$65)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B28,"{link}",Inputs!$B$8),"{window}",Inputs!$B$19),"{launch_date}",Inputs!$B$66),"{launch_time}",Inputs!$B$67)</f>
         <v/>
       </c>
     </row>
@@ -1943,7 +1967,7 @@
         </is>
       </c>
       <c r="C29" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B29,"{link}",Inputs!$B$8),"{close_date}",Inputs!$B$68),"{close_time}",Inputs!$B$69)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B29,"{link}",Inputs!$B$8),"{close_date}",Inputs!$B$70),"{close_time}",Inputs!$B$71)</f>
         <v/>
       </c>
     </row>
@@ -1959,7 +1983,7 @@
         </is>
       </c>
       <c r="C30" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B30,"{link}",Inputs!$B$8),"{a_unit}",Inputs!$B$48),"{close_date}",Inputs!$B$68),"{close_time}",Inputs!$B$69)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B30,"{link}",Inputs!$B$8),"{a_unit}",Inputs!$B$49),"{close_date}",Inputs!$B$70),"{close_time}",Inputs!$B$71)</f>
         <v/>
       </c>
     </row>
@@ -2014,7 +2038,7 @@
         </is>
       </c>
       <c r="C34" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(B34,"{close_date}",Inputs!$B$68),"{close_time}",Inputs!$B$69)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(B34,"{close_date}",Inputs!$B$70),"{close_time}",Inputs!$B$71)</f>
         <v/>
       </c>
     </row>
@@ -2046,7 +2070,7 @@
         </is>
       </c>
       <c r="C36" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(B36,"{artist}",Inputs!$B$4),"{a_unit}",Inputs!$B$48)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(B36,"{artist}",Inputs!$B$4),"{a_unit}",Inputs!$B$49)</f>
         <v/>
       </c>
     </row>
@@ -2101,7 +2125,7 @@
         </is>
       </c>
       <c r="C40" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(B40,"{artist}",Inputs!$B$4),"{edition_phrase_cap}",Inputs!$B$73)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(B40,"{artist}",Inputs!$B$4),"{edition_phrase_cap}",Inputs!$B$75)</f>
         <v/>
       </c>
     </row>
@@ -2117,7 +2141,7 @@
         </is>
       </c>
       <c r="C41" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B41,"{collab_with}",Inputs!$B$5),"{work_intro}",Inputs!$B$53),"{support}",Inputs!$B$54),"{ordinal}",Inputs!$B$10)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B41,"{collab_with}",Inputs!$B$5),"{work_intro}",Inputs!$B$54),"{support}",Inputs!$B$55),"{ordinal}",Inputs!$B$10)</f>
         <v/>
       </c>
     </row>
@@ -2133,7 +2157,7 @@
         </is>
       </c>
       <c r="C42" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B42,"{window}",Inputs!$B$19),"{launch_time}",Inputs!$B$65),"{launch_weekday}",Inputs!$B$66),"{launch_date_dd}",Inputs!$B$67)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B42,"{window}",Inputs!$B$19),"{launch_time}",Inputs!$B$67),"{launch_weekday}",Inputs!$B$68),"{launch_date_dd}",Inputs!$B$69)</f>
         <v/>
       </c>
     </row>
@@ -2243,7 +2267,7 @@
         </is>
       </c>
       <c r="C50" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B50,"{collab_with}",Inputs!$B$5),"{ordinal}",Inputs!$B$10),"{window}",Inputs!$B$19),"{launch_time}",Inputs!$B$65)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B50,"{collab_with}",Inputs!$B$5),"{ordinal}",Inputs!$B$10),"{window}",Inputs!$B$19),"{launch_time}",Inputs!$B$67)</f>
         <v/>
       </c>
     </row>
@@ -2307,7 +2331,7 @@
         </is>
       </c>
       <c r="C54" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B54,"{collab_with}",Inputs!$B$5),"{work_intro}",Inputs!$B$53),"{support}",Inputs!$B$54),"{ordinal}",Inputs!$B$10)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B54,"{collab_with}",Inputs!$B$5),"{work_intro}",Inputs!$B$54),"{support}",Inputs!$B$55),"{ordinal}",Inputs!$B$10)</f>
         <v/>
       </c>
     </row>
@@ -2323,7 +2347,7 @@
         </is>
       </c>
       <c r="C55" s="10">
-        <f>SUBSTITUTE(B55,"{launch_date}",Inputs!$B$64)</f>
+        <f>SUBSTITUTE(B55,"{launch_date}",Inputs!$B$66)</f>
         <v/>
       </c>
     </row>
@@ -2355,7 +2379,7 @@
         </is>
       </c>
       <c r="C57" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B57,"{collab_with}",Inputs!$B$5),"{work_intro}",Inputs!$B$53),"{support}",Inputs!$B$54),"{ordinal}",Inputs!$B$10)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B57,"{collab_with}",Inputs!$B$5),"{work_intro}",Inputs!$B$54),"{support}",Inputs!$B$55),"{ordinal}",Inputs!$B$10)</f>
         <v/>
       </c>
     </row>
@@ -2371,7 +2395,7 @@
         </is>
       </c>
       <c r="C58" s="10">
-        <f>SUBSTITUTE(B58,"{launch_date}",Inputs!$B$64)</f>
+        <f>SUBSTITUTE(B58,"{launch_date}",Inputs!$B$66)</f>
         <v/>
       </c>
     </row>
@@ -2387,7 +2411,7 @@
         </is>
       </c>
       <c r="C59" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(B59,"{window}",Inputs!$B$19),"{launch_time}",Inputs!$B$65)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(B59,"{window}",Inputs!$B$19),"{launch_time}",Inputs!$B$67)</f>
         <v/>
       </c>
     </row>
@@ -2460,7 +2484,7 @@
         </is>
       </c>
       <c r="C64" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B64,"{collab_with}",Inputs!$B$5),"{work_intro}",Inputs!$B$53),"{support}",Inputs!$B$54),"{ordinal}",Inputs!$B$10),"{window}",Inputs!$B$19)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B64,"{collab_with}",Inputs!$B$5),"{work_intro}",Inputs!$B$54),"{support}",Inputs!$B$55),"{ordinal}",Inputs!$B$10),"{window}",Inputs!$B$19)</f>
         <v/>
       </c>
     </row>
@@ -2476,7 +2500,7 @@
         </is>
       </c>
       <c r="C65" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B65,"{close_time}",Inputs!$B$69),"{close_weekday}",Inputs!$B$70),"{close_date_dd}",Inputs!$B$71),"{add_what}",Inputs!$B$79)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B65,"{close_time}",Inputs!$B$71),"{close_weekday}",Inputs!$B$72),"{close_date_dd}",Inputs!$B$73),"{add_what}",Inputs!$B$81)</f>
         <v/>
       </c>
     </row>
@@ -2508,7 +2532,7 @@
         </is>
       </c>
       <c r="C67" s="10">
-        <f>SUBSTITUTE(B67,"{a_unit}",Inputs!$B$48)</f>
+        <f>SUBSTITUTE(B67,"{a_unit}",Inputs!$B$49)</f>
         <v/>
       </c>
     </row>
@@ -2556,7 +2580,7 @@
         </is>
       </c>
       <c r="C70" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(B70,"{artist}",Inputs!$B$4),"{collect_phrase}",Inputs!$B$72)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(B70,"{artist}",Inputs!$B$4),"{collect_phrase}",Inputs!$B$74)</f>
         <v/>
       </c>
     </row>
@@ -2572,7 +2596,7 @@
         </is>
       </c>
       <c r="C71" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B71,"{close_time}",Inputs!$B$69),"{close_weekday}",Inputs!$B$70),"{close_date_dd}",Inputs!$B$71)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B71,"{close_time}",Inputs!$B$71),"{close_weekday}",Inputs!$B$72),"{close_date_dd}",Inputs!$B$73)</f>
         <v/>
       </c>
     </row>
@@ -2588,7 +2612,7 @@
         </is>
       </c>
       <c r="C72" s="10">
-        <f>SUBSTITUTE(B72,"{a_unit}",Inputs!$B$48)</f>
+        <f>SUBSTITUTE(B72,"{a_unit}",Inputs!$B$49)</f>
         <v/>
       </c>
     </row>
@@ -2611,7 +2635,7 @@
         </is>
       </c>
       <c r="C74" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B74,"{collab_with}",Inputs!$B$5),"{collect_phrase}",Inputs!$B$72),"{ordinal}",Inputs!$B$10),"{close_time}",Inputs!$B$69),"{close_weekday}",Inputs!$B$70),"{close_date_dd}",Inputs!$B$71)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B74,"{collab_with}",Inputs!$B$5),"{collect_phrase}",Inputs!$B$74),"{ordinal}",Inputs!$B$10),"{close_time}",Inputs!$B$71),"{close_weekday}",Inputs!$B$72),"{close_date_dd}",Inputs!$B$73)</f>
         <v/>
       </c>
     </row>
@@ -2627,7 +2651,7 @@
         </is>
       </c>
       <c r="C75" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(B75,"{each_artwork}",Inputs!$B$77),"{work_word}",Inputs!$B$78)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(B75,"{each_artwork}",Inputs!$B$79),"{work_word}",Inputs!$B$80)</f>
         <v/>
       </c>
     </row>
@@ -2643,7 +2667,7 @@
         </is>
       </c>
       <c r="C76" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B76,"{artist}",Inputs!$B$4),"{work_email}",Inputs!$B$51),"{collect_phrase}",Inputs!$B$72)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B76,"{artist}",Inputs!$B$4),"{work_email}",Inputs!$B$52),"{collect_phrase}",Inputs!$B$74)</f>
         <v/>
       </c>
     </row>
@@ -2659,7 +2683,7 @@
         </is>
       </c>
       <c r="C77" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B77,"{close_time}",Inputs!$B$69),"{close_weekday}",Inputs!$B$70),"{close_date_dd}",Inputs!$B$71)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B77,"{close_time}",Inputs!$B$71),"{close_weekday}",Inputs!$B$72),"{close_date_dd}",Inputs!$B$73)</f>
         <v/>
       </c>
     </row>
@@ -2849,7 +2873,7 @@
         </is>
       </c>
       <c r="C90" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B90,"{collab_with}",Inputs!$B$5),"{work_intro}",Inputs!$B$53),"{support}",Inputs!$B$54)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B90,"{collab_with}",Inputs!$B$5),"{work_intro}",Inputs!$B$54),"{support}",Inputs!$B$55)</f>
         <v/>
       </c>
     </row>
@@ -2865,7 +2889,7 @@
         </is>
       </c>
       <c r="C91" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(B91,"{close_date}",Inputs!$B$68),"{close_time}",Inputs!$B$69)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(B91,"{close_date}",Inputs!$B$70),"{close_time}",Inputs!$B$71)</f>
         <v/>
       </c>
     </row>
@@ -2881,7 +2905,7 @@
         </is>
       </c>
       <c r="C92" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B92,"{window}",Inputs!$B$19),"{launch_time}",Inputs!$B$65),"{launch_weekday}",Inputs!$B$66),"{launch_date_dd}",Inputs!$B$67)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B92,"{window}",Inputs!$B$19),"{launch_time}",Inputs!$B$67),"{launch_weekday}",Inputs!$B$68),"{launch_date_dd}",Inputs!$B$69)</f>
         <v/>
       </c>
     </row>
@@ -3007,7 +3031,7 @@
         <v/>
       </c>
       <c r="F4" s="11">
-        <f>Inputs!$B$57</f>
+        <f>Inputs!$B$58</f>
         <v/>
       </c>
       <c r="G4" s="11">
@@ -3059,7 +3083,7 @@
         <v/>
       </c>
       <c r="G5" s="11">
-        <f>Lines!$C$15&amp;IF(Inputs!$B$58,"",IF(Inputs!$B$56="",""," "&amp;Lines!$C$16))</f>
+        <f>Lines!$C$15&amp;IF(Inputs!$B$59,"",IF(Inputs!$B$57="",""," "&amp;Lines!$C$16))</f>
         <v/>
       </c>
       <c r="H5" s="11">
@@ -3103,11 +3127,11 @@
         <v/>
       </c>
       <c r="F6" s="11">
-        <f>Inputs!$B$63</f>
+        <f>Inputs!$B$65</f>
         <v/>
       </c>
       <c r="G6" s="11">
-        <f>Lines!$C$15&amp;IF(Inputs!$B$56="",""," "&amp;Lines!$C$16)</f>
+        <f>Lines!$C$15&amp;IF(Inputs!$B$57="",""," "&amp;Lines!$C$16)</f>
         <v/>
       </c>
       <c r="H6" s="11">
@@ -3147,19 +3171,19 @@
         </is>
       </c>
       <c r="E7" s="11">
-        <f>IF(Inputs!$B$42="","(no quote given, post skipped)",Lines!$C$9)</f>
+        <f>IF(Inputs!$B$43="","(no quote given, post skipped)",Lines!$C$9)</f>
         <v/>
       </c>
       <c r="F7" s="11">
-        <f>IF(Inputs!$B$42="","",Lines!$C$10)</f>
+        <f>IF(Inputs!$B$43="","",Lines!$C$10)</f>
         <v/>
       </c>
       <c r="G7" s="11">
-        <f>IF(Inputs!$B$42="","",Lines!$C$15&amp;IF(Inputs!$B$56="",""," "&amp;Lines!$C$16))</f>
+        <f>IF(Inputs!$B$43="","",Lines!$C$15&amp;IF(Inputs!$B$57="",""," "&amp;Lines!$C$16))</f>
         <v/>
       </c>
       <c r="H7" s="11">
-        <f>IF(Inputs!$B$42="","",IF(Inputs!$B$18="draw",Lines!$C$18,Lines!$C$17))</f>
+        <f>IF(Inputs!$B$43="","",IF(Inputs!$B$18="draw",Lines!$C$18,Lines!$C$17))</f>
         <v/>
       </c>
       <c r="I7" s="11">
@@ -3167,7 +3191,7 @@
         <v/>
       </c>
       <c r="J7" s="11">
-        <f>IF(Inputs!$B$42="","(no quote given, post skipped)",E7&amp;IF(F7="","",CHAR(10)&amp;CHAR(10)&amp;F7)&amp;IF(G7="","",CHAR(10)&amp;CHAR(10)&amp;G7)&amp;IF(H7="","",CHAR(10)&amp;CHAR(10)&amp;H7))</f>
+        <f>IF(Inputs!$B$43="","(no quote given, post skipped)",E7&amp;IF(F7="","",CHAR(10)&amp;CHAR(10)&amp;F7)&amp;IF(G7="","",CHAR(10)&amp;CHAR(10)&amp;G7)&amp;IF(H7="","",CHAR(10)&amp;CHAR(10)&amp;H7))</f>
         <v/>
       </c>
       <c r="K7" s="11">
@@ -3203,7 +3227,7 @@
         <v/>
       </c>
       <c r="G8" s="11">
-        <f>IF(Inputs!$B$18="draw","",Lines!$C$15&amp;IF(Inputs!$B$56="",""," "&amp;Lines!$C$16))</f>
+        <f>IF(Inputs!$B$18="draw","",Lines!$C$15&amp;IF(Inputs!$B$57="",""," "&amp;Lines!$C$16))</f>
         <v/>
       </c>
       <c r="H8" s="11">
@@ -3251,7 +3275,7 @@
         <v/>
       </c>
       <c r="G9" s="11">
-        <f>IF(Inputs!$B$18="draw","",Lines!$C$15&amp;IF(Inputs!$B$56="",""," "&amp;Lines!$C$16))</f>
+        <f>IF(Inputs!$B$18="draw","",Lines!$C$15&amp;IF(Inputs!$B$57="",""," "&amp;Lines!$C$16))</f>
         <v/>
       </c>
       <c r="H9" s="11">
@@ -3299,7 +3323,7 @@
         <v/>
       </c>
       <c r="G10" s="11">
-        <f>Lines!$C$15&amp;IF(Inputs!$B$56="",""," "&amp;Lines!$C$16)</f>
+        <f>Lines!$C$15&amp;IF(Inputs!$B$57="",""," "&amp;Lines!$C$16)</f>
         <v/>
       </c>
       <c r="H10" s="11">
@@ -3498,7 +3522,7 @@
         </is>
       </c>
       <c r="D6" s="11">
-        <f>IF(Inputs!$B$18="draw","(not used for a draw)",SUBSTITUTE(Lines!$C$11,Inputs!$B$45,Inputs!$B$46))</f>
+        <f>IF(Inputs!$B$18="draw","(not used for a draw)",SUBSTITUTE(Lines!$C$11,Inputs!$B$46,Inputs!$B$47))</f>
         <v/>
       </c>
       <c r="E6" s="11">
@@ -3537,7 +3561,7 @@
         </is>
       </c>
       <c r="D7" s="11">
-        <f>IF(Inputs!$B$18="draw","(not used for a draw)",SUBSTITUTE(Lines!$C$12,Inputs!$B$45,Inputs!$B$46))</f>
+        <f>IF(Inputs!$B$18="draw","(not used for a draw)",SUBSTITUTE(Lines!$C$12,Inputs!$B$46,Inputs!$B$47))</f>
         <v/>
       </c>
       <c r="E7" s="11">
@@ -3576,7 +3600,7 @@
         </is>
       </c>
       <c r="D8" s="11">
-        <f>IF(Inputs!$B$18="draw",SUBSTITUTE(Lines!$C$14,Inputs!$B$45,Inputs!$B$46),SUBSTITUTE(Lines!$C$13,Inputs!$B$45,Inputs!$B$46))</f>
+        <f>IF(Inputs!$B$18="draw",SUBSTITUTE(Lines!$C$14,Inputs!$B$46,Inputs!$B$47),SUBSTITUTE(Lines!$C$13,Inputs!$B$46,Inputs!$B$47))</f>
         <v/>
       </c>
       <c r="E8" s="11">
@@ -3745,19 +3769,19 @@
         <v/>
       </c>
       <c r="F4" s="11">
-        <f>IF($D4&lt;&gt;"yes","",IF(Inputs!$B$18="draw","Enter the draw for a chance to collect. Closes "&amp;Inputs!$B$68&amp;".","Launching "&amp;Inputs!$B$64&amp;". Register for updates."))</f>
+        <f>IF($D4&lt;&gt;"yes","",IF(Inputs!$B$18="draw","Enter the draw for a chance to collect. Closes "&amp;Inputs!$B$70&amp;".","Launching "&amp;Inputs!$B$66&amp;". Register for updates."))</f>
         <v/>
       </c>
       <c r="G4" s="11">
-        <f>IF($D4&lt;&gt;"yes","",IF(Inputs!$B$18="draw","Enter the draw","Launching "&amp;Inputs!$B$64))</f>
+        <f>IF($D4&lt;&gt;"yes","",IF(Inputs!$B$18="draw","Enter the draw","Launching "&amp;Inputs!$B$66))</f>
         <v/>
       </c>
       <c r="H4" s="11">
-        <f>IF($D4&lt;&gt;"yes","",IF(Inputs!$B$18="draw",Inputs!$B$52,Inputs!$B$52&amp;" by "&amp;Inputs!$B$4))</f>
+        <f>IF($D4&lt;&gt;"yes","",IF(Inputs!$B$18="draw",Inputs!$B$53,Inputs!$B$53&amp;" by "&amp;Inputs!$B$4))</f>
         <v/>
       </c>
       <c r="I4" s="11">
-        <f>IF($D4&lt;&gt;"yes","",(Lines!$C$41&amp;IF(Inputs!$B$36="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$36)&amp;IF(Inputs!$B$62="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$62)&amp;IF(Inputs!$B$60="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$60)&amp;IF(IF(Inputs!$B$18="draw",Lines!$C$34,(Lines!$C$42&amp;IF(Lines!$C$43="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$43)))="","",CHAR(10)&amp;CHAR(10)&amp;IF(Inputs!$B$18="draw",Lines!$C$34,(Lines!$C$42&amp;IF(Lines!$C$43="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$43))))))</f>
+        <f>IF($D4&lt;&gt;"yes","",(IF(Inputs!$B$38="",Lines!$C$41,Inputs!$B$38)&amp;IF(Inputs!$B$36="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$36)&amp;IF(Inputs!$B$64="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$64)&amp;IF(IF(OR(Inputs!$B$38="",Inputs!$B$60),Inputs!$B$62,Inputs!$B$63)="","",CHAR(10)&amp;CHAR(10)&amp;IF(OR(Inputs!$B$38="",Inputs!$B$60),Inputs!$B$62,Inputs!$B$63))&amp;IF(IF(Inputs!$B$18="draw",Lines!$C$34,(Lines!$C$42&amp;IF(Lines!$C$43="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$43)))="","",CHAR(10)&amp;CHAR(10)&amp;IF(Inputs!$B$18="draw",Lines!$C$34,(Lines!$C$42&amp;IF(Lines!$C$43="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$43))))))</f>
         <v/>
       </c>
       <c r="J4" s="11">
@@ -3765,15 +3789,15 @@
         <v/>
       </c>
       <c r="K4" s="11">
-        <f>IF($D4&lt;&gt;"yes","",Inputs!$B$75)</f>
+        <f>IF($D4&lt;&gt;"yes","",Inputs!$B$77)</f>
         <v/>
       </c>
       <c r="L4" s="11">
-        <f>IF($D4&lt;&gt;"yes","",Inputs!$B$76)</f>
+        <f>IF($D4&lt;&gt;"yes","",Inputs!$B$78)</f>
         <v/>
       </c>
       <c r="M4" s="11">
-        <f>IF($D4&lt;&gt;"yes","",IF(Inputs!$B$18="draw","Collect "&amp;Inputs!$B$72,"Launching "&amp;Inputs!$B$64))</f>
+        <f>IF($D4&lt;&gt;"yes","",IF(Inputs!$B$18="draw","Collect "&amp;Inputs!$B$74,"Launching "&amp;Inputs!$B$66))</f>
         <v/>
       </c>
       <c r="N4" s="11">
@@ -3883,7 +3907,7 @@
         <v/>
       </c>
       <c r="I6" s="11">
-        <f>IF($D6&lt;&gt;"yes","",(Lines!$C$32&amp;IF(Lines!$C$50="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$50)&amp;IF(Inputs!$B$36="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$36)&amp;IF(Inputs!$B$61="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$61)&amp;IF(Lines!$C$51="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$51)&amp;IF(IF(Inputs!$B$26="","",Lines!$C$37)="","",CHAR(10)&amp;CHAR(10)&amp;IF(Inputs!$B$26="","",Lines!$C$37))&amp;IF(Lines!$C$53="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$53)))</f>
+        <f>IF($D6&lt;&gt;"yes","",(Lines!$C$32&amp;IF(Lines!$C$50="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$50)&amp;IF(Inputs!$B$36="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$36)&amp;IF(Inputs!$B$63="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$63)&amp;IF(Lines!$C$51="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$51)&amp;IF(IF(Inputs!$B$26="","",Lines!$C$37)="","",CHAR(10)&amp;CHAR(10)&amp;IF(Inputs!$B$26="","",Lines!$C$37))&amp;IF(Lines!$C$53="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$53)))</f>
         <v/>
       </c>
       <c r="J6" s="11">
@@ -3946,7 +3970,7 @@
         <v/>
       </c>
       <c r="I7" s="11">
-        <f>IF($D7&lt;&gt;"yes","",(Lines!$C$32&amp;IF(Lines!$C$50="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$50)&amp;IF(Inputs!$B$36="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$36)&amp;IF(Inputs!$B$61="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$61)&amp;IF(Lines!$C$52="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$52)&amp;IF(Lines!$C$53="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$53)&amp;IF(Lines!$C$35="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$35)&amp;IF(Lines!$C$33="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$33)))</f>
+        <f>IF($D7&lt;&gt;"yes","",(Lines!$C$32&amp;IF(Lines!$C$50="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$50)&amp;IF(Inputs!$B$36="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$36)&amp;IF(Inputs!$B$63="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$63)&amp;IF(Lines!$C$52="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$52)&amp;IF(Lines!$C$53="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$53)&amp;IF(Lines!$C$35="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$35)&amp;IF(Lines!$C$33="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$33)))</f>
         <v/>
       </c>
       <c r="J7" s="11">
@@ -3954,7 +3978,7 @@
         <v/>
       </c>
       <c r="K7" s="11">
-        <f>IF($D7&lt;&gt;"yes","",Inputs!$B$75)</f>
+        <f>IF($D7&lt;&gt;"yes","",Inputs!$B$77)</f>
         <v/>
       </c>
       <c r="L7" s="11">
@@ -4017,7 +4041,7 @@
         <v/>
       </c>
       <c r="K8" s="11">
-        <f>IF($D8&lt;&gt;"yes","",Inputs!$B$75)</f>
+        <f>IF($D8&lt;&gt;"yes","",Inputs!$B$77)</f>
         <v/>
       </c>
       <c r="L8" s="11">
@@ -4080,7 +4104,7 @@
         <v/>
       </c>
       <c r="K9" s="11">
-        <f>IF($D9&lt;&gt;"yes","",Inputs!$B$75)</f>
+        <f>IF($D9&lt;&gt;"yes","",Inputs!$B$77)</f>
         <v/>
       </c>
       <c r="L9" s="11">
@@ -4123,7 +4147,7 @@
         <v/>
       </c>
       <c r="F10" s="11">
-        <f>IF($D10&lt;&gt;"yes","",Inputs!$B$74&amp;", starting now.")</f>
+        <f>IF($D10&lt;&gt;"yes","",Inputs!$B$76&amp;", starting now.")</f>
         <v/>
       </c>
       <c r="G10" s="11">
@@ -4131,11 +4155,11 @@
         <v/>
       </c>
       <c r="H10" s="11">
-        <f>IF($D10&lt;&gt;"yes","",Inputs!$B$74&amp;", starting now")</f>
+        <f>IF($D10&lt;&gt;"yes","",Inputs!$B$76&amp;", starting now")</f>
         <v/>
       </c>
       <c r="I10" s="11">
-        <f>IF($D10&lt;&gt;"yes","",(Lines!$C$64&amp;IF(Inputs!$B$36="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$36)&amp;IF(Inputs!$B$62="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$62)&amp;IF(Inputs!$B$61="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$61)&amp;IF(Lines!$C$65="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$65)&amp;IF(IF(Inputs!$B$26="","",Lines!$C$37)="","",CHAR(10)&amp;CHAR(10)&amp;IF(Inputs!$B$26="","",Lines!$C$37))))</f>
+        <f>IF($D10&lt;&gt;"yes","",(Lines!$C$64&amp;IF(Inputs!$B$36="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$36)&amp;IF(Inputs!$B$64="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$64)&amp;IF(Inputs!$B$63="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$63)&amp;IF(Lines!$C$65="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$65)&amp;IF(IF(Inputs!$B$26="","",Lines!$C$37)="","",CHAR(10)&amp;CHAR(10)&amp;IF(Inputs!$B$26="","",Lines!$C$37))))</f>
         <v/>
       </c>
       <c r="J10" s="11">
@@ -4143,15 +4167,15 @@
         <v/>
       </c>
       <c r="K10" s="11">
-        <f>IF($D10&lt;&gt;"yes","",Inputs!$B$75)</f>
+        <f>IF($D10&lt;&gt;"yes","",Inputs!$B$77)</f>
         <v/>
       </c>
       <c r="L10" s="11">
-        <f>IF($D10&lt;&gt;"yes","",Inputs!$B$76)</f>
+        <f>IF($D10&lt;&gt;"yes","",Inputs!$B$78)</f>
         <v/>
       </c>
       <c r="M10" s="11">
-        <f>IF($D10&lt;&gt;"yes","","Collect "&amp;Inputs!$B$72)</f>
+        <f>IF($D10&lt;&gt;"yes","","Collect "&amp;Inputs!$B$74)</f>
         <v/>
       </c>
       <c r="N10" s="11">
@@ -4265,7 +4289,7 @@
         <v/>
       </c>
       <c r="J12" s="11">
-        <f>IF($D12&lt;&gt;"yes","","Buy "&amp;Inputs!$B$48)</f>
+        <f>IF($D12&lt;&gt;"yes","","Buy "&amp;Inputs!$B$49)</f>
         <v/>
       </c>
       <c r="K12" s="11">
@@ -4316,7 +4340,7 @@
         <v/>
       </c>
       <c r="G13" s="11">
-        <f>IF($D13&lt;&gt;"yes","",Inputs!$B$52&amp;" by "&amp;Inputs!$B$4)</f>
+        <f>IF($D13&lt;&gt;"yes","",Inputs!$B$53&amp;" by "&amp;Inputs!$B$4)</f>
         <v/>
       </c>
       <c r="H13" s="11">
@@ -4328,11 +4352,11 @@
         <v/>
       </c>
       <c r="J13" s="11">
-        <f>IF($D13&lt;&gt;"yes","","Buy "&amp;Inputs!$B$48)</f>
+        <f>IF($D13&lt;&gt;"yes","","Buy "&amp;Inputs!$B$49)</f>
         <v/>
       </c>
       <c r="K13" s="11">
-        <f>IF($D13&lt;&gt;"yes","",Inputs!$B$75)</f>
+        <f>IF($D13&lt;&gt;"yes","",Inputs!$B$77)</f>
         <v/>
       </c>
       <c r="L13" s="11">
@@ -4375,7 +4399,7 @@
         <v/>
       </c>
       <c r="F14" s="11">
-        <f>IF($D14&lt;&gt;"yes","",IF(Inputs!$B$18="draw","The draw closes at "&amp;Inputs!$B$69&amp;" on "&amp;Inputs!$B$68&amp;".","Time is almost up."))</f>
+        <f>IF($D14&lt;&gt;"yes","",IF(Inputs!$B$18="draw","The draw closes at "&amp;Inputs!$B$71&amp;" on "&amp;Inputs!$B$70&amp;".","Time is almost up."))</f>
         <v/>
       </c>
       <c r="G14" s="11">
@@ -4395,7 +4419,7 @@
         <v/>
       </c>
       <c r="K14" s="11">
-        <f>IF($D14&lt;&gt;"yes","",Inputs!$B$75)</f>
+        <f>IF($D14&lt;&gt;"yes","",Inputs!$B$77)</f>
         <v/>
       </c>
       <c r="L14" s="11">
@@ -4576,7 +4600,7 @@
         <v/>
       </c>
       <c r="I17" s="11">
-        <f>IF($D17&lt;&gt;"yes","",(Lines!$C$90&amp;IF(Inputs!$B$36="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$36)&amp;IF(Inputs!$B$62="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$62)&amp;IF(IF(Inputs!$B$18="draw",Lines!$C$91,Lines!$C$92)="","",CHAR(10)&amp;CHAR(10)&amp;IF(Inputs!$B$18="draw",Lines!$C$91,Lines!$C$92))))</f>
+        <f>IF($D17&lt;&gt;"yes","",(Lines!$C$90&amp;IF(Inputs!$B$36="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$36)&amp;IF(Inputs!$B$64="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$64)&amp;IF(IF(Inputs!$B$18="draw",Lines!$C$91,Lines!$C$92)="","",CHAR(10)&amp;CHAR(10)&amp;IF(Inputs!$B$18="draw",Lines!$C$91,Lines!$C$92))))</f>
         <v/>
       </c>
       <c r="J17" s="11">

--- a/tool/release-copy-maurizio-cattelan-le-26.xlsx
+++ b/tool/release-copy-maurizio-cattelan-le-26.xlsx
@@ -2002,7 +2002,7 @@
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>Hi {{ personalization_token('contact.firstname', 'there') }},</t>
+          <t>Hi [name],</t>
         </is>
       </c>
       <c r="C32" s="10">
@@ -2184,7 +2184,7 @@
         </is>
       </c>
     </row>
-    <row r="45" ht="32" customHeight="1">
+    <row r="45" ht="16" customHeight="1">
       <c r="A45" s="4" t="inlineStr">
         <is>
           <t>email · welcome · 1</t>
@@ -2192,7 +2192,7 @@
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>Welcome {{ personalization_token('contact.firstname', 'to Avant Arte') }}!</t>
+          <t>Welcome [name]!</t>
         </is>
       </c>
       <c r="C45" s="10">

--- a/tool/release-copy-maurizio-cattelan-le-26.xlsx
+++ b/tool/release-copy-maurizio-cattelan-le-26.xlsx
@@ -1534,7 +1534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C92"/>
+  <dimension ref="A1:C89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -2523,28 +2523,28 @@
     <row r="67" ht="16" customHeight="1">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>email · halfway · footer</t>
+          <t>email · 5 days · headline</t>
         </is>
       </c>
       <c r="B67" s="8" t="inlineStr">
         <is>
-          <t>There's still time to add {a_unit} to your collection.</t>
+          <t>2 days down, 5 days to go</t>
         </is>
       </c>
       <c r="C67" s="10">
-        <f>SUBSTITUTE(B67,"{a_unit}",Inputs!$B$49)</f>
+        <f>B67</f>
         <v/>
       </c>
     </row>
     <row r="68" ht="16" customHeight="1">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>email · 5 days · headline</t>
+          <t>email · 3 days · headline</t>
         </is>
       </c>
       <c r="B68" s="8" t="inlineStr">
         <is>
-          <t>2 days down, 5 days to go</t>
+          <t>Three days left to collect</t>
         </is>
       </c>
       <c r="C68" s="10">
@@ -2552,221 +2552,221 @@
         <v/>
       </c>
     </row>
-    <row r="69" ht="16" customHeight="1">
+    <row r="69" ht="32" customHeight="1">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>email · 3 days · headline</t>
+          <t>email · 3 days · 1</t>
         </is>
       </c>
       <c r="B69" s="8" t="inlineStr">
         <is>
-          <t>Three days left to collect</t>
+          <t>There are just three days left to collect {collect_phrase} by {artist}.</t>
         </is>
       </c>
       <c r="C69" s="10">
-        <f>B69</f>
+        <f>SUBSTITUTE(SUBSTITUTE(B69,"{artist}",Inputs!$B$4),"{collect_phrase}",Inputs!$B$74)</f>
         <v/>
       </c>
     </row>
     <row r="70" ht="32" customHeight="1">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>email · 3 days · 1</t>
+          <t>email · 3 days · 2</t>
         </is>
       </c>
       <c r="B70" s="8" t="inlineStr">
         <is>
-          <t>There are just three days left to collect {collect_phrase} by {artist}.</t>
+          <t>Click the link to collect before {close_time} on {close_weekday}, {close_date_dd}.</t>
         </is>
       </c>
       <c r="C70" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(B70,"{artist}",Inputs!$B$4),"{collect_phrase}",Inputs!$B$74)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="71" ht="32" customHeight="1">
-      <c r="A71" s="4" t="inlineStr">
-        <is>
-          <t>email · 3 days · 2</t>
-        </is>
-      </c>
-      <c r="B71" s="8" t="inlineStr">
-        <is>
-          <t>Click the link to collect before {close_time} on {close_weekday}, {close_date_dd}.</t>
-        </is>
-      </c>
-      <c r="C71" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B71,"{close_time}",Inputs!$B$71),"{close_weekday}",Inputs!$B$72),"{close_date_dd}",Inputs!$B$73)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="72" ht="16" customHeight="1">
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B70,"{close_time}",Inputs!$B$71),"{close_weekday}",Inputs!$B$72),"{close_date_dd}",Inputs!$B$73)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t>EMAILS · last chance</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="48" customHeight="1">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>email · days to go · footer</t>
+          <t>email · last chance, timed · 1</t>
         </is>
       </c>
       <c r="B72" s="8" t="inlineStr">
         <is>
-          <t>Add {a_unit} to your collection</t>
+          <t>It's now or never for our {ordinal} collaboration with {collab_with} – {collect_phrase} will be available to order until {close_time} on {close_weekday}, {close_date_dd}.</t>
         </is>
       </c>
       <c r="C72" s="10">
-        <f>SUBSTITUTE(B72,"{a_unit}",Inputs!$B$49)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="3" t="inlineStr">
-        <is>
-          <t>EMAILS · last chance</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="48" customHeight="1">
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B72,"{collab_with}",Inputs!$B$5),"{collect_phrase}",Inputs!$B$74),"{ordinal}",Inputs!$B$10),"{close_time}",Inputs!$B$71),"{close_weekday}",Inputs!$B$72),"{close_date_dd}",Inputs!$B$73)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73" ht="32" customHeight="1">
+      <c r="A73" s="4" t="inlineStr">
+        <is>
+          <t>email · last chance, timed · 2</t>
+        </is>
+      </c>
+      <c r="B73" s="8" t="inlineStr">
+        <is>
+          <t>After this time, the edition size{each_artwork} will be confirmed, and the {work_word} will no longer be available to purchase.</t>
+        </is>
+      </c>
+      <c r="C73" s="10">
+        <f>SUBSTITUTE(SUBSTITUTE(B73,"{each_artwork}",Inputs!$B$79),"{work_word}",Inputs!$B$80)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="74" ht="32" customHeight="1">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>email · last chance, timed · 1</t>
+          <t>email · last chance, draw · 1</t>
         </is>
       </c>
       <c r="B74" s="8" t="inlineStr">
         <is>
-          <t>It's now or never for our {ordinal} collaboration with {collab_with} – {collect_phrase} will be available to order until {close_time} on {close_weekday}, {close_date_dd}.</t>
+          <t>This is your final opportunity to enter the draw for {work_email}, {collect_phrase} by {artist}.</t>
         </is>
       </c>
       <c r="C74" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B74,"{collab_with}",Inputs!$B$5),"{collect_phrase}",Inputs!$B$74),"{ordinal}",Inputs!$B$10),"{close_time}",Inputs!$B$71),"{close_weekday}",Inputs!$B$72),"{close_date_dd}",Inputs!$B$73)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B74,"{artist}",Inputs!$B$4),"{work_email}",Inputs!$B$52),"{collect_phrase}",Inputs!$B$74)</f>
         <v/>
       </c>
     </row>
     <row r="75" ht="32" customHeight="1">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>email · last chance, timed · 2</t>
+          <t>email · last chance, draw · 2</t>
         </is>
       </c>
       <c r="B75" s="8" t="inlineStr">
         <is>
-          <t>After this time, the edition size{each_artwork} will be confirmed, and the {work_word} will no longer be available to purchase.</t>
+          <t>For a chance to collect, click the link below to enter the draw. The draw closes at {close_time} on {close_weekday}, {close_date_dd}.</t>
         </is>
       </c>
       <c r="C75" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(B75,"{each_artwork}",Inputs!$B$79),"{work_word}",Inputs!$B$80)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="76" ht="32" customHeight="1">
-      <c r="A76" s="4" t="inlineStr">
-        <is>
-          <t>email · last chance, draw · 1</t>
-        </is>
-      </c>
-      <c r="B76" s="8" t="inlineStr">
-        <is>
-          <t>This is your final opportunity to enter the draw for {work_email}, {collect_phrase} by {artist}.</t>
-        </is>
-      </c>
-      <c r="C76" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B76,"{artist}",Inputs!$B$4),"{work_email}",Inputs!$B$52),"{collect_phrase}",Inputs!$B$74)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="77" ht="32" customHeight="1">
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B75,"{close_time}",Inputs!$B$71),"{close_weekday}",Inputs!$B$72),"{close_date_dd}",Inputs!$B$73)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="3" t="inlineStr">
+        <is>
+          <t>EMAILS · surveys (LE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="16" customHeight="1">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>email · last chance, draw · 2</t>
+          <t>email · first-time survey · subject</t>
         </is>
       </c>
       <c r="B77" s="8" t="inlineStr">
         <is>
-          <t>For a chance to collect, click the link below to enter the draw. The draw closes at {close_time} on {close_weekday}, {close_date_dd}.</t>
+          <t>Congratulations on your first Avant Arte edition</t>
         </is>
       </c>
       <c r="C77" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B77,"{close_time}",Inputs!$B$71),"{close_weekday}",Inputs!$B$72),"{close_date_dd}",Inputs!$B$73)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="3" t="inlineStr">
-        <is>
-          <t>EMAILS · surveys (LE)</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="16" customHeight="1">
+        <f>B77</f>
+        <v/>
+      </c>
+    </row>
+    <row r="78" ht="32" customHeight="1">
+      <c r="A78" s="4" t="inlineStr">
+        <is>
+          <t>email · first-time survey · 1</t>
+        </is>
+      </c>
+      <c r="B78" s="8" t="inlineStr">
+        <is>
+          <t>Thank you for adding our collaboration with {collab_with} to your collection. Great choice!</t>
+        </is>
+      </c>
+      <c r="C78" s="10">
+        <f>SUBSTITUTE(B78,"{collab_with}",Inputs!$B$5)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="79" ht="48" customHeight="1">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>email · first-time survey · subject</t>
+          <t>email · first-time survey · 2</t>
         </is>
       </c>
       <c r="B79" s="8" t="inlineStr">
         <is>
-          <t>Congratulations on your first Avant Arte edition</t>
+          <t>I'm {advisor}, an art advisor at Avant Arte. I'm here to connect collectors with artists by making suggestions, answering questions and offering early access to our collaborations.</t>
         </is>
       </c>
       <c r="C79" s="10">
-        <f>B79</f>
+        <f>SUBSTITUTE(B79,"{advisor}",Inputs!$B$24)</f>
         <v/>
       </c>
     </row>
     <row r="80" ht="32" customHeight="1">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>email · first-time survey · 1</t>
+          <t>email · first-time survey · 3</t>
         </is>
       </c>
       <c r="B80" s="8" t="inlineStr">
         <is>
-          <t>Thank you for adding our collaboration with {collab_with} to your collection. Great choice!</t>
+          <t>If you have two minutes to complete a short survey about your collecting journey to date, your responses will help guide my recommendations.</t>
         </is>
       </c>
       <c r="C80" s="10">
-        <f>SUBSTITUTE(B80,"{collab_with}",Inputs!$B$5)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="81" ht="48" customHeight="1">
+        <f>B80</f>
+        <v/>
+      </c>
+    </row>
+    <row r="81" ht="16" customHeight="1">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>email · first-time survey · 2</t>
+          <t>email · first-time survey · 4</t>
         </is>
       </c>
       <c r="B81" s="8" t="inlineStr">
         <is>
-          <t>I'm {advisor}, an art advisor at Avant Arte. I'm here to connect collectors with artists by making suggestions, answering questions and offering early access to our collaborations.</t>
+          <t>Any questions? Reply to this email.</t>
         </is>
       </c>
       <c r="C81" s="10">
-        <f>SUBSTITUTE(B81,"{advisor}",Inputs!$B$24)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="82" ht="32" customHeight="1">
+        <f>B81</f>
+        <v/>
+      </c>
+    </row>
+    <row r="82" ht="48" customHeight="1">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>email · first-time survey · 3</t>
+          <t>email · non-purchaser survey · 1</t>
         </is>
       </c>
       <c r="B82" s="8" t="inlineStr">
         <is>
-          <t>If you have two minutes to complete a short survey about your collecting journey to date, your responses will help guide my recommendations.</t>
+          <t>As someone who registered for updates but ultimately decided not to enter the draw for our collaboration with {collab_with}, we'd love your feedback.</t>
         </is>
       </c>
       <c r="C82" s="10">
-        <f>B82</f>
-        <v/>
-      </c>
-    </row>
-    <row r="83" ht="16" customHeight="1">
+        <f>SUBSTITUTE(B82,"{collab_with}",Inputs!$B$5)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="83" ht="32" customHeight="1">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>email · first-time survey · 4</t>
+          <t>email · non-purchaser survey · 2</t>
         </is>
       </c>
       <c r="B83" s="8" t="inlineStr">
         <is>
-          <t>Any questions? Reply to this email.</t>
+          <t>This two-minute survey will guide our future collaborations and help us recommend the right artists and editions for your collection.</t>
         </is>
       </c>
       <c r="C83" s="10">
@@ -2777,28 +2777,28 @@
     <row r="84" ht="48" customHeight="1">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>email · non-purchaser survey · 1</t>
+          <t>email · non-purchaser survey · 3</t>
         </is>
       </c>
       <c r="B84" s="8" t="inlineStr">
         <is>
-          <t>As someone who registered for updates but ultimately decided not to enter the draw for our collaboration with {collab_with}, we'd love your feedback.</t>
+          <t>As a thank you for taking part in the survey and helping us improve the collector experience, you'll be entered into a draw to win a €500 Avant Arte gift card.</t>
         </is>
       </c>
       <c r="C84" s="10">
-        <f>SUBSTITUTE(B84,"{collab_with}",Inputs!$B$5)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="85" ht="32" customHeight="1">
+        <f>B84</f>
+        <v/>
+      </c>
+    </row>
+    <row r="85" ht="16" customHeight="1">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>email · non-purchaser survey · 2</t>
+          <t>email · non-purchaser survey · terms</t>
         </is>
       </c>
       <c r="B85" s="8" t="inlineStr">
         <is>
-          <t>This two-minute survey will guide our future collaborations and help us recommend the right artists and editions for your collection.</t>
+          <t>You can read the terms here.</t>
         </is>
       </c>
       <c r="C85" s="10">
@@ -2806,106 +2806,58 @@
         <v/>
       </c>
     </row>
-    <row r="86" ht="48" customHeight="1">
-      <c r="A86" s="4" t="inlineStr">
-        <is>
-          <t>email · non-purchaser survey · 3</t>
-        </is>
-      </c>
-      <c r="B86" s="8" t="inlineStr">
-        <is>
-          <t>As a thank you for taking part in the survey and helping us improve the collector experience, you'll be entered into a draw to win a €500 Avant Arte gift card.</t>
-        </is>
-      </c>
-      <c r="C86" s="10">
-        <f>B86</f>
-        <v/>
+    <row r="86">
+      <c r="A86" s="3" t="inlineStr">
+        <is>
+          <t>EMAILS · monthly preview</t>
+        </is>
       </c>
     </row>
     <row r="87" ht="16" customHeight="1">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>email · non-purchaser survey · terms</t>
+          <t>email · monthly preview · opener</t>
         </is>
       </c>
       <c r="B87" s="8" t="inlineStr">
         <is>
-          <t>You can read the terms here.</t>
+          <t>From {collab_with} comes {work_intro}{support}.</t>
         </is>
       </c>
       <c r="C87" s="10">
-        <f>B87</f>
-        <v/>
-      </c>
-    </row>
-    <row r="88" ht="16" customHeight="1">
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B87,"{collab_with}",Inputs!$B$5),"{work_intro}",Inputs!$B$54),"{support}",Inputs!$B$55)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="88" ht="32" customHeight="1">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>email · non-purchaser survey · footer</t>
+          <t>email · monthly preview · when, draw</t>
         </is>
       </c>
       <c r="B88" s="8" t="inlineStr">
         <is>
-          <t>What can we do better?</t>
+          <t>The edition will be allocated by a randomised draw, which closes at {close_time} on {close_date}.</t>
         </is>
       </c>
       <c r="C88" s="10">
-        <f>B88</f>
-        <v/>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="3" t="inlineStr">
-        <is>
-          <t>EMAILS · monthly preview</t>
-        </is>
-      </c>
-    </row>
-    <row r="90" ht="16" customHeight="1">
-      <c r="A90" s="4" t="inlineStr">
-        <is>
-          <t>email · monthly preview · opener</t>
-        </is>
-      </c>
-      <c r="B90" s="8" t="inlineStr">
-        <is>
-          <t>From {collab_with} comes {work_intro}{support}.</t>
-        </is>
-      </c>
-      <c r="C90" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B90,"{collab_with}",Inputs!$B$5),"{work_intro}",Inputs!$B$54),"{support}",Inputs!$B$55)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="91" ht="32" customHeight="1">
-      <c r="A91" s="4" t="inlineStr">
-        <is>
-          <t>email · monthly preview · when, draw</t>
-        </is>
-      </c>
-      <c r="B91" s="8" t="inlineStr">
-        <is>
-          <t>The edition will be allocated by a randomised draw, which closes at {close_time} on {close_date}.</t>
-        </is>
-      </c>
-      <c r="C91" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(B91,"{close_date}",Inputs!$B$70),"{close_time}",Inputs!$B$71)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="92" ht="32" customHeight="1">
-      <c r="A92" s="4" t="inlineStr">
+        <f>SUBSTITUTE(SUBSTITUTE(B88,"{close_date}",Inputs!$B$70),"{close_time}",Inputs!$B$71)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="89" ht="32" customHeight="1">
+      <c r="A89" s="4" t="inlineStr">
         <is>
           <t>email · monthly preview · when, timed</t>
         </is>
       </c>
-      <c r="B92" s="8" t="inlineStr">
+      <c r="B89" s="8" t="inlineStr">
         <is>
           <t>The edition will be available to collect for {window} only, from {launch_time} on {launch_weekday}, {launch_date_dd}.</t>
         </is>
       </c>
-      <c r="C92" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B92,"{window}",Inputs!$B$19),"{launch_time}",Inputs!$B$67),"{launch_weekday}",Inputs!$B$68),"{launch_date_dd}",Inputs!$B$69)</f>
+      <c r="C89" s="10">
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B89,"{window}",Inputs!$B$19),"{launch_time}",Inputs!$B$67),"{launch_weekday}",Inputs!$B$68),"{launch_date_dd}",Inputs!$B$69)</f>
         <v/>
       </c>
     </row>
@@ -3635,7 +3587,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O17"/>
+  <dimension ref="A1:N17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -3650,9 +3602,8 @@
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="30" customWidth="1" min="11" max="11"/>
     <col width="34" customWidth="1" min="12" max="12"/>
-    <col width="26" customWidth="1" min="13" max="13"/>
-    <col width="96" customWidth="1" min="14" max="14"/>
-    <col width="11" customWidth="1" min="15" max="15"/>
+    <col width="96" customWidth="1" min="13" max="13"/>
+    <col width="11" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3732,15 +3683,10 @@
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>Footer</t>
+          <t>Full email, ready to paste</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
-        <is>
-          <t>Full email, ready to paste</t>
-        </is>
-      </c>
-      <c r="O3" s="3" t="inlineStr">
         <is>
           <t>Characters</t>
         </is>
@@ -3797,15 +3743,11 @@
         <v/>
       </c>
       <c r="M4" s="11">
-        <f>IF($D4&lt;&gt;"yes","",IF(Inputs!$B$18="draw","Collect "&amp;Inputs!$B$74,"Launching "&amp;Inputs!$B$66))</f>
+        <f>IF(D4&lt;&gt;"yes",D4,IF(E4="","","Subject: "&amp;E4)&amp;IF(F4="","",CHAR(10)&amp;"Preview: "&amp;F4)&amp;IF(G4="","",CHAR(10)&amp;"Kicker: "&amp;G4)&amp;IF(H4="","",CHAR(10)&amp;"Headline: "&amp;H4)&amp;IF(I4="","",IF(E4&amp;F4&amp;G4&amp;H4="","",CHAR(10)&amp;CHAR(10))&amp;I4)&amp;IF(J4="","",CHAR(10)&amp;CHAR(10)&amp;"CTA: "&amp;J4)&amp;IF(K4="","",CHAR(10)&amp;CHAR(10)&amp;"Card: "&amp;K4)&amp;IF(L4="","",CHAR(10)&amp;CHAR(10)&amp;"Quote: "&amp;L4))</f>
         <v/>
       </c>
       <c r="N4" s="11">
-        <f>IF(D4&lt;&gt;"yes",D4,IF(E4="","","Subject: "&amp;E4)&amp;IF(F4="","",CHAR(10)&amp;"Preview: "&amp;F4)&amp;IF(G4="","",CHAR(10)&amp;"Kicker: "&amp;G4)&amp;IF(H4="","",CHAR(10)&amp;"Headline: "&amp;H4)&amp;IF(I4="","",IF(E4&amp;F4&amp;G4&amp;H4="","",CHAR(10)&amp;CHAR(10))&amp;I4)&amp;IF(J4="","",CHAR(10)&amp;CHAR(10)&amp;"CTA: "&amp;J4)&amp;IF(K4="","",CHAR(10)&amp;CHAR(10)&amp;"Card: "&amp;K4)&amp;IF(L4="","",CHAR(10)&amp;CHAR(10)&amp;"Quote: "&amp;L4)&amp;IF(M4="","",CHAR(10)&amp;CHAR(10)&amp;"Footer: "&amp;M4))</f>
-        <v/>
-      </c>
-      <c r="O4" s="11">
-        <f>LEN(N4)</f>
+        <f>LEN(M4)</f>
         <v/>
       </c>
     </row>
@@ -3860,15 +3802,11 @@
         <v/>
       </c>
       <c r="M5" s="11">
-        <f>IF($D5&lt;&gt;"yes","","Where the art world is more accessible")</f>
+        <f>IF(D5&lt;&gt;"yes",D5,IF(E5="","","Subject: "&amp;E5)&amp;IF(F5="","",CHAR(10)&amp;"Preview: "&amp;F5)&amp;IF(G5="","",CHAR(10)&amp;"Kicker: "&amp;G5)&amp;IF(H5="","",CHAR(10)&amp;"Headline: "&amp;H5)&amp;IF(I5="","",IF(E5&amp;F5&amp;G5&amp;H5="","",CHAR(10)&amp;CHAR(10))&amp;I5)&amp;IF(J5="","",CHAR(10)&amp;CHAR(10)&amp;"CTA: "&amp;J5)&amp;IF(K5="","",CHAR(10)&amp;CHAR(10)&amp;"Card: "&amp;K5)&amp;IF(L5="","",CHAR(10)&amp;CHAR(10)&amp;"Quote: "&amp;L5))</f>
         <v/>
       </c>
       <c r="N5" s="11">
-        <f>IF(D5&lt;&gt;"yes",D5,IF(E5="","","Subject: "&amp;E5)&amp;IF(F5="","",CHAR(10)&amp;"Preview: "&amp;F5)&amp;IF(G5="","",CHAR(10)&amp;"Kicker: "&amp;G5)&amp;IF(H5="","",CHAR(10)&amp;"Headline: "&amp;H5)&amp;IF(I5="","",IF(E5&amp;F5&amp;G5&amp;H5="","",CHAR(10)&amp;CHAR(10))&amp;I5)&amp;IF(J5="","",CHAR(10)&amp;CHAR(10)&amp;"CTA: "&amp;J5)&amp;IF(K5="","",CHAR(10)&amp;CHAR(10)&amp;"Card: "&amp;K5)&amp;IF(L5="","",CHAR(10)&amp;CHAR(10)&amp;"Quote: "&amp;L5)&amp;IF(M5="","",CHAR(10)&amp;CHAR(10)&amp;"Footer: "&amp;M5))</f>
-        <v/>
-      </c>
-      <c r="O5" s="11">
-        <f>LEN(N5)</f>
+        <f>LEN(M5)</f>
         <v/>
       </c>
     </row>
@@ -3923,15 +3861,11 @@
         <v/>
       </c>
       <c r="M6" s="11">
-        <f>IF($D6&lt;&gt;"yes","","24 hours ahead of the public launch")</f>
+        <f>IF(D6&lt;&gt;"yes",D6,IF(E6="","","Subject: "&amp;E6)&amp;IF(F6="","",CHAR(10)&amp;"Preview: "&amp;F6)&amp;IF(G6="","",CHAR(10)&amp;"Kicker: "&amp;G6)&amp;IF(H6="","",CHAR(10)&amp;"Headline: "&amp;H6)&amp;IF(I6="","",IF(E6&amp;F6&amp;G6&amp;H6="","",CHAR(10)&amp;CHAR(10))&amp;I6)&amp;IF(J6="","",CHAR(10)&amp;CHAR(10)&amp;"CTA: "&amp;J6)&amp;IF(K6="","",CHAR(10)&amp;CHAR(10)&amp;"Card: "&amp;K6)&amp;IF(L6="","",CHAR(10)&amp;CHAR(10)&amp;"Quote: "&amp;L6))</f>
         <v/>
       </c>
       <c r="N6" s="11">
-        <f>IF(D6&lt;&gt;"yes",D6,IF(E6="","","Subject: "&amp;E6)&amp;IF(F6="","",CHAR(10)&amp;"Preview: "&amp;F6)&amp;IF(G6="","",CHAR(10)&amp;"Kicker: "&amp;G6)&amp;IF(H6="","",CHAR(10)&amp;"Headline: "&amp;H6)&amp;IF(I6="","",IF(E6&amp;F6&amp;G6&amp;H6="","",CHAR(10)&amp;CHAR(10))&amp;I6)&amp;IF(J6="","",CHAR(10)&amp;CHAR(10)&amp;"CTA: "&amp;J6)&amp;IF(K6="","",CHAR(10)&amp;CHAR(10)&amp;"Card: "&amp;K6)&amp;IF(L6="","",CHAR(10)&amp;CHAR(10)&amp;"Quote: "&amp;L6)&amp;IF(M6="","",CHAR(10)&amp;CHAR(10)&amp;"Footer: "&amp;M6))</f>
-        <v/>
-      </c>
-      <c r="O6" s="11">
-        <f>LEN(N6)</f>
+        <f>LEN(M6)</f>
         <v/>
       </c>
     </row>
@@ -3986,15 +3920,11 @@
         <v/>
       </c>
       <c r="M7" s="11">
-        <f>IF($D7&lt;&gt;"yes","","24 hours ahead of the public launch")</f>
+        <f>IF(D7&lt;&gt;"yes",D7,IF(E7="","","Subject: "&amp;E7)&amp;IF(F7="","",CHAR(10)&amp;"Preview: "&amp;F7)&amp;IF(G7="","",CHAR(10)&amp;"Kicker: "&amp;G7)&amp;IF(H7="","",CHAR(10)&amp;"Headline: "&amp;H7)&amp;IF(I7="","",IF(E7&amp;F7&amp;G7&amp;H7="","",CHAR(10)&amp;CHAR(10))&amp;I7)&amp;IF(J7="","",CHAR(10)&amp;CHAR(10)&amp;"CTA: "&amp;J7)&amp;IF(K7="","",CHAR(10)&amp;CHAR(10)&amp;"Card: "&amp;K7)&amp;IF(L7="","",CHAR(10)&amp;CHAR(10)&amp;"Quote: "&amp;L7))</f>
         <v/>
       </c>
       <c r="N7" s="11">
-        <f>IF(D7&lt;&gt;"yes",D7,IF(E7="","","Subject: "&amp;E7)&amp;IF(F7="","",CHAR(10)&amp;"Preview: "&amp;F7)&amp;IF(G7="","",CHAR(10)&amp;"Kicker: "&amp;G7)&amp;IF(H7="","",CHAR(10)&amp;"Headline: "&amp;H7)&amp;IF(I7="","",IF(E7&amp;F7&amp;G7&amp;H7="","",CHAR(10)&amp;CHAR(10))&amp;I7)&amp;IF(J7="","",CHAR(10)&amp;CHAR(10)&amp;"CTA: "&amp;J7)&amp;IF(K7="","",CHAR(10)&amp;CHAR(10)&amp;"Card: "&amp;K7)&amp;IF(L7="","",CHAR(10)&amp;CHAR(10)&amp;"Quote: "&amp;L7)&amp;IF(M7="","",CHAR(10)&amp;CHAR(10)&amp;"Footer: "&amp;M7))</f>
-        <v/>
-      </c>
-      <c r="O7" s="11">
-        <f>LEN(N7)</f>
+        <f>LEN(M7)</f>
         <v/>
       </c>
     </row>
@@ -4049,15 +3979,11 @@
         <v/>
       </c>
       <c r="M8" s="11">
-        <f>IF($D8&lt;&gt;"yes","",IF(Inputs!$B$18="draw","Especially for you.","24 hours ahead of the public launch"))</f>
+        <f>IF(D8&lt;&gt;"yes",D8,IF(E8="","","Subject: "&amp;E8)&amp;IF(F8="","",CHAR(10)&amp;"Preview: "&amp;F8)&amp;IF(G8="","",CHAR(10)&amp;"Kicker: "&amp;G8)&amp;IF(H8="","",CHAR(10)&amp;"Headline: "&amp;H8)&amp;IF(I8="","",IF(E8&amp;F8&amp;G8&amp;H8="","",CHAR(10)&amp;CHAR(10))&amp;I8)&amp;IF(J8="","",CHAR(10)&amp;CHAR(10)&amp;"CTA: "&amp;J8)&amp;IF(K8="","",CHAR(10)&amp;CHAR(10)&amp;"Card: "&amp;K8)&amp;IF(L8="","",CHAR(10)&amp;CHAR(10)&amp;"Quote: "&amp;L8))</f>
         <v/>
       </c>
       <c r="N8" s="11">
-        <f>IF(D8&lt;&gt;"yes",D8,IF(E8="","","Subject: "&amp;E8)&amp;IF(F8="","",CHAR(10)&amp;"Preview: "&amp;F8)&amp;IF(G8="","",CHAR(10)&amp;"Kicker: "&amp;G8)&amp;IF(H8="","",CHAR(10)&amp;"Headline: "&amp;H8)&amp;IF(I8="","",IF(E8&amp;F8&amp;G8&amp;H8="","",CHAR(10)&amp;CHAR(10))&amp;I8)&amp;IF(J8="","",CHAR(10)&amp;CHAR(10)&amp;"CTA: "&amp;J8)&amp;IF(K8="","",CHAR(10)&amp;CHAR(10)&amp;"Card: "&amp;K8)&amp;IF(L8="","",CHAR(10)&amp;CHAR(10)&amp;"Quote: "&amp;L8)&amp;IF(M8="","",CHAR(10)&amp;CHAR(10)&amp;"Footer: "&amp;M8))</f>
-        <v/>
-      </c>
-      <c r="O8" s="11">
-        <f>LEN(N8)</f>
+        <f>LEN(M8)</f>
         <v/>
       </c>
     </row>
@@ -4112,15 +4038,11 @@
         <v/>
       </c>
       <c r="M9" s="11">
-        <f>IF($D9&lt;&gt;"yes","","Especially for you.")</f>
+        <f>IF(D9&lt;&gt;"yes",D9,IF(E9="","","Subject: "&amp;E9)&amp;IF(F9="","",CHAR(10)&amp;"Preview: "&amp;F9)&amp;IF(G9="","",CHAR(10)&amp;"Kicker: "&amp;G9)&amp;IF(H9="","",CHAR(10)&amp;"Headline: "&amp;H9)&amp;IF(I9="","",IF(E9&amp;F9&amp;G9&amp;H9="","",CHAR(10)&amp;CHAR(10))&amp;I9)&amp;IF(J9="","",CHAR(10)&amp;CHAR(10)&amp;"CTA: "&amp;J9)&amp;IF(K9="","",CHAR(10)&amp;CHAR(10)&amp;"Card: "&amp;K9)&amp;IF(L9="","",CHAR(10)&amp;CHAR(10)&amp;"Quote: "&amp;L9))</f>
         <v/>
       </c>
       <c r="N9" s="11">
-        <f>IF(D9&lt;&gt;"yes",D9,IF(E9="","","Subject: "&amp;E9)&amp;IF(F9="","",CHAR(10)&amp;"Preview: "&amp;F9)&amp;IF(G9="","",CHAR(10)&amp;"Kicker: "&amp;G9)&amp;IF(H9="","",CHAR(10)&amp;"Headline: "&amp;H9)&amp;IF(I9="","",IF(E9&amp;F9&amp;G9&amp;H9="","",CHAR(10)&amp;CHAR(10))&amp;I9)&amp;IF(J9="","",CHAR(10)&amp;CHAR(10)&amp;"CTA: "&amp;J9)&amp;IF(K9="","",CHAR(10)&amp;CHAR(10)&amp;"Card: "&amp;K9)&amp;IF(L9="","",CHAR(10)&amp;CHAR(10)&amp;"Quote: "&amp;L9)&amp;IF(M9="","",CHAR(10)&amp;CHAR(10)&amp;"Footer: "&amp;M9))</f>
-        <v/>
-      </c>
-      <c r="O9" s="11">
-        <f>LEN(N9)</f>
+        <f>LEN(M9)</f>
         <v/>
       </c>
     </row>
@@ -4175,15 +4097,11 @@
         <v/>
       </c>
       <c r="M10" s="11">
-        <f>IF($D10&lt;&gt;"yes","","Collect "&amp;Inputs!$B$74)</f>
+        <f>IF(D10&lt;&gt;"yes",D10,IF(E10="","","Subject: "&amp;E10)&amp;IF(F10="","",CHAR(10)&amp;"Preview: "&amp;F10)&amp;IF(G10="","",CHAR(10)&amp;"Kicker: "&amp;G10)&amp;IF(H10="","",CHAR(10)&amp;"Headline: "&amp;H10)&amp;IF(I10="","",IF(E10&amp;F10&amp;G10&amp;H10="","",CHAR(10)&amp;CHAR(10))&amp;I10)&amp;IF(J10="","",CHAR(10)&amp;CHAR(10)&amp;"CTA: "&amp;J10)&amp;IF(K10="","",CHAR(10)&amp;CHAR(10)&amp;"Card: "&amp;K10)&amp;IF(L10="","",CHAR(10)&amp;CHAR(10)&amp;"Quote: "&amp;L10))</f>
         <v/>
       </c>
       <c r="N10" s="11">
-        <f>IF(D10&lt;&gt;"yes",D10,IF(E10="","","Subject: "&amp;E10)&amp;IF(F10="","",CHAR(10)&amp;"Preview: "&amp;F10)&amp;IF(G10="","",CHAR(10)&amp;"Kicker: "&amp;G10)&amp;IF(H10="","",CHAR(10)&amp;"Headline: "&amp;H10)&amp;IF(I10="","",IF(E10&amp;F10&amp;G10&amp;H10="","",CHAR(10)&amp;CHAR(10))&amp;I10)&amp;IF(J10="","",CHAR(10)&amp;CHAR(10)&amp;"CTA: "&amp;J10)&amp;IF(K10="","",CHAR(10)&amp;CHAR(10)&amp;"Card: "&amp;K10)&amp;IF(L10="","",CHAR(10)&amp;CHAR(10)&amp;"Quote: "&amp;L10)&amp;IF(M10="","",CHAR(10)&amp;CHAR(10)&amp;"Footer: "&amp;M10))</f>
-        <v/>
-      </c>
-      <c r="O10" s="11">
-        <f>LEN(N10)</f>
+        <f>LEN(M10)</f>
         <v/>
       </c>
     </row>
@@ -4238,15 +4156,11 @@
         <v/>
       </c>
       <c r="M11" s="11">
-        <f>IF($D11&lt;&gt;"yes","",Lines!$C$67)</f>
+        <f>IF(D11&lt;&gt;"yes",D11,IF(E11="","","Subject: "&amp;E11)&amp;IF(F11="","",CHAR(10)&amp;"Preview: "&amp;F11)&amp;IF(G11="","",CHAR(10)&amp;"Kicker: "&amp;G11)&amp;IF(H11="","",CHAR(10)&amp;"Headline: "&amp;H11)&amp;IF(I11="","",IF(E11&amp;F11&amp;G11&amp;H11="","",CHAR(10)&amp;CHAR(10))&amp;I11)&amp;IF(J11="","",CHAR(10)&amp;CHAR(10)&amp;"CTA: "&amp;J11)&amp;IF(K11="","",CHAR(10)&amp;CHAR(10)&amp;"Card: "&amp;K11)&amp;IF(L11="","",CHAR(10)&amp;CHAR(10)&amp;"Quote: "&amp;L11))</f>
         <v/>
       </c>
       <c r="N11" s="11">
-        <f>IF(D11&lt;&gt;"yes",D11,IF(E11="","","Subject: "&amp;E11)&amp;IF(F11="","",CHAR(10)&amp;"Preview: "&amp;F11)&amp;IF(G11="","",CHAR(10)&amp;"Kicker: "&amp;G11)&amp;IF(H11="","",CHAR(10)&amp;"Headline: "&amp;H11)&amp;IF(I11="","",IF(E11&amp;F11&amp;G11&amp;H11="","",CHAR(10)&amp;CHAR(10))&amp;I11)&amp;IF(J11="","",CHAR(10)&amp;CHAR(10)&amp;"CTA: "&amp;J11)&amp;IF(K11="","",CHAR(10)&amp;CHAR(10)&amp;"Card: "&amp;K11)&amp;IF(L11="","",CHAR(10)&amp;CHAR(10)&amp;"Quote: "&amp;L11)&amp;IF(M11="","",CHAR(10)&amp;CHAR(10)&amp;"Footer: "&amp;M11))</f>
-        <v/>
-      </c>
-      <c r="O11" s="11">
-        <f>LEN(N11)</f>
+        <f>LEN(M11)</f>
         <v/>
       </c>
     </row>
@@ -4281,7 +4195,7 @@
         <v/>
       </c>
       <c r="H12" s="11">
-        <f>IF($D12&lt;&gt;"yes","",Lines!$C$68)</f>
+        <f>IF($D12&lt;&gt;"yes","",Lines!$C$67)</f>
         <v/>
       </c>
       <c r="I12" s="11">
@@ -4301,15 +4215,11 @@
         <v/>
       </c>
       <c r="M12" s="11">
-        <f>IF($D12&lt;&gt;"yes","",Lines!$C$72)</f>
+        <f>IF(D12&lt;&gt;"yes",D12,IF(E12="","","Subject: "&amp;E12)&amp;IF(F12="","",CHAR(10)&amp;"Preview: "&amp;F12)&amp;IF(G12="","",CHAR(10)&amp;"Kicker: "&amp;G12)&amp;IF(H12="","",CHAR(10)&amp;"Headline: "&amp;H12)&amp;IF(I12="","",IF(E12&amp;F12&amp;G12&amp;H12="","",CHAR(10)&amp;CHAR(10))&amp;I12)&amp;IF(J12="","",CHAR(10)&amp;CHAR(10)&amp;"CTA: "&amp;J12)&amp;IF(K12="","",CHAR(10)&amp;CHAR(10)&amp;"Card: "&amp;K12)&amp;IF(L12="","",CHAR(10)&amp;CHAR(10)&amp;"Quote: "&amp;L12))</f>
         <v/>
       </c>
       <c r="N12" s="11">
-        <f>IF(D12&lt;&gt;"yes",D12,IF(E12="","","Subject: "&amp;E12)&amp;IF(F12="","",CHAR(10)&amp;"Preview: "&amp;F12)&amp;IF(G12="","",CHAR(10)&amp;"Kicker: "&amp;G12)&amp;IF(H12="","",CHAR(10)&amp;"Headline: "&amp;H12)&amp;IF(I12="","",IF(E12&amp;F12&amp;G12&amp;H12="","",CHAR(10)&amp;CHAR(10))&amp;I12)&amp;IF(J12="","",CHAR(10)&amp;CHAR(10)&amp;"CTA: "&amp;J12)&amp;IF(K12="","",CHAR(10)&amp;CHAR(10)&amp;"Card: "&amp;K12)&amp;IF(L12="","",CHAR(10)&amp;CHAR(10)&amp;"Quote: "&amp;L12)&amp;IF(M12="","",CHAR(10)&amp;CHAR(10)&amp;"Footer: "&amp;M12))</f>
-        <v/>
-      </c>
-      <c r="O12" s="11">
-        <f>LEN(N12)</f>
+        <f>LEN(M12)</f>
         <v/>
       </c>
     </row>
@@ -4344,11 +4254,11 @@
         <v/>
       </c>
       <c r="H13" s="11">
-        <f>IF($D13&lt;&gt;"yes","",Lines!$C$69)</f>
+        <f>IF($D13&lt;&gt;"yes","",Lines!$C$68)</f>
         <v/>
       </c>
       <c r="I13" s="11">
-        <f>IF($D13&lt;&gt;"yes","",(Lines!$C$70&amp;IF(Inputs!$B$36="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$36)&amp;IF(Lines!$C$71="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$71)&amp;IF(IF(Inputs!$B$26="","",Lines!$C$38)="","",CHAR(10)&amp;CHAR(10)&amp;IF(Inputs!$B$26="","",Lines!$C$38))))</f>
+        <f>IF($D13&lt;&gt;"yes","",(Lines!$C$69&amp;IF(Inputs!$B$36="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$36)&amp;IF(Lines!$C$70="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$70)&amp;IF(IF(Inputs!$B$26="","",Lines!$C$38)="","",CHAR(10)&amp;CHAR(10)&amp;IF(Inputs!$B$26="","",Lines!$C$38))))</f>
         <v/>
       </c>
       <c r="J13" s="11">
@@ -4364,15 +4274,11 @@
         <v/>
       </c>
       <c r="M13" s="11">
-        <f>IF($D13&lt;&gt;"yes","",Lines!$C$72)</f>
+        <f>IF(D13&lt;&gt;"yes",D13,IF(E13="","","Subject: "&amp;E13)&amp;IF(F13="","",CHAR(10)&amp;"Preview: "&amp;F13)&amp;IF(G13="","",CHAR(10)&amp;"Kicker: "&amp;G13)&amp;IF(H13="","",CHAR(10)&amp;"Headline: "&amp;H13)&amp;IF(I13="","",IF(E13&amp;F13&amp;G13&amp;H13="","",CHAR(10)&amp;CHAR(10))&amp;I13)&amp;IF(J13="","",CHAR(10)&amp;CHAR(10)&amp;"CTA: "&amp;J13)&amp;IF(K13="","",CHAR(10)&amp;CHAR(10)&amp;"Card: "&amp;K13)&amp;IF(L13="","",CHAR(10)&amp;CHAR(10)&amp;"Quote: "&amp;L13))</f>
         <v/>
       </c>
       <c r="N13" s="11">
-        <f>IF(D13&lt;&gt;"yes",D13,IF(E13="","","Subject: "&amp;E13)&amp;IF(F13="","",CHAR(10)&amp;"Preview: "&amp;F13)&amp;IF(G13="","",CHAR(10)&amp;"Kicker: "&amp;G13)&amp;IF(H13="","",CHAR(10)&amp;"Headline: "&amp;H13)&amp;IF(I13="","",IF(E13&amp;F13&amp;G13&amp;H13="","",CHAR(10)&amp;CHAR(10))&amp;I13)&amp;IF(J13="","",CHAR(10)&amp;CHAR(10)&amp;"CTA: "&amp;J13)&amp;IF(K13="","",CHAR(10)&amp;CHAR(10)&amp;"Card: "&amp;K13)&amp;IF(L13="","",CHAR(10)&amp;CHAR(10)&amp;"Quote: "&amp;L13)&amp;IF(M13="","",CHAR(10)&amp;CHAR(10)&amp;"Footer: "&amp;M13))</f>
-        <v/>
-      </c>
-      <c r="O13" s="11">
-        <f>LEN(N13)</f>
+        <f>LEN(M13)</f>
         <v/>
       </c>
     </row>
@@ -4411,7 +4317,7 @@
         <v/>
       </c>
       <c r="I14" s="11">
-        <f>IF($D14&lt;&gt;"yes","",IF(Inputs!$B$18="draw",(Lines!$C$76&amp;IF(Inputs!$B$36="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$36)&amp;IF(Lines!$C$77="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$77)),(Lines!$C$74&amp;IF(Lines!$C$75="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$75)&amp;IF(IF(Inputs!$B$26="","",Lines!$C$38)="","",CHAR(10)&amp;CHAR(10)&amp;IF(Inputs!$B$26="","",Lines!$C$38)))))</f>
+        <f>IF($D14&lt;&gt;"yes","",IF(Inputs!$B$18="draw",(Lines!$C$74&amp;IF(Inputs!$B$36="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$36)&amp;IF(Lines!$C$75="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$75)),(Lines!$C$72&amp;IF(Lines!$C$73="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$73)&amp;IF(IF(Inputs!$B$26="","",Lines!$C$38)="","",CHAR(10)&amp;CHAR(10)&amp;IF(Inputs!$B$26="","",Lines!$C$38)))))</f>
         <v/>
       </c>
       <c r="J14" s="11">
@@ -4427,15 +4333,11 @@
         <v/>
       </c>
       <c r="M14" s="11">
-        <f>IF($D14&lt;&gt;"yes","","Time is almost up")</f>
+        <f>IF(D14&lt;&gt;"yes",D14,IF(E14="","","Subject: "&amp;E14)&amp;IF(F14="","",CHAR(10)&amp;"Preview: "&amp;F14)&amp;IF(G14="","",CHAR(10)&amp;"Kicker: "&amp;G14)&amp;IF(H14="","",CHAR(10)&amp;"Headline: "&amp;H14)&amp;IF(I14="","",IF(E14&amp;F14&amp;G14&amp;H14="","",CHAR(10)&amp;CHAR(10))&amp;I14)&amp;IF(J14="","",CHAR(10)&amp;CHAR(10)&amp;"CTA: "&amp;J14)&amp;IF(K14="","",CHAR(10)&amp;CHAR(10)&amp;"Card: "&amp;K14)&amp;IF(L14="","",CHAR(10)&amp;CHAR(10)&amp;"Quote: "&amp;L14))</f>
         <v/>
       </c>
       <c r="N14" s="11">
-        <f>IF(D14&lt;&gt;"yes",D14,IF(E14="","","Subject: "&amp;E14)&amp;IF(F14="","",CHAR(10)&amp;"Preview: "&amp;F14)&amp;IF(G14="","",CHAR(10)&amp;"Kicker: "&amp;G14)&amp;IF(H14="","",CHAR(10)&amp;"Headline: "&amp;H14)&amp;IF(I14="","",IF(E14&amp;F14&amp;G14&amp;H14="","",CHAR(10)&amp;CHAR(10))&amp;I14)&amp;IF(J14="","",CHAR(10)&amp;CHAR(10)&amp;"CTA: "&amp;J14)&amp;IF(K14="","",CHAR(10)&amp;CHAR(10)&amp;"Card: "&amp;K14)&amp;IF(L14="","",CHAR(10)&amp;CHAR(10)&amp;"Quote: "&amp;L14)&amp;IF(M14="","",CHAR(10)&amp;CHAR(10)&amp;"Footer: "&amp;M14))</f>
-        <v/>
-      </c>
-      <c r="O14" s="11">
-        <f>LEN(N14)</f>
+        <f>LEN(M14)</f>
         <v/>
       </c>
     </row>
@@ -4458,7 +4360,7 @@
         <v/>
       </c>
       <c r="E15" s="11">
-        <f>IF($D15&lt;&gt;"yes","",Lines!$C$79)</f>
+        <f>IF($D15&lt;&gt;"yes","",Lines!$C$77)</f>
         <v/>
       </c>
       <c r="F15" s="11">
@@ -4474,7 +4376,7 @@
         <v/>
       </c>
       <c r="I15" s="11">
-        <f>IF($D15&lt;&gt;"yes","",(Lines!$C$32&amp;IF(Lines!$C$80="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$80)&amp;IF(Lines!$C$81="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$81)&amp;IF(Lines!$C$82="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$82)&amp;IF(Lines!$C$83="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$83)))</f>
+        <f>IF($D15&lt;&gt;"yes","",(Lines!$C$32&amp;IF(Lines!$C$78="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$78)&amp;IF(Lines!$C$79="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$79)&amp;IF(Lines!$C$80="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$80)&amp;IF(Lines!$C$81="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$81)))</f>
         <v/>
       </c>
       <c r="J15" s="11">
@@ -4490,15 +4392,11 @@
         <v/>
       </c>
       <c r="M15" s="11">
-        <f>""</f>
+        <f>IF(D15&lt;&gt;"yes",D15,IF(E15="","","Subject: "&amp;E15)&amp;IF(F15="","",CHAR(10)&amp;"Preview: "&amp;F15)&amp;IF(G15="","",CHAR(10)&amp;"Kicker: "&amp;G15)&amp;IF(H15="","",CHAR(10)&amp;"Headline: "&amp;H15)&amp;IF(I15="","",IF(E15&amp;F15&amp;G15&amp;H15="","",CHAR(10)&amp;CHAR(10))&amp;I15)&amp;IF(J15="","",CHAR(10)&amp;CHAR(10)&amp;"CTA: "&amp;J15)&amp;IF(K15="","",CHAR(10)&amp;CHAR(10)&amp;"Card: "&amp;K15)&amp;IF(L15="","",CHAR(10)&amp;CHAR(10)&amp;"Quote: "&amp;L15))</f>
         <v/>
       </c>
       <c r="N15" s="11">
-        <f>IF(D15&lt;&gt;"yes",D15,IF(E15="","","Subject: "&amp;E15)&amp;IF(F15="","",CHAR(10)&amp;"Preview: "&amp;F15)&amp;IF(G15="","",CHAR(10)&amp;"Kicker: "&amp;G15)&amp;IF(H15="","",CHAR(10)&amp;"Headline: "&amp;H15)&amp;IF(I15="","",IF(E15&amp;F15&amp;G15&amp;H15="","",CHAR(10)&amp;CHAR(10))&amp;I15)&amp;IF(J15="","",CHAR(10)&amp;CHAR(10)&amp;"CTA: "&amp;J15)&amp;IF(K15="","",CHAR(10)&amp;CHAR(10)&amp;"Card: "&amp;K15)&amp;IF(L15="","",CHAR(10)&amp;CHAR(10)&amp;"Quote: "&amp;L15)&amp;IF(M15="","",CHAR(10)&amp;CHAR(10)&amp;"Footer: "&amp;M15))</f>
-        <v/>
-      </c>
-      <c r="O15" s="11">
-        <f>LEN(N15)</f>
+        <f>LEN(M15)</f>
         <v/>
       </c>
     </row>
@@ -4537,7 +4435,7 @@
         <v/>
       </c>
       <c r="I16" s="11">
-        <f>IF($D16&lt;&gt;"yes","",(Lines!$C$84&amp;IF(Lines!$C$85="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$85)&amp;IF(Lines!$C$86="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$86)&amp;IF(Lines!$C$87="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$87)))</f>
+        <f>IF($D16&lt;&gt;"yes","",(Lines!$C$82&amp;IF(Lines!$C$83="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$83)&amp;IF(Lines!$C$84="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$84)&amp;IF(Lines!$C$85="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$85)))</f>
         <v/>
       </c>
       <c r="J16" s="11">
@@ -4553,15 +4451,11 @@
         <v/>
       </c>
       <c r="M16" s="11">
-        <f>IF($D16&lt;&gt;"yes","",Lines!$C$88)</f>
+        <f>IF(D16&lt;&gt;"yes",D16,IF(E16="","","Subject: "&amp;E16)&amp;IF(F16="","",CHAR(10)&amp;"Preview: "&amp;F16)&amp;IF(G16="","",CHAR(10)&amp;"Kicker: "&amp;G16)&amp;IF(H16="","",CHAR(10)&amp;"Headline: "&amp;H16)&amp;IF(I16="","",IF(E16&amp;F16&amp;G16&amp;H16="","",CHAR(10)&amp;CHAR(10))&amp;I16)&amp;IF(J16="","",CHAR(10)&amp;CHAR(10)&amp;"CTA: "&amp;J16)&amp;IF(K16="","",CHAR(10)&amp;CHAR(10)&amp;"Card: "&amp;K16)&amp;IF(L16="","",CHAR(10)&amp;CHAR(10)&amp;"Quote: "&amp;L16))</f>
         <v/>
       </c>
       <c r="N16" s="11">
-        <f>IF(D16&lt;&gt;"yes",D16,IF(E16="","","Subject: "&amp;E16)&amp;IF(F16="","",CHAR(10)&amp;"Preview: "&amp;F16)&amp;IF(G16="","",CHAR(10)&amp;"Kicker: "&amp;G16)&amp;IF(H16="","",CHAR(10)&amp;"Headline: "&amp;H16)&amp;IF(I16="","",IF(E16&amp;F16&amp;G16&amp;H16="","",CHAR(10)&amp;CHAR(10))&amp;I16)&amp;IF(J16="","",CHAR(10)&amp;CHAR(10)&amp;"CTA: "&amp;J16)&amp;IF(K16="","",CHAR(10)&amp;CHAR(10)&amp;"Card: "&amp;K16)&amp;IF(L16="","",CHAR(10)&amp;CHAR(10)&amp;"Quote: "&amp;L16)&amp;IF(M16="","",CHAR(10)&amp;CHAR(10)&amp;"Footer: "&amp;M16))</f>
-        <v/>
-      </c>
-      <c r="O16" s="11">
-        <f>LEN(N16)</f>
+        <f>LEN(M16)</f>
         <v/>
       </c>
     </row>
@@ -4600,7 +4494,7 @@
         <v/>
       </c>
       <c r="I17" s="11">
-        <f>IF($D17&lt;&gt;"yes","",(Lines!$C$90&amp;IF(Inputs!$B$36="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$36)&amp;IF(Inputs!$B$64="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$64)&amp;IF(IF(Inputs!$B$18="draw",Lines!$C$91,Lines!$C$92)="","",CHAR(10)&amp;CHAR(10)&amp;IF(Inputs!$B$18="draw",Lines!$C$91,Lines!$C$92))))</f>
+        <f>IF($D17&lt;&gt;"yes","",(Lines!$C$87&amp;IF(Inputs!$B$36="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$36)&amp;IF(Inputs!$B$64="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$64)&amp;IF(IF(Inputs!$B$18="draw",Lines!$C$88,Lines!$C$89)="","",CHAR(10)&amp;CHAR(10)&amp;IF(Inputs!$B$18="draw",Lines!$C$88,Lines!$C$89))))</f>
         <v/>
       </c>
       <c r="J17" s="11">
@@ -4616,15 +4510,11 @@
         <v/>
       </c>
       <c r="M17" s="11">
-        <f>""</f>
+        <f>IF(D17&lt;&gt;"yes",D17,IF(E17="","","Subject: "&amp;E17)&amp;IF(F17="","",CHAR(10)&amp;"Preview: "&amp;F17)&amp;IF(G17="","",CHAR(10)&amp;"Kicker: "&amp;G17)&amp;IF(H17="","",CHAR(10)&amp;"Headline: "&amp;H17)&amp;IF(I17="","",IF(E17&amp;F17&amp;G17&amp;H17="","",CHAR(10)&amp;CHAR(10))&amp;I17)&amp;IF(J17="","",CHAR(10)&amp;CHAR(10)&amp;"CTA: "&amp;J17)&amp;IF(K17="","",CHAR(10)&amp;CHAR(10)&amp;"Card: "&amp;K17)&amp;IF(L17="","",CHAR(10)&amp;CHAR(10)&amp;"Quote: "&amp;L17))</f>
         <v/>
       </c>
       <c r="N17" s="11">
-        <f>IF(D17&lt;&gt;"yes",D17,IF(E17="","","Subject: "&amp;E17)&amp;IF(F17="","",CHAR(10)&amp;"Preview: "&amp;F17)&amp;IF(G17="","",CHAR(10)&amp;"Kicker: "&amp;G17)&amp;IF(H17="","",CHAR(10)&amp;"Headline: "&amp;H17)&amp;IF(I17="","",IF(E17&amp;F17&amp;G17&amp;H17="","",CHAR(10)&amp;CHAR(10))&amp;I17)&amp;IF(J17="","",CHAR(10)&amp;CHAR(10)&amp;"CTA: "&amp;J17)&amp;IF(K17="","",CHAR(10)&amp;CHAR(10)&amp;"Card: "&amp;K17)&amp;IF(L17="","",CHAR(10)&amp;CHAR(10)&amp;"Quote: "&amp;L17)&amp;IF(M17="","",CHAR(10)&amp;CHAR(10)&amp;"Footer: "&amp;M17))</f>
-        <v/>
-      </c>
-      <c r="O17" s="11">
-        <f>LEN(N17)</f>
+        <f>LEN(M17)</f>
         <v/>
       </c>
     </row>
@@ -4709,7 +4599,7 @@
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>Every email is: subject, preview, kicker, headline, body paragraphs, CTA, card, quote, footer. Bodies are fixed sentences from the Lines sheet with the same fragments dropped in. Halfway and 5 days to go have no body: they are image-led.</t>
+          <t>Every email is: subject, preview, kicker, headline, body paragraphs, CTA, card, quote. Bodies are fixed sentences from the Lines sheet with the same fragments dropped in. Halfway and 5 days to go have no body: they are image-led.</t>
         </is>
       </c>
     </row>
